--- a/Resultados/Entregable/Reporte_Dip_vf_2.xlsx
+++ b/Resultados/Entregable/Reporte_Dip_vf_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Desktop\Ivan\Laboral\EstrategiaSur\GitProjects\Proyeccion-electoral-congreso\Resultados\Entregable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18ABC0E7-EF2B-42EB-9CF0-147180F966CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C24FE0E-FBD7-459C-ACC9-194A3767EBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen de Pactos" sheetId="33" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="80">
   <si>
     <t>Esc</t>
   </si>
@@ -851,6 +851,12 @@
 </t>
     </r>
   </si>
+  <si>
+    <t>Personalizado 3 CHV+</t>
+  </si>
+  <si>
+    <t>Personalizado 3 CHV</t>
+  </si>
 </sst>
 </file>
 
@@ -1190,7 +1196,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1237,6 +1243,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -1269,7 +1276,28 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="115">
+  <dxfs count="142">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1280,7 +1308,157 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1301,7 +1479,42 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1315,14 +1528,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1330,13 +1536,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1395,6 +1594,55 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
@@ -1403,6 +1651,243 @@
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1472,6 +1957,149 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -1480,13 +2108,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1510,7 +2131,28 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1524,450 +2166,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2009,7 +2208,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF7030A0"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2023,28 +2236,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2072,6 +2264,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
@@ -2079,14 +2278,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2453,6 +2652,106 @@
         <a:xfrm>
           <a:off x="36925251" y="5868213"/>
           <a:ext cx="4451349" cy="549361"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>172263</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>3438525</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>181874</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagen 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9AE5277-13B7-493A-8D22-866E7F0ABB8D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="42919651" y="5938063"/>
+          <a:ext cx="4448174" cy="562061"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>6351</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>172263</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>3425825</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>181874</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagen 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{726FF3FF-3F6C-4242-9402-4EEC9DB7DEAC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="48926751" y="5938063"/>
+          <a:ext cx="4448174" cy="562061"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -24639,7 +24938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7CAECAB-FB20-46F5-B407-265A1B6AF463}">
-  <dimension ref="B2:AA27"/>
+  <dimension ref="B2:AI27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.7265625" customWidth="1"/>
@@ -24656,9 +24955,13 @@
     <col min="23" max="23" width="49.6328125" customWidth="1"/>
     <col min="26" max="26" width="14.7265625" customWidth="1"/>
     <col min="27" max="27" width="49.6328125" customWidth="1"/>
+    <col min="30" max="30" width="14.7265625" customWidth="1"/>
+    <col min="31" max="31" width="49.6328125" customWidth="1"/>
+    <col min="34" max="34" width="14.7265625" customWidth="1"/>
+    <col min="35" max="35" width="49.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
@@ -24701,8 +25004,20 @@
       <c r="AA2" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="2:27" ht="77" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:35" ht="77" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="10" t="s">
         <v>8</v>
       </c>
@@ -24757,8 +25072,20 @@
       <c r="AA3" s="31" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD3" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE3" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH3" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI3" s="31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B4" s="33" t="s">
         <v>40</v>
       </c>
@@ -24813,8 +25140,20 @@
       <c r="AA4" s="33" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD4" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE4" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH4" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="AI4" s="33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
@@ -24857,8 +25196,20 @@
       <c r="AA5" s="12" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE5" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI5" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>12</v>
       </c>
@@ -24901,8 +25252,20 @@
       <c r="AA6" s="12" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI6" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B7" s="11" t="s">
         <v>38</v>
       </c>
@@ -24945,8 +25308,20 @@
       <c r="AA7" s="12" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="8" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE7" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI7" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B8" s="11" t="s">
         <v>17</v>
       </c>
@@ -24989,8 +25364,20 @@
       <c r="AA8" s="12" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI8" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B9" s="13" t="s">
         <v>23</v>
       </c>
@@ -25033,8 +25420,20 @@
       <c r="AA9" s="12" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE9" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI9" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B10" s="13" t="s">
         <v>13</v>
       </c>
@@ -25077,8 +25476,20 @@
       <c r="AA10" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE10" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI10" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B11" s="13" t="s">
         <v>19</v>
       </c>
@@ -25121,8 +25532,20 @@
       <c r="AA11" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD11" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE11" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH11" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI11" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B12" s="13" t="s">
         <v>15</v>
       </c>
@@ -25165,8 +25588,20 @@
       <c r="AA12" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="13" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE12" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI12" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B13" s="13" t="s">
         <v>26</v>
       </c>
@@ -25209,8 +25644,20 @@
       <c r="AA13" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE13" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI13" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B14" s="14" t="s">
         <v>21</v>
       </c>
@@ -25253,8 +25700,20 @@
       <c r="AA14" s="12" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD14" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE14" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH14" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI14" s="20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B15" s="14" t="s">
         <v>24</v>
       </c>
@@ -25297,8 +25756,20 @@
       <c r="AA15" s="12" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD15" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE15" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH15" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI15" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B16" s="14" t="s">
         <v>16</v>
       </c>
@@ -25341,8 +25812,20 @@
       <c r="AA16" s="12" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD16" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE16" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH16" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI16" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B17" s="14" t="s">
         <v>27</v>
       </c>
@@ -25385,8 +25868,20 @@
       <c r="AA17" s="12" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD17" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE17" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH17" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI17" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B18" s="14" t="s">
         <v>20</v>
       </c>
@@ -25429,8 +25924,20 @@
       <c r="AA18" s="12" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD18" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE18" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH18" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI18" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B19" s="14" t="s">
         <v>14</v>
       </c>
@@ -25473,8 +25980,20 @@
       <c r="AA19" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD19" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE19" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH19" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI19" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B20" s="14" t="s">
         <v>22</v>
       </c>
@@ -25517,8 +26036,20 @@
       <c r="AA20" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD20" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE20" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI20" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B21" s="15" t="s">
         <v>45</v>
       </c>
@@ -25561,8 +26092,20 @@
       <c r="AA21" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE21" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH21" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI21" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B22" s="16" t="s">
         <v>18</v>
       </c>
@@ -25605,8 +26148,20 @@
       <c r="AA22" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE22" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI22" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B23" s="17" t="s">
         <v>25</v>
       </c>
@@ -25649,8 +26204,20 @@
       <c r="AA23" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD23" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE23" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH23" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI23" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B24" s="18" t="s">
         <v>49</v>
       </c>
@@ -25693,8 +26260,20 @@
       <c r="AA24" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE24" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH24" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI24" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B25" s="18" t="s">
         <v>39</v>
       </c>
@@ -25737,8 +26316,20 @@
       <c r="AA25" s="12" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD25" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE25" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI25" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B26" s="18" t="s">
         <v>51</v>
       </c>
@@ -25781,8 +26372,20 @@
       <c r="AA26" s="12" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="AD26" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH26" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI26" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B27" s="19" t="s">
         <v>37</v>
       </c>
@@ -25825,387 +26428,488 @@
       <c r="AA27" s="20" t="s">
         <v>53</v>
       </c>
+      <c r="AD27" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE27" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH27" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI27" s="12" t="s">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C27">
-    <cfRule type="cellIs" dxfId="114" priority="109" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="155" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="140" priority="149" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="110" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="151" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="138" priority="150" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="111" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="112" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="152" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="113" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="153" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="114" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="154" operator="equal">
       <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="115" operator="equal">
-      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:G27">
-    <cfRule type="cellIs" dxfId="107" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="111" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="110" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="132" priority="109" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="131" priority="108" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="130" priority="107" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="68" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="69" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="70" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="71" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="112" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="73" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="113" operator="equal">
       <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:G27">
-    <cfRule type="cellIs" dxfId="100" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="106" operator="equal">
       <formula>"p8"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:K4">
-    <cfRule type="cellIs" dxfId="99" priority="102" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="142" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="103" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="143" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="104" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="148" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="123" priority="147" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="122" priority="146" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="145" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="144" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="105" operator="equal">
-      <formula>"p4"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:K27 AD5:AE27">
+    <cfRule type="cellIs" dxfId="119" priority="95" operator="equal">
+      <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="106" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="107" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="108" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K27">
-    <cfRule type="cellIs" dxfId="92" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="93" operator="equal">
       <formula>"p13"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="94" operator="equal">
       <formula>"p12"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="55" operator="equal">
-      <formula>"p11"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="96" operator="equal">
       <formula>"p10"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="97" operator="equal">
       <formula>"p9"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K27">
-    <cfRule type="cellIs" dxfId="87" priority="58" operator="equal">
-      <formula>"p8"</formula>
+  <conditionalFormatting sqref="K5:K27 AE5:AE27">
+    <cfRule type="cellIs" dxfId="114" priority="105" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="102" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="104" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="103" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="110" priority="101" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="100" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="99" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="60" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="61" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="62" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="63" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="64" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="65" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="107" priority="98" operator="equal">
+      <formula>"p8"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:O4">
-    <cfRule type="cellIs" dxfId="79" priority="95" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="138" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="141" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="104" priority="140" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="139" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="136" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="101" priority="135" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="96" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="97" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="137" operator="equal">
       <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="98" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="99" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="100" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="101" operator="equal">
-      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O27">
-    <cfRule type="cellIs" dxfId="72" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="84" operator="equal">
+      <formula>"p9"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="98" priority="82" operator="equal">
+      <formula>"p11"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="81" operator="equal">
+      <formula>"p12"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="80" operator="equal">
       <formula>"p13"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="41" operator="equal">
-      <formula>"p12"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="42" operator="equal">
-      <formula>"p11"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="83" operator="equal">
       <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="44" operator="equal">
-      <formula>"p9"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O5:O27">
-    <cfRule type="cellIs" dxfId="67" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="85" operator="equal">
       <formula>"p8"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="86" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="87" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="88" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="89" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="90" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="91" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="92" operator="equal">
       <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4:S4">
-    <cfRule type="cellIs" dxfId="59" priority="88" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="128" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="89" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="85" priority="134" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="133" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="83" priority="132" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="131" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="130" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="91" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="92" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="93" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="94" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="80" priority="129" operator="equal">
+      <formula>"p6"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:S27">
-    <cfRule type="cellIs" dxfId="52" priority="27" operator="equal">
-      <formula>"p13"</formula>
+    <cfRule type="cellIs" dxfId="79" priority="71" operator="equal">
+      <formula>"p9"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="68" operator="equal">
       <formula>"p12"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="70" operator="equal">
+      <formula>"p10"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="69" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="30" operator="equal">
-      <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="31" operator="equal">
-      <formula>"p9"</formula>
+    <cfRule type="cellIs" dxfId="75" priority="67" operator="equal">
+      <formula>"p13"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:S27">
-    <cfRule type="cellIs" dxfId="47" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="76" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="75" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="74" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="71" priority="73" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="72" operator="equal">
       <formula>"p8"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="33" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="69" priority="79" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="34" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="35" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="36" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="37" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="78" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="39" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="67" priority="77" operator="equal">
+      <formula>"p3"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V4:W4">
-    <cfRule type="cellIs" dxfId="39" priority="81" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="122" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="127" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="126" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="125" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="124" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="123" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="84" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="85" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="86" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="87" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="60" priority="121" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W27">
-    <cfRule type="cellIs" dxfId="32" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="54" operator="equal">
       <formula>"p13"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="15" operator="equal">
-      <formula>"p12"</formula>
+    <cfRule type="cellIs" dxfId="58" priority="57" operator="equal">
+      <formula>"p10"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="58" operator="equal">
+      <formula>"p9"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="56" priority="56" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="17" operator="equal">
-      <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="18" operator="equal">
-      <formula>"p9"</formula>
+    <cfRule type="cellIs" dxfId="55" priority="55" operator="equal">
+      <formula>"p12"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W27">
-    <cfRule type="cellIs" dxfId="27" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="59" operator="equal">
       <formula>"p8"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="60" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="61" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="62" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="63" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="64" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="66" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="65" operator="equal">
       <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="26" operator="equal">
-      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z4:AA4">
-    <cfRule type="cellIs" dxfId="19" priority="74" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="116" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="115" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="114" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="75" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="76" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="117" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="78" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="118" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="79" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="119" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="80" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="120" operator="equal">
       <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z5:AA27">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="41" operator="equal">
       <formula>"p13"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="42" operator="equal">
       <formula>"p12"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="43" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="45" operator="equal">
+      <formula>"p9"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="44" operator="equal">
       <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
-      <formula>"p9"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA5:AA27">
+    <cfRule type="cellIs" dxfId="34" priority="48" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="53" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="52" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="51" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="49" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="47" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
+      <formula>"p8"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="50" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD4:AE4">
+    <cfRule type="cellIs" dxfId="26" priority="38" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="37" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="36" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="35" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="34" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="40" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="39" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH4:AI4">
+    <cfRule type="cellIs" dxfId="19" priority="19" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="17" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="20" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH5:AI27">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+      <formula>"p12"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+      <formula>"p11"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+      <formula>"p10"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+      <formula>"p9"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"p13"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI5:AI27">
     <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"p8"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
+      <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
-      <formula>"p5"</formula>
+    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="12" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="10" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="11" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="12" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="13" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
+      <formula>"p5"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -26628,116 +27332,116 @@
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="37"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="40"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="40"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="40"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="40"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="40"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="40"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="40"/>
     </row>
     <row r="23" spans="2:10" ht="141" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -27075,96 +27779,96 @@
     </row>
     <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="37"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="40"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="40"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="40"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
     </row>
     <row r="20" spans="2:8" ht="87" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="40"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
     </row>
     <row r="23" spans="2:8" ht="74.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -27631,126 +28335,126 @@
     </row>
     <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="37"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="40"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="40"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="40"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="40"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="40"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="40"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="40"/>
     </row>
     <row r="23" spans="2:11" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -28216,126 +28920,126 @@
     </row>
     <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="37"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="40"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="40"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="40"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="40"/>
     </row>
     <row r="20" spans="2:11" ht="69.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="40"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="40"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="40"/>
     </row>
     <row r="23" spans="2:11" ht="62.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -28716,106 +29420,106 @@
     </row>
     <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="37"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="40"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="40"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="40"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="40"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="40"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="40"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="40"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="40"/>
     </row>
     <row r="23" spans="2:9" ht="131" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -29195,106 +29899,106 @@
     </row>
     <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="37"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="40"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="40"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="40"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="40"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="40"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="40"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="40"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="40"/>
     </row>
     <row r="23" spans="2:9" ht="112.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -29718,116 +30422,116 @@
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="37"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="40"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="40"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="40"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="40"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="40"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="40"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="40"/>
     </row>
     <row r="23" spans="2:10" ht="140.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -30421,156 +31125,156 @@
     </row>
     <row r="13" spans="1:14" ht="6.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="36"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="37"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="40"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="40"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="40"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="40"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="40"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="40"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="40"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="40"/>
     </row>
     <row r="23" spans="2:14" ht="131" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="41"/>
-      <c r="L23" s="41"/>
-      <c r="M23" s="41"/>
-      <c r="N23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -31036,126 +31740,126 @@
     </row>
     <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="37"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="40"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="40"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="40"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="40"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="40"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="40"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="40"/>
     </row>
     <row r="23" spans="2:11" ht="105" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -31624,126 +32328,126 @@
     </row>
     <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="37"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="40"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="40"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="40"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="40"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="40"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="40"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="40"/>
     </row>
     <row r="23" spans="2:11" ht="98.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -32211,126 +32915,126 @@
     </row>
     <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="37"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="40"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="40"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="40"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="40"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="40"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="40"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="40"/>
     </row>
     <row r="23" spans="2:11" ht="146" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -32756,116 +33460,116 @@
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="37"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="40"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="40"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="40"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="40"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="40"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="40"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="40"/>
     </row>
     <row r="23" spans="2:10" ht="116.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -33332,126 +34036,126 @@
     </row>
     <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="37"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="40"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="40"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="40"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="40"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="40"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="40"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="40"/>
     </row>
     <row r="23" spans="2:11" ht="116.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -33919,126 +34623,126 @@
     </row>
     <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="37"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="40"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="40"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="40"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="40"/>
     </row>
     <row r="20" spans="2:11" ht="74" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="40"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="40"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="40"/>
     </row>
     <row r="23" spans="2:11" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -34378,96 +35082,96 @@
     </row>
     <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="37"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="40"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="40"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="40"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="39"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
     </row>
     <row r="20" spans="2:8" ht="71" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="39"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="40"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="39"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="39"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
     </row>
     <row r="23" spans="2:8" ht="89" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="42"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Resultados/Entregable/Reporte_Dip_vf_2.xlsx
+++ b/Resultados/Entregable/Reporte_Dip_vf_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Desktop\Ivan\Laboral\EstrategiaSur\GitProjects\Proyeccion-electoral-congreso\Resultados\Entregable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C24FE0E-FBD7-459C-ACC9-194A3767EBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E112D6-04B3-4323-ACB1-8743BEB76079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="15" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen de Pactos" sheetId="33" r:id="rId1"/>
@@ -40,6 +40,8 @@
     <externalReference r:id="rId23"/>
     <externalReference r:id="rId24"/>
     <externalReference r:id="rId25"/>
+    <externalReference r:id="rId26"/>
+    <externalReference r:id="rId27"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="80">
   <si>
     <t>Esc</t>
   </si>
@@ -1280,14 +1282,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1295,170 +1290,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1479,7 +1310,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1493,35 +1331,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1529,13 +1346,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1594,7 +1404,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1608,7 +1418,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1616,13 +1433,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1651,243 +1461,6 @@
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1957,149 +1530,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -2108,6 +1538,13 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2131,7 +1568,28 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2145,7 +1603,28 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2159,6 +1638,86 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
@@ -2166,7 +1725,450 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2208,7 +2210,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2222,21 +2238,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2264,6 +2273,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="2" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
@@ -2271,21 +2287,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2769,13 +2771,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>179667</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2824,13 +2826,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>27267</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>149225</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2879,13 +2881,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>275904</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2934,13 +2936,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>352104</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2989,13 +2991,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>9526</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>27410</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3044,13 +3046,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>215900</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>1818</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3099,13 +3101,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>173268</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3154,13 +3156,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>15875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>162512</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3209,13 +3211,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>135556</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3264,13 +3266,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>59356</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3319,13 +3321,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>273050</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>103806</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3374,13 +3376,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>263525</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>135749</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3429,13 +3431,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>82551</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>120651</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>295276</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>161150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3484,13 +3486,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>330200</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>164324</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3539,13 +3541,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>106642</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5917,6 +5919,4680 @@
           </cell>
           <cell r="Z29">
             <v>0.13883301897193301</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="resultados_integracion_partido_"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Distrito</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>AH</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>AMA</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>DEM</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>EVO</v>
+          </cell>
+          <cell r="F1" t="str">
+            <v>FA</v>
+          </cell>
+          <cell r="G1" t="str">
+            <v>FREVS</v>
+          </cell>
+          <cell r="H1" t="str">
+            <v>IGU</v>
+          </cell>
+          <cell r="I1" t="str">
+            <v>IND</v>
+          </cell>
+          <cell r="J1" t="str">
+            <v>PAVP</v>
+          </cell>
+          <cell r="K1" t="str">
+            <v>PCCH</v>
+          </cell>
+          <cell r="L1" t="str">
+            <v>PDC</v>
+          </cell>
+          <cell r="M1" t="str">
+            <v>PDG</v>
+          </cell>
+          <cell r="N1" t="str">
+            <v>PH</v>
+          </cell>
+          <cell r="O1" t="str">
+            <v>PL</v>
+          </cell>
+          <cell r="P1" t="str">
+            <v>POP</v>
+          </cell>
+          <cell r="Q1" t="str">
+            <v>PPD</v>
+          </cell>
+          <cell r="R1" t="str">
+            <v>PR</v>
+          </cell>
+          <cell r="S1" t="str">
+            <v>PS</v>
+          </cell>
+          <cell r="T1" t="str">
+            <v>PSC</v>
+          </cell>
+          <cell r="U1" t="str">
+            <v>PTR</v>
+          </cell>
+          <cell r="V1" t="str">
+            <v>REP</v>
+          </cell>
+          <cell r="W1" t="str">
+            <v>RN</v>
+          </cell>
+          <cell r="X1" t="str">
+            <v>UDI</v>
+          </cell>
+          <cell r="Y1" t="str">
+            <v>Votos Blancos</v>
+          </cell>
+          <cell r="Z1" t="str">
+            <v>Votos Nulos</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+          <cell r="B2">
+            <v>0</v>
+          </cell>
+          <cell r="C2">
+            <v>0</v>
+          </cell>
+          <cell r="D2">
+            <v>0</v>
+          </cell>
+          <cell r="E2">
+            <v>0</v>
+          </cell>
+          <cell r="F2">
+            <v>0</v>
+          </cell>
+          <cell r="G2">
+            <v>0</v>
+          </cell>
+          <cell r="H2">
+            <v>0</v>
+          </cell>
+          <cell r="I2">
+            <v>0</v>
+          </cell>
+          <cell r="J2">
+            <v>0</v>
+          </cell>
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="L2">
+            <v>0</v>
+          </cell>
+          <cell r="M2">
+            <v>0</v>
+          </cell>
+          <cell r="N2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+          <cell r="P2">
+            <v>0</v>
+          </cell>
+          <cell r="Q2">
+            <v>0</v>
+          </cell>
+          <cell r="R2">
+            <v>0</v>
+          </cell>
+          <cell r="S2">
+            <v>0</v>
+          </cell>
+          <cell r="T2">
+            <v>0</v>
+          </cell>
+          <cell r="U2">
+            <v>0</v>
+          </cell>
+          <cell r="V2">
+            <v>1</v>
+          </cell>
+          <cell r="W2">
+            <v>1</v>
+          </cell>
+          <cell r="X2">
+            <v>0</v>
+          </cell>
+          <cell r="Y2">
+            <v>0</v>
+          </cell>
+          <cell r="Z2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+          <cell r="B3">
+            <v>0</v>
+          </cell>
+          <cell r="C3">
+            <v>0</v>
+          </cell>
+          <cell r="D3">
+            <v>0</v>
+          </cell>
+          <cell r="E3">
+            <v>0</v>
+          </cell>
+          <cell r="F3">
+            <v>0</v>
+          </cell>
+          <cell r="G3">
+            <v>0</v>
+          </cell>
+          <cell r="H3">
+            <v>0</v>
+          </cell>
+          <cell r="I3">
+            <v>0</v>
+          </cell>
+          <cell r="J3">
+            <v>0</v>
+          </cell>
+          <cell r="K3">
+            <v>0</v>
+          </cell>
+          <cell r="L3">
+            <v>1</v>
+          </cell>
+          <cell r="M3">
+            <v>0</v>
+          </cell>
+          <cell r="N3">
+            <v>0</v>
+          </cell>
+          <cell r="O3">
+            <v>0</v>
+          </cell>
+          <cell r="P3">
+            <v>0</v>
+          </cell>
+          <cell r="Q3">
+            <v>0</v>
+          </cell>
+          <cell r="R3">
+            <v>1</v>
+          </cell>
+          <cell r="S3">
+            <v>0</v>
+          </cell>
+          <cell r="T3">
+            <v>0</v>
+          </cell>
+          <cell r="U3">
+            <v>0</v>
+          </cell>
+          <cell r="V3">
+            <v>0</v>
+          </cell>
+          <cell r="W3">
+            <v>1</v>
+          </cell>
+          <cell r="X3">
+            <v>0</v>
+          </cell>
+          <cell r="Y3">
+            <v>0</v>
+          </cell>
+          <cell r="Z3">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+          <cell r="B4">
+            <v>0</v>
+          </cell>
+          <cell r="C4">
+            <v>0</v>
+          </cell>
+          <cell r="D4">
+            <v>0</v>
+          </cell>
+          <cell r="E4">
+            <v>0</v>
+          </cell>
+          <cell r="F4">
+            <v>0</v>
+          </cell>
+          <cell r="G4">
+            <v>1</v>
+          </cell>
+          <cell r="H4">
+            <v>0</v>
+          </cell>
+          <cell r="I4">
+            <v>0</v>
+          </cell>
+          <cell r="J4">
+            <v>0</v>
+          </cell>
+          <cell r="K4">
+            <v>1</v>
+          </cell>
+          <cell r="L4">
+            <v>0</v>
+          </cell>
+          <cell r="M4">
+            <v>0</v>
+          </cell>
+          <cell r="N4">
+            <v>0</v>
+          </cell>
+          <cell r="O4">
+            <v>0</v>
+          </cell>
+          <cell r="P4">
+            <v>0</v>
+          </cell>
+          <cell r="Q4">
+            <v>0</v>
+          </cell>
+          <cell r="R4">
+            <v>1</v>
+          </cell>
+          <cell r="S4">
+            <v>0</v>
+          </cell>
+          <cell r="T4">
+            <v>0</v>
+          </cell>
+          <cell r="U4">
+            <v>0</v>
+          </cell>
+          <cell r="V4">
+            <v>1</v>
+          </cell>
+          <cell r="W4">
+            <v>1</v>
+          </cell>
+          <cell r="X4">
+            <v>0</v>
+          </cell>
+          <cell r="Y4">
+            <v>0</v>
+          </cell>
+          <cell r="Z4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+          <cell r="B5">
+            <v>0</v>
+          </cell>
+          <cell r="C5">
+            <v>0</v>
+          </cell>
+          <cell r="D5">
+            <v>0</v>
+          </cell>
+          <cell r="E5">
+            <v>0</v>
+          </cell>
+          <cell r="F5">
+            <v>0</v>
+          </cell>
+          <cell r="G5">
+            <v>1</v>
+          </cell>
+          <cell r="H5">
+            <v>0</v>
+          </cell>
+          <cell r="I5">
+            <v>0</v>
+          </cell>
+          <cell r="J5">
+            <v>0</v>
+          </cell>
+          <cell r="K5">
+            <v>1</v>
+          </cell>
+          <cell r="L5">
+            <v>0</v>
+          </cell>
+          <cell r="M5">
+            <v>0</v>
+          </cell>
+          <cell r="N5">
+            <v>0</v>
+          </cell>
+          <cell r="O5">
+            <v>0</v>
+          </cell>
+          <cell r="P5">
+            <v>0</v>
+          </cell>
+          <cell r="Q5">
+            <v>0</v>
+          </cell>
+          <cell r="R5">
+            <v>0</v>
+          </cell>
+          <cell r="S5">
+            <v>1</v>
+          </cell>
+          <cell r="T5">
+            <v>0</v>
+          </cell>
+          <cell r="U5">
+            <v>0</v>
+          </cell>
+          <cell r="V5">
+            <v>1</v>
+          </cell>
+          <cell r="W5">
+            <v>1</v>
+          </cell>
+          <cell r="X5">
+            <v>0</v>
+          </cell>
+          <cell r="Y5">
+            <v>0</v>
+          </cell>
+          <cell r="Z5">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+          <cell r="B6">
+            <v>0</v>
+          </cell>
+          <cell r="C6">
+            <v>0</v>
+          </cell>
+          <cell r="D6">
+            <v>0</v>
+          </cell>
+          <cell r="E6">
+            <v>0</v>
+          </cell>
+          <cell r="F6">
+            <v>1</v>
+          </cell>
+          <cell r="G6">
+            <v>0</v>
+          </cell>
+          <cell r="H6">
+            <v>0</v>
+          </cell>
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+          <cell r="J6">
+            <v>0</v>
+          </cell>
+          <cell r="K6">
+            <v>1</v>
+          </cell>
+          <cell r="L6">
+            <v>1</v>
+          </cell>
+          <cell r="M6">
+            <v>0</v>
+          </cell>
+          <cell r="N6">
+            <v>0</v>
+          </cell>
+          <cell r="O6">
+            <v>0</v>
+          </cell>
+          <cell r="P6">
+            <v>0</v>
+          </cell>
+          <cell r="Q6">
+            <v>0</v>
+          </cell>
+          <cell r="R6">
+            <v>0</v>
+          </cell>
+          <cell r="S6">
+            <v>1</v>
+          </cell>
+          <cell r="T6">
+            <v>0</v>
+          </cell>
+          <cell r="U6">
+            <v>0</v>
+          </cell>
+          <cell r="V6">
+            <v>1</v>
+          </cell>
+          <cell r="W6">
+            <v>1</v>
+          </cell>
+          <cell r="X6">
+            <v>1</v>
+          </cell>
+          <cell r="Y6">
+            <v>0</v>
+          </cell>
+          <cell r="Z6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+          <cell r="B7">
+            <v>0</v>
+          </cell>
+          <cell r="C7">
+            <v>0</v>
+          </cell>
+          <cell r="D7">
+            <v>0</v>
+          </cell>
+          <cell r="E7">
+            <v>0</v>
+          </cell>
+          <cell r="F7">
+            <v>1</v>
+          </cell>
+          <cell r="G7">
+            <v>0</v>
+          </cell>
+          <cell r="H7">
+            <v>0</v>
+          </cell>
+          <cell r="I7">
+            <v>0</v>
+          </cell>
+          <cell r="J7">
+            <v>0</v>
+          </cell>
+          <cell r="K7">
+            <v>1</v>
+          </cell>
+          <cell r="L7">
+            <v>1</v>
+          </cell>
+          <cell r="M7">
+            <v>0</v>
+          </cell>
+          <cell r="N7">
+            <v>0</v>
+          </cell>
+          <cell r="O7">
+            <v>0</v>
+          </cell>
+          <cell r="P7">
+            <v>0</v>
+          </cell>
+          <cell r="Q7">
+            <v>0</v>
+          </cell>
+          <cell r="R7">
+            <v>0</v>
+          </cell>
+          <cell r="S7">
+            <v>1</v>
+          </cell>
+          <cell r="T7">
+            <v>0</v>
+          </cell>
+          <cell r="U7">
+            <v>0</v>
+          </cell>
+          <cell r="V7">
+            <v>2</v>
+          </cell>
+          <cell r="W7">
+            <v>2</v>
+          </cell>
+          <cell r="X7">
+            <v>0</v>
+          </cell>
+          <cell r="Y7">
+            <v>0</v>
+          </cell>
+          <cell r="Z7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+          <cell r="B8">
+            <v>0</v>
+          </cell>
+          <cell r="C8">
+            <v>0</v>
+          </cell>
+          <cell r="D8">
+            <v>0</v>
+          </cell>
+          <cell r="E8">
+            <v>0</v>
+          </cell>
+          <cell r="F8">
+            <v>2</v>
+          </cell>
+          <cell r="G8">
+            <v>0</v>
+          </cell>
+          <cell r="H8">
+            <v>0</v>
+          </cell>
+          <cell r="I8">
+            <v>0</v>
+          </cell>
+          <cell r="J8">
+            <v>0</v>
+          </cell>
+          <cell r="K8">
+            <v>1</v>
+          </cell>
+          <cell r="L8">
+            <v>1</v>
+          </cell>
+          <cell r="M8">
+            <v>0</v>
+          </cell>
+          <cell r="N8">
+            <v>0</v>
+          </cell>
+          <cell r="O8">
+            <v>0</v>
+          </cell>
+          <cell r="P8">
+            <v>0</v>
+          </cell>
+          <cell r="Q8">
+            <v>0</v>
+          </cell>
+          <cell r="R8">
+            <v>0</v>
+          </cell>
+          <cell r="S8">
+            <v>0</v>
+          </cell>
+          <cell r="T8">
+            <v>0</v>
+          </cell>
+          <cell r="U8">
+            <v>0</v>
+          </cell>
+          <cell r="V8">
+            <v>2</v>
+          </cell>
+          <cell r="W8">
+            <v>1</v>
+          </cell>
+          <cell r="X8">
+            <v>1</v>
+          </cell>
+          <cell r="Y8">
+            <v>0</v>
+          </cell>
+          <cell r="Z8">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+          <cell r="B9">
+            <v>0</v>
+          </cell>
+          <cell r="C9">
+            <v>0</v>
+          </cell>
+          <cell r="D9">
+            <v>0</v>
+          </cell>
+          <cell r="E9">
+            <v>0</v>
+          </cell>
+          <cell r="F9">
+            <v>3</v>
+          </cell>
+          <cell r="G9">
+            <v>0</v>
+          </cell>
+          <cell r="H9">
+            <v>0</v>
+          </cell>
+          <cell r="I9">
+            <v>0</v>
+          </cell>
+          <cell r="J9">
+            <v>0</v>
+          </cell>
+          <cell r="K9">
+            <v>1</v>
+          </cell>
+          <cell r="L9">
+            <v>1</v>
+          </cell>
+          <cell r="M9">
+            <v>0</v>
+          </cell>
+          <cell r="N9">
+            <v>0</v>
+          </cell>
+          <cell r="O9">
+            <v>0</v>
+          </cell>
+          <cell r="P9">
+            <v>0</v>
+          </cell>
+          <cell r="Q9">
+            <v>0</v>
+          </cell>
+          <cell r="R9">
+            <v>0</v>
+          </cell>
+          <cell r="S9">
+            <v>0</v>
+          </cell>
+          <cell r="T9">
+            <v>0</v>
+          </cell>
+          <cell r="U9">
+            <v>0</v>
+          </cell>
+          <cell r="V9">
+            <v>1</v>
+          </cell>
+          <cell r="W9">
+            <v>1</v>
+          </cell>
+          <cell r="X9">
+            <v>1</v>
+          </cell>
+          <cell r="Y9">
+            <v>0</v>
+          </cell>
+          <cell r="Z9">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+          <cell r="B10">
+            <v>0</v>
+          </cell>
+          <cell r="C10">
+            <v>0</v>
+          </cell>
+          <cell r="D10">
+            <v>0</v>
+          </cell>
+          <cell r="E10">
+            <v>0</v>
+          </cell>
+          <cell r="F10">
+            <v>1</v>
+          </cell>
+          <cell r="G10">
+            <v>0</v>
+          </cell>
+          <cell r="H10">
+            <v>0</v>
+          </cell>
+          <cell r="I10">
+            <v>0</v>
+          </cell>
+          <cell r="J10">
+            <v>0</v>
+          </cell>
+          <cell r="K10">
+            <v>2</v>
+          </cell>
+          <cell r="L10">
+            <v>0</v>
+          </cell>
+          <cell r="M10">
+            <v>0</v>
+          </cell>
+          <cell r="N10">
+            <v>0</v>
+          </cell>
+          <cell r="O10">
+            <v>0</v>
+          </cell>
+          <cell r="P10">
+            <v>0</v>
+          </cell>
+          <cell r="Q10">
+            <v>0</v>
+          </cell>
+          <cell r="R10">
+            <v>0</v>
+          </cell>
+          <cell r="S10">
+            <v>1</v>
+          </cell>
+          <cell r="T10">
+            <v>0</v>
+          </cell>
+          <cell r="U10">
+            <v>0</v>
+          </cell>
+          <cell r="V10">
+            <v>1</v>
+          </cell>
+          <cell r="W10">
+            <v>1</v>
+          </cell>
+          <cell r="X10">
+            <v>1</v>
+          </cell>
+          <cell r="Y10">
+            <v>0</v>
+          </cell>
+          <cell r="Z10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+          <cell r="B11">
+            <v>0</v>
+          </cell>
+          <cell r="C11">
+            <v>0</v>
+          </cell>
+          <cell r="D11">
+            <v>0</v>
+          </cell>
+          <cell r="E11">
+            <v>0</v>
+          </cell>
+          <cell r="F11">
+            <v>3</v>
+          </cell>
+          <cell r="G11">
+            <v>0</v>
+          </cell>
+          <cell r="H11">
+            <v>0</v>
+          </cell>
+          <cell r="I11">
+            <v>0</v>
+          </cell>
+          <cell r="J11">
+            <v>0</v>
+          </cell>
+          <cell r="K11">
+            <v>2</v>
+          </cell>
+          <cell r="L11">
+            <v>0</v>
+          </cell>
+          <cell r="M11">
+            <v>0</v>
+          </cell>
+          <cell r="N11">
+            <v>0</v>
+          </cell>
+          <cell r="O11">
+            <v>0</v>
+          </cell>
+          <cell r="P11">
+            <v>0</v>
+          </cell>
+          <cell r="Q11">
+            <v>0</v>
+          </cell>
+          <cell r="R11">
+            <v>0</v>
+          </cell>
+          <cell r="S11">
+            <v>0</v>
+          </cell>
+          <cell r="T11">
+            <v>0</v>
+          </cell>
+          <cell r="U11">
+            <v>0</v>
+          </cell>
+          <cell r="V11">
+            <v>1</v>
+          </cell>
+          <cell r="W11">
+            <v>1</v>
+          </cell>
+          <cell r="X11">
+            <v>1</v>
+          </cell>
+          <cell r="Y11">
+            <v>0</v>
+          </cell>
+          <cell r="Z11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+          <cell r="B12">
+            <v>0</v>
+          </cell>
+          <cell r="C12">
+            <v>0</v>
+          </cell>
+          <cell r="D12">
+            <v>0</v>
+          </cell>
+          <cell r="E12">
+            <v>1</v>
+          </cell>
+          <cell r="F12">
+            <v>2</v>
+          </cell>
+          <cell r="G12">
+            <v>0</v>
+          </cell>
+          <cell r="H12">
+            <v>0</v>
+          </cell>
+          <cell r="I12">
+            <v>0</v>
+          </cell>
+          <cell r="J12">
+            <v>0</v>
+          </cell>
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+          <cell r="L12">
+            <v>0</v>
+          </cell>
+          <cell r="M12">
+            <v>0</v>
+          </cell>
+          <cell r="N12">
+            <v>0</v>
+          </cell>
+          <cell r="O12">
+            <v>0</v>
+          </cell>
+          <cell r="P12">
+            <v>0</v>
+          </cell>
+          <cell r="Q12">
+            <v>0</v>
+          </cell>
+          <cell r="R12">
+            <v>0</v>
+          </cell>
+          <cell r="S12">
+            <v>0</v>
+          </cell>
+          <cell r="T12">
+            <v>0</v>
+          </cell>
+          <cell r="U12">
+            <v>0</v>
+          </cell>
+          <cell r="V12">
+            <v>1</v>
+          </cell>
+          <cell r="W12">
+            <v>1</v>
+          </cell>
+          <cell r="X12">
+            <v>1</v>
+          </cell>
+          <cell r="Y12">
+            <v>0</v>
+          </cell>
+          <cell r="Z12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+          <cell r="B13">
+            <v>0</v>
+          </cell>
+          <cell r="C13">
+            <v>0</v>
+          </cell>
+          <cell r="D13">
+            <v>0</v>
+          </cell>
+          <cell r="E13">
+            <v>0</v>
+          </cell>
+          <cell r="F13">
+            <v>1</v>
+          </cell>
+          <cell r="G13">
+            <v>0</v>
+          </cell>
+          <cell r="H13">
+            <v>0</v>
+          </cell>
+          <cell r="I13">
+            <v>0</v>
+          </cell>
+          <cell r="J13">
+            <v>1</v>
+          </cell>
+          <cell r="K13">
+            <v>2</v>
+          </cell>
+          <cell r="L13">
+            <v>0</v>
+          </cell>
+          <cell r="M13">
+            <v>0</v>
+          </cell>
+          <cell r="N13">
+            <v>0</v>
+          </cell>
+          <cell r="O13">
+            <v>0</v>
+          </cell>
+          <cell r="P13">
+            <v>0</v>
+          </cell>
+          <cell r="Q13">
+            <v>0</v>
+          </cell>
+          <cell r="R13">
+            <v>0</v>
+          </cell>
+          <cell r="S13">
+            <v>0</v>
+          </cell>
+          <cell r="T13">
+            <v>0</v>
+          </cell>
+          <cell r="U13">
+            <v>0</v>
+          </cell>
+          <cell r="V13">
+            <v>1</v>
+          </cell>
+          <cell r="W13">
+            <v>2</v>
+          </cell>
+          <cell r="X13">
+            <v>0</v>
+          </cell>
+          <cell r="Y13">
+            <v>0</v>
+          </cell>
+          <cell r="Z13">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+          <cell r="B14">
+            <v>0</v>
+          </cell>
+          <cell r="C14">
+            <v>0</v>
+          </cell>
+          <cell r="D14">
+            <v>0</v>
+          </cell>
+          <cell r="E14">
+            <v>0</v>
+          </cell>
+          <cell r="F14">
+            <v>1</v>
+          </cell>
+          <cell r="G14">
+            <v>0</v>
+          </cell>
+          <cell r="H14">
+            <v>0</v>
+          </cell>
+          <cell r="I14">
+            <v>0</v>
+          </cell>
+          <cell r="J14">
+            <v>0</v>
+          </cell>
+          <cell r="K14">
+            <v>1</v>
+          </cell>
+          <cell r="L14">
+            <v>0</v>
+          </cell>
+          <cell r="M14">
+            <v>0</v>
+          </cell>
+          <cell r="N14">
+            <v>0</v>
+          </cell>
+          <cell r="O14">
+            <v>0</v>
+          </cell>
+          <cell r="P14">
+            <v>0</v>
+          </cell>
+          <cell r="Q14">
+            <v>0</v>
+          </cell>
+          <cell r="R14">
+            <v>0</v>
+          </cell>
+          <cell r="S14">
+            <v>1</v>
+          </cell>
+          <cell r="T14">
+            <v>0</v>
+          </cell>
+          <cell r="U14">
+            <v>0</v>
+          </cell>
+          <cell r="V14">
+            <v>1</v>
+          </cell>
+          <cell r="W14">
+            <v>1</v>
+          </cell>
+          <cell r="X14">
+            <v>0</v>
+          </cell>
+          <cell r="Y14">
+            <v>0</v>
+          </cell>
+          <cell r="Z14">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+          <cell r="B15">
+            <v>0</v>
+          </cell>
+          <cell r="C15">
+            <v>0</v>
+          </cell>
+          <cell r="D15">
+            <v>0</v>
+          </cell>
+          <cell r="E15">
+            <v>0</v>
+          </cell>
+          <cell r="F15">
+            <v>1</v>
+          </cell>
+          <cell r="G15">
+            <v>0</v>
+          </cell>
+          <cell r="H15">
+            <v>0</v>
+          </cell>
+          <cell r="I15">
+            <v>0</v>
+          </cell>
+          <cell r="J15">
+            <v>0</v>
+          </cell>
+          <cell r="K15">
+            <v>1</v>
+          </cell>
+          <cell r="L15">
+            <v>0</v>
+          </cell>
+          <cell r="M15">
+            <v>0</v>
+          </cell>
+          <cell r="N15">
+            <v>0</v>
+          </cell>
+          <cell r="O15">
+            <v>0</v>
+          </cell>
+          <cell r="P15">
+            <v>0</v>
+          </cell>
+          <cell r="Q15">
+            <v>0</v>
+          </cell>
+          <cell r="R15">
+            <v>0</v>
+          </cell>
+          <cell r="S15">
+            <v>1</v>
+          </cell>
+          <cell r="T15">
+            <v>0</v>
+          </cell>
+          <cell r="U15">
+            <v>0</v>
+          </cell>
+          <cell r="V15">
+            <v>1</v>
+          </cell>
+          <cell r="W15">
+            <v>1</v>
+          </cell>
+          <cell r="X15">
+            <v>1</v>
+          </cell>
+          <cell r="Y15">
+            <v>0</v>
+          </cell>
+          <cell r="Z15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+          <cell r="B16">
+            <v>0</v>
+          </cell>
+          <cell r="C16">
+            <v>0</v>
+          </cell>
+          <cell r="D16">
+            <v>0</v>
+          </cell>
+          <cell r="E16">
+            <v>0</v>
+          </cell>
+          <cell r="F16">
+            <v>0</v>
+          </cell>
+          <cell r="G16">
+            <v>0</v>
+          </cell>
+          <cell r="H16">
+            <v>0</v>
+          </cell>
+          <cell r="I16">
+            <v>0</v>
+          </cell>
+          <cell r="J16">
+            <v>0</v>
+          </cell>
+          <cell r="K16">
+            <v>0</v>
+          </cell>
+          <cell r="L16">
+            <v>0</v>
+          </cell>
+          <cell r="M16">
+            <v>0</v>
+          </cell>
+          <cell r="N16">
+            <v>0</v>
+          </cell>
+          <cell r="O16">
+            <v>0</v>
+          </cell>
+          <cell r="P16">
+            <v>0</v>
+          </cell>
+          <cell r="Q16">
+            <v>1</v>
+          </cell>
+          <cell r="R16">
+            <v>1</v>
+          </cell>
+          <cell r="S16">
+            <v>1</v>
+          </cell>
+          <cell r="T16">
+            <v>0</v>
+          </cell>
+          <cell r="U16">
+            <v>0</v>
+          </cell>
+          <cell r="V16">
+            <v>1</v>
+          </cell>
+          <cell r="W16">
+            <v>1</v>
+          </cell>
+          <cell r="X16">
+            <v>0</v>
+          </cell>
+          <cell r="Y16">
+            <v>0</v>
+          </cell>
+          <cell r="Z16">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+          <cell r="B17">
+            <v>0</v>
+          </cell>
+          <cell r="C17">
+            <v>0</v>
+          </cell>
+          <cell r="D17">
+            <v>0</v>
+          </cell>
+          <cell r="E17">
+            <v>0</v>
+          </cell>
+          <cell r="F17">
+            <v>0</v>
+          </cell>
+          <cell r="G17">
+            <v>0</v>
+          </cell>
+          <cell r="H17">
+            <v>0</v>
+          </cell>
+          <cell r="I17">
+            <v>0</v>
+          </cell>
+          <cell r="J17">
+            <v>0</v>
+          </cell>
+          <cell r="K17">
+            <v>0</v>
+          </cell>
+          <cell r="L17">
+            <v>0</v>
+          </cell>
+          <cell r="M17">
+            <v>0</v>
+          </cell>
+          <cell r="N17">
+            <v>0</v>
+          </cell>
+          <cell r="O17">
+            <v>0</v>
+          </cell>
+          <cell r="P17">
+            <v>0</v>
+          </cell>
+          <cell r="Q17">
+            <v>0</v>
+          </cell>
+          <cell r="R17">
+            <v>1</v>
+          </cell>
+          <cell r="S17">
+            <v>1</v>
+          </cell>
+          <cell r="T17">
+            <v>0</v>
+          </cell>
+          <cell r="U17">
+            <v>0</v>
+          </cell>
+          <cell r="V17">
+            <v>0</v>
+          </cell>
+          <cell r="W17">
+            <v>1</v>
+          </cell>
+          <cell r="X17">
+            <v>1</v>
+          </cell>
+          <cell r="Y17">
+            <v>0</v>
+          </cell>
+          <cell r="Z17">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+          <cell r="B18">
+            <v>0</v>
+          </cell>
+          <cell r="C18">
+            <v>0</v>
+          </cell>
+          <cell r="D18">
+            <v>0</v>
+          </cell>
+          <cell r="E18">
+            <v>0</v>
+          </cell>
+          <cell r="F18">
+            <v>0</v>
+          </cell>
+          <cell r="G18">
+            <v>0</v>
+          </cell>
+          <cell r="H18">
+            <v>0</v>
+          </cell>
+          <cell r="I18">
+            <v>0</v>
+          </cell>
+          <cell r="J18">
+            <v>0</v>
+          </cell>
+          <cell r="K18">
+            <v>0</v>
+          </cell>
+          <cell r="L18">
+            <v>1</v>
+          </cell>
+          <cell r="M18">
+            <v>0</v>
+          </cell>
+          <cell r="N18">
+            <v>0</v>
+          </cell>
+          <cell r="O18">
+            <v>0</v>
+          </cell>
+          <cell r="P18">
+            <v>0</v>
+          </cell>
+          <cell r="Q18">
+            <v>0</v>
+          </cell>
+          <cell r="R18">
+            <v>1</v>
+          </cell>
+          <cell r="S18">
+            <v>1</v>
+          </cell>
+          <cell r="T18">
+            <v>0</v>
+          </cell>
+          <cell r="U18">
+            <v>0</v>
+          </cell>
+          <cell r="V18">
+            <v>1</v>
+          </cell>
+          <cell r="W18">
+            <v>2</v>
+          </cell>
+          <cell r="X18">
+            <v>1</v>
+          </cell>
+          <cell r="Y18">
+            <v>0</v>
+          </cell>
+          <cell r="Z18">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+          <cell r="B19">
+            <v>0</v>
+          </cell>
+          <cell r="C19">
+            <v>0</v>
+          </cell>
+          <cell r="D19">
+            <v>0</v>
+          </cell>
+          <cell r="E19">
+            <v>0</v>
+          </cell>
+          <cell r="F19">
+            <v>0</v>
+          </cell>
+          <cell r="G19">
+            <v>0</v>
+          </cell>
+          <cell r="H19">
+            <v>0</v>
+          </cell>
+          <cell r="I19">
+            <v>0</v>
+          </cell>
+          <cell r="J19">
+            <v>0</v>
+          </cell>
+          <cell r="K19">
+            <v>0</v>
+          </cell>
+          <cell r="L19">
+            <v>1</v>
+          </cell>
+          <cell r="M19">
+            <v>0</v>
+          </cell>
+          <cell r="N19">
+            <v>0</v>
+          </cell>
+          <cell r="O19">
+            <v>0</v>
+          </cell>
+          <cell r="P19">
+            <v>0</v>
+          </cell>
+          <cell r="Q19">
+            <v>1</v>
+          </cell>
+          <cell r="R19">
+            <v>0</v>
+          </cell>
+          <cell r="S19">
+            <v>0</v>
+          </cell>
+          <cell r="T19">
+            <v>0</v>
+          </cell>
+          <cell r="U19">
+            <v>0</v>
+          </cell>
+          <cell r="V19">
+            <v>0</v>
+          </cell>
+          <cell r="W19">
+            <v>1</v>
+          </cell>
+          <cell r="X19">
+            <v>1</v>
+          </cell>
+          <cell r="Y19">
+            <v>0</v>
+          </cell>
+          <cell r="Z19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+          <cell r="B20">
+            <v>0</v>
+          </cell>
+          <cell r="C20">
+            <v>0</v>
+          </cell>
+          <cell r="D20">
+            <v>0</v>
+          </cell>
+          <cell r="E20">
+            <v>0</v>
+          </cell>
+          <cell r="F20">
+            <v>0</v>
+          </cell>
+          <cell r="G20">
+            <v>0</v>
+          </cell>
+          <cell r="H20">
+            <v>0</v>
+          </cell>
+          <cell r="I20">
+            <v>0</v>
+          </cell>
+          <cell r="J20">
+            <v>0</v>
+          </cell>
+          <cell r="K20">
+            <v>0</v>
+          </cell>
+          <cell r="L20">
+            <v>0</v>
+          </cell>
+          <cell r="M20">
+            <v>0</v>
+          </cell>
+          <cell r="N20">
+            <v>0</v>
+          </cell>
+          <cell r="O20">
+            <v>0</v>
+          </cell>
+          <cell r="P20">
+            <v>0</v>
+          </cell>
+          <cell r="Q20">
+            <v>0</v>
+          </cell>
+          <cell r="R20">
+            <v>1</v>
+          </cell>
+          <cell r="S20">
+            <v>1</v>
+          </cell>
+          <cell r="T20">
+            <v>0</v>
+          </cell>
+          <cell r="U20">
+            <v>0</v>
+          </cell>
+          <cell r="V20">
+            <v>1</v>
+          </cell>
+          <cell r="W20">
+            <v>1</v>
+          </cell>
+          <cell r="X20">
+            <v>1</v>
+          </cell>
+          <cell r="Y20">
+            <v>0</v>
+          </cell>
+          <cell r="Z20">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>20</v>
+          </cell>
+          <cell r="B21">
+            <v>0</v>
+          </cell>
+          <cell r="C21">
+            <v>0</v>
+          </cell>
+          <cell r="D21">
+            <v>0</v>
+          </cell>
+          <cell r="E21">
+            <v>0</v>
+          </cell>
+          <cell r="F21">
+            <v>1</v>
+          </cell>
+          <cell r="G21">
+            <v>1</v>
+          </cell>
+          <cell r="H21">
+            <v>0</v>
+          </cell>
+          <cell r="I21">
+            <v>0</v>
+          </cell>
+          <cell r="J21">
+            <v>0</v>
+          </cell>
+          <cell r="K21">
+            <v>1</v>
+          </cell>
+          <cell r="L21">
+            <v>1</v>
+          </cell>
+          <cell r="M21">
+            <v>0</v>
+          </cell>
+          <cell r="N21">
+            <v>0</v>
+          </cell>
+          <cell r="O21">
+            <v>0</v>
+          </cell>
+          <cell r="P21">
+            <v>0</v>
+          </cell>
+          <cell r="Q21">
+            <v>0</v>
+          </cell>
+          <cell r="R21">
+            <v>0</v>
+          </cell>
+          <cell r="S21">
+            <v>0</v>
+          </cell>
+          <cell r="T21">
+            <v>1</v>
+          </cell>
+          <cell r="U21">
+            <v>0</v>
+          </cell>
+          <cell r="V21">
+            <v>1</v>
+          </cell>
+          <cell r="W21">
+            <v>1</v>
+          </cell>
+          <cell r="X21">
+            <v>1</v>
+          </cell>
+          <cell r="Y21">
+            <v>0</v>
+          </cell>
+          <cell r="Z21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>21</v>
+          </cell>
+          <cell r="B22">
+            <v>0</v>
+          </cell>
+          <cell r="C22">
+            <v>0</v>
+          </cell>
+          <cell r="D22">
+            <v>0</v>
+          </cell>
+          <cell r="E22">
+            <v>0</v>
+          </cell>
+          <cell r="F22">
+            <v>0</v>
+          </cell>
+          <cell r="G22">
+            <v>0</v>
+          </cell>
+          <cell r="H22">
+            <v>0</v>
+          </cell>
+          <cell r="I22">
+            <v>0</v>
+          </cell>
+          <cell r="J22">
+            <v>0</v>
+          </cell>
+          <cell r="K22">
+            <v>0</v>
+          </cell>
+          <cell r="L22">
+            <v>1</v>
+          </cell>
+          <cell r="M22">
+            <v>0</v>
+          </cell>
+          <cell r="N22">
+            <v>0</v>
+          </cell>
+          <cell r="O22">
+            <v>0</v>
+          </cell>
+          <cell r="P22">
+            <v>0</v>
+          </cell>
+          <cell r="Q22">
+            <v>0</v>
+          </cell>
+          <cell r="R22">
+            <v>1</v>
+          </cell>
+          <cell r="S22">
+            <v>0</v>
+          </cell>
+          <cell r="T22">
+            <v>0</v>
+          </cell>
+          <cell r="U22">
+            <v>0</v>
+          </cell>
+          <cell r="V22">
+            <v>1</v>
+          </cell>
+          <cell r="W22">
+            <v>1</v>
+          </cell>
+          <cell r="X22">
+            <v>1</v>
+          </cell>
+          <cell r="Y22">
+            <v>0</v>
+          </cell>
+          <cell r="Z22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>22</v>
+          </cell>
+          <cell r="B23">
+            <v>0</v>
+          </cell>
+          <cell r="C23">
+            <v>0</v>
+          </cell>
+          <cell r="D23">
+            <v>0</v>
+          </cell>
+          <cell r="E23">
+            <v>0</v>
+          </cell>
+          <cell r="F23">
+            <v>0</v>
+          </cell>
+          <cell r="G23">
+            <v>0</v>
+          </cell>
+          <cell r="H23">
+            <v>0</v>
+          </cell>
+          <cell r="I23">
+            <v>0</v>
+          </cell>
+          <cell r="J23">
+            <v>0</v>
+          </cell>
+          <cell r="K23">
+            <v>0</v>
+          </cell>
+          <cell r="L23">
+            <v>1</v>
+          </cell>
+          <cell r="M23">
+            <v>0</v>
+          </cell>
+          <cell r="N23">
+            <v>0</v>
+          </cell>
+          <cell r="O23">
+            <v>0</v>
+          </cell>
+          <cell r="P23">
+            <v>0</v>
+          </cell>
+          <cell r="Q23">
+            <v>1</v>
+          </cell>
+          <cell r="R23">
+            <v>0</v>
+          </cell>
+          <cell r="S23">
+            <v>0</v>
+          </cell>
+          <cell r="T23">
+            <v>0</v>
+          </cell>
+          <cell r="U23">
+            <v>0</v>
+          </cell>
+          <cell r="V23">
+            <v>0</v>
+          </cell>
+          <cell r="W23">
+            <v>1</v>
+          </cell>
+          <cell r="X23">
+            <v>1</v>
+          </cell>
+          <cell r="Y23">
+            <v>0</v>
+          </cell>
+          <cell r="Z23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>23</v>
+          </cell>
+          <cell r="B24">
+            <v>0</v>
+          </cell>
+          <cell r="C24">
+            <v>0</v>
+          </cell>
+          <cell r="D24">
+            <v>0</v>
+          </cell>
+          <cell r="E24">
+            <v>0</v>
+          </cell>
+          <cell r="F24">
+            <v>1</v>
+          </cell>
+          <cell r="G24">
+            <v>0</v>
+          </cell>
+          <cell r="H24">
+            <v>0</v>
+          </cell>
+          <cell r="I24">
+            <v>0</v>
+          </cell>
+          <cell r="J24">
+            <v>0</v>
+          </cell>
+          <cell r="K24">
+            <v>0</v>
+          </cell>
+          <cell r="L24">
+            <v>0</v>
+          </cell>
+          <cell r="M24">
+            <v>0</v>
+          </cell>
+          <cell r="N24">
+            <v>0</v>
+          </cell>
+          <cell r="O24">
+            <v>0</v>
+          </cell>
+          <cell r="P24">
+            <v>0</v>
+          </cell>
+          <cell r="Q24">
+            <v>1</v>
+          </cell>
+          <cell r="R24">
+            <v>1</v>
+          </cell>
+          <cell r="S24">
+            <v>0</v>
+          </cell>
+          <cell r="T24">
+            <v>0</v>
+          </cell>
+          <cell r="U24">
+            <v>0</v>
+          </cell>
+          <cell r="V24">
+            <v>1</v>
+          </cell>
+          <cell r="W24">
+            <v>2</v>
+          </cell>
+          <cell r="X24">
+            <v>1</v>
+          </cell>
+          <cell r="Y24">
+            <v>0</v>
+          </cell>
+          <cell r="Z24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>24</v>
+          </cell>
+          <cell r="B25">
+            <v>0</v>
+          </cell>
+          <cell r="C25">
+            <v>0</v>
+          </cell>
+          <cell r="D25">
+            <v>0</v>
+          </cell>
+          <cell r="E25">
+            <v>0</v>
+          </cell>
+          <cell r="F25">
+            <v>1</v>
+          </cell>
+          <cell r="G25">
+            <v>0</v>
+          </cell>
+          <cell r="H25">
+            <v>0</v>
+          </cell>
+          <cell r="I25">
+            <v>0</v>
+          </cell>
+          <cell r="J25">
+            <v>0</v>
+          </cell>
+          <cell r="K25">
+            <v>0</v>
+          </cell>
+          <cell r="L25">
+            <v>0</v>
+          </cell>
+          <cell r="M25">
+            <v>0</v>
+          </cell>
+          <cell r="N25">
+            <v>0</v>
+          </cell>
+          <cell r="O25">
+            <v>0</v>
+          </cell>
+          <cell r="P25">
+            <v>0</v>
+          </cell>
+          <cell r="Q25">
+            <v>1</v>
+          </cell>
+          <cell r="R25">
+            <v>0</v>
+          </cell>
+          <cell r="S25">
+            <v>1</v>
+          </cell>
+          <cell r="T25">
+            <v>0</v>
+          </cell>
+          <cell r="U25">
+            <v>0</v>
+          </cell>
+          <cell r="V25">
+            <v>1</v>
+          </cell>
+          <cell r="W25">
+            <v>1</v>
+          </cell>
+          <cell r="X25">
+            <v>0</v>
+          </cell>
+          <cell r="Y25">
+            <v>0</v>
+          </cell>
+          <cell r="Z25">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>25</v>
+          </cell>
+          <cell r="B26">
+            <v>0</v>
+          </cell>
+          <cell r="C26">
+            <v>0</v>
+          </cell>
+          <cell r="D26">
+            <v>0</v>
+          </cell>
+          <cell r="E26">
+            <v>0</v>
+          </cell>
+          <cell r="F26">
+            <v>0</v>
+          </cell>
+          <cell r="G26">
+            <v>0</v>
+          </cell>
+          <cell r="H26">
+            <v>0</v>
+          </cell>
+          <cell r="I26">
+            <v>0</v>
+          </cell>
+          <cell r="J26">
+            <v>0</v>
+          </cell>
+          <cell r="K26">
+            <v>0</v>
+          </cell>
+          <cell r="L26">
+            <v>1</v>
+          </cell>
+          <cell r="M26">
+            <v>0</v>
+          </cell>
+          <cell r="N26">
+            <v>0</v>
+          </cell>
+          <cell r="O26">
+            <v>0</v>
+          </cell>
+          <cell r="P26">
+            <v>0</v>
+          </cell>
+          <cell r="Q26">
+            <v>0</v>
+          </cell>
+          <cell r="R26">
+            <v>0</v>
+          </cell>
+          <cell r="S26">
+            <v>1</v>
+          </cell>
+          <cell r="T26">
+            <v>0</v>
+          </cell>
+          <cell r="U26">
+            <v>0</v>
+          </cell>
+          <cell r="V26">
+            <v>1</v>
+          </cell>
+          <cell r="W26">
+            <v>0</v>
+          </cell>
+          <cell r="X26">
+            <v>1</v>
+          </cell>
+          <cell r="Y26">
+            <v>0</v>
+          </cell>
+          <cell r="Z26">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>26</v>
+          </cell>
+          <cell r="B27">
+            <v>0</v>
+          </cell>
+          <cell r="C27">
+            <v>0</v>
+          </cell>
+          <cell r="D27">
+            <v>0</v>
+          </cell>
+          <cell r="E27">
+            <v>0</v>
+          </cell>
+          <cell r="F27">
+            <v>1</v>
+          </cell>
+          <cell r="G27">
+            <v>0</v>
+          </cell>
+          <cell r="H27">
+            <v>0</v>
+          </cell>
+          <cell r="I27">
+            <v>0</v>
+          </cell>
+          <cell r="J27">
+            <v>0</v>
+          </cell>
+          <cell r="K27">
+            <v>0</v>
+          </cell>
+          <cell r="L27">
+            <v>0</v>
+          </cell>
+          <cell r="M27">
+            <v>0</v>
+          </cell>
+          <cell r="N27">
+            <v>0</v>
+          </cell>
+          <cell r="O27">
+            <v>0</v>
+          </cell>
+          <cell r="P27">
+            <v>0</v>
+          </cell>
+          <cell r="Q27">
+            <v>0</v>
+          </cell>
+          <cell r="R27">
+            <v>0</v>
+          </cell>
+          <cell r="S27">
+            <v>1</v>
+          </cell>
+          <cell r="T27">
+            <v>0</v>
+          </cell>
+          <cell r="U27">
+            <v>0</v>
+          </cell>
+          <cell r="V27">
+            <v>1</v>
+          </cell>
+          <cell r="W27">
+            <v>1</v>
+          </cell>
+          <cell r="X27">
+            <v>1</v>
+          </cell>
+          <cell r="Y27">
+            <v>0</v>
+          </cell>
+          <cell r="Z27">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>27</v>
+          </cell>
+          <cell r="B28">
+            <v>0</v>
+          </cell>
+          <cell r="C28">
+            <v>0</v>
+          </cell>
+          <cell r="D28">
+            <v>0</v>
+          </cell>
+          <cell r="E28">
+            <v>0</v>
+          </cell>
+          <cell r="F28">
+            <v>0</v>
+          </cell>
+          <cell r="G28">
+            <v>0</v>
+          </cell>
+          <cell r="H28">
+            <v>0</v>
+          </cell>
+          <cell r="I28">
+            <v>0</v>
+          </cell>
+          <cell r="J28">
+            <v>0</v>
+          </cell>
+          <cell r="K28">
+            <v>0</v>
+          </cell>
+          <cell r="L28">
+            <v>1</v>
+          </cell>
+          <cell r="M28">
+            <v>0</v>
+          </cell>
+          <cell r="N28">
+            <v>0</v>
+          </cell>
+          <cell r="O28">
+            <v>0</v>
+          </cell>
+          <cell r="P28">
+            <v>0</v>
+          </cell>
+          <cell r="Q28">
+            <v>0</v>
+          </cell>
+          <cell r="R28">
+            <v>0</v>
+          </cell>
+          <cell r="S28">
+            <v>1</v>
+          </cell>
+          <cell r="T28">
+            <v>0</v>
+          </cell>
+          <cell r="U28">
+            <v>0</v>
+          </cell>
+          <cell r="V28">
+            <v>0</v>
+          </cell>
+          <cell r="W28">
+            <v>1</v>
+          </cell>
+          <cell r="X28">
+            <v>0</v>
+          </cell>
+          <cell r="Y28">
+            <v>0</v>
+          </cell>
+          <cell r="Z28">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>28</v>
+          </cell>
+          <cell r="B29">
+            <v>0</v>
+          </cell>
+          <cell r="C29">
+            <v>0</v>
+          </cell>
+          <cell r="D29">
+            <v>0</v>
+          </cell>
+          <cell r="E29">
+            <v>0</v>
+          </cell>
+          <cell r="F29">
+            <v>0</v>
+          </cell>
+          <cell r="G29">
+            <v>0</v>
+          </cell>
+          <cell r="H29">
+            <v>0</v>
+          </cell>
+          <cell r="I29">
+            <v>0</v>
+          </cell>
+          <cell r="J29">
+            <v>0</v>
+          </cell>
+          <cell r="K29">
+            <v>0</v>
+          </cell>
+          <cell r="L29">
+            <v>0</v>
+          </cell>
+          <cell r="M29">
+            <v>0</v>
+          </cell>
+          <cell r="N29">
+            <v>0</v>
+          </cell>
+          <cell r="O29">
+            <v>0</v>
+          </cell>
+          <cell r="P29">
+            <v>0</v>
+          </cell>
+          <cell r="Q29">
+            <v>0</v>
+          </cell>
+          <cell r="R29">
+            <v>1</v>
+          </cell>
+          <cell r="S29">
+            <v>1</v>
+          </cell>
+          <cell r="T29">
+            <v>0</v>
+          </cell>
+          <cell r="U29">
+            <v>0</v>
+          </cell>
+          <cell r="V29">
+            <v>0</v>
+          </cell>
+          <cell r="W29">
+            <v>1</v>
+          </cell>
+          <cell r="X29">
+            <v>0</v>
+          </cell>
+          <cell r="Y29">
+            <v>0</v>
+          </cell>
+          <cell r="Z29">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="resultados_integracion_partido_"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Distrito</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>AH</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>AMA</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>DEM</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>EVO</v>
+          </cell>
+          <cell r="F1" t="str">
+            <v>FA</v>
+          </cell>
+          <cell r="G1" t="str">
+            <v>FREVS</v>
+          </cell>
+          <cell r="H1" t="str">
+            <v>IGU</v>
+          </cell>
+          <cell r="I1" t="str">
+            <v>IND</v>
+          </cell>
+          <cell r="J1" t="str">
+            <v>PAVP</v>
+          </cell>
+          <cell r="K1" t="str">
+            <v>PCCH</v>
+          </cell>
+          <cell r="L1" t="str">
+            <v>PDC</v>
+          </cell>
+          <cell r="M1" t="str">
+            <v>PDG</v>
+          </cell>
+          <cell r="N1" t="str">
+            <v>PH</v>
+          </cell>
+          <cell r="O1" t="str">
+            <v>PL</v>
+          </cell>
+          <cell r="P1" t="str">
+            <v>POP</v>
+          </cell>
+          <cell r="Q1" t="str">
+            <v>PPD</v>
+          </cell>
+          <cell r="R1" t="str">
+            <v>PR</v>
+          </cell>
+          <cell r="S1" t="str">
+            <v>PS</v>
+          </cell>
+          <cell r="T1" t="str">
+            <v>PSC</v>
+          </cell>
+          <cell r="U1" t="str">
+            <v>PTR</v>
+          </cell>
+          <cell r="V1" t="str">
+            <v>REP</v>
+          </cell>
+          <cell r="W1" t="str">
+            <v>RN</v>
+          </cell>
+          <cell r="X1" t="str">
+            <v>UDI</v>
+          </cell>
+          <cell r="Y1" t="str">
+            <v>Votos Blancos</v>
+          </cell>
+          <cell r="Z1" t="str">
+            <v>Votos Nulos</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+          <cell r="B2">
+            <v>0</v>
+          </cell>
+          <cell r="C2">
+            <v>0</v>
+          </cell>
+          <cell r="D2">
+            <v>0</v>
+          </cell>
+          <cell r="E2">
+            <v>0</v>
+          </cell>
+          <cell r="F2">
+            <v>0</v>
+          </cell>
+          <cell r="G2">
+            <v>0</v>
+          </cell>
+          <cell r="H2">
+            <v>0</v>
+          </cell>
+          <cell r="I2">
+            <v>0</v>
+          </cell>
+          <cell r="J2">
+            <v>0</v>
+          </cell>
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="L2">
+            <v>0</v>
+          </cell>
+          <cell r="M2">
+            <v>0</v>
+          </cell>
+          <cell r="N2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+          <cell r="P2">
+            <v>0</v>
+          </cell>
+          <cell r="Q2">
+            <v>0</v>
+          </cell>
+          <cell r="R2">
+            <v>0</v>
+          </cell>
+          <cell r="S2">
+            <v>1</v>
+          </cell>
+          <cell r="T2">
+            <v>0</v>
+          </cell>
+          <cell r="U2">
+            <v>0</v>
+          </cell>
+          <cell r="V2">
+            <v>1</v>
+          </cell>
+          <cell r="W2">
+            <v>0</v>
+          </cell>
+          <cell r="X2">
+            <v>0</v>
+          </cell>
+          <cell r="Y2">
+            <v>0</v>
+          </cell>
+          <cell r="Z2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+          <cell r="B3">
+            <v>0</v>
+          </cell>
+          <cell r="C3">
+            <v>0</v>
+          </cell>
+          <cell r="D3">
+            <v>0</v>
+          </cell>
+          <cell r="E3">
+            <v>0</v>
+          </cell>
+          <cell r="F3">
+            <v>0</v>
+          </cell>
+          <cell r="G3">
+            <v>0</v>
+          </cell>
+          <cell r="H3">
+            <v>0</v>
+          </cell>
+          <cell r="I3">
+            <v>0</v>
+          </cell>
+          <cell r="J3">
+            <v>0</v>
+          </cell>
+          <cell r="K3">
+            <v>0</v>
+          </cell>
+          <cell r="L3">
+            <v>1</v>
+          </cell>
+          <cell r="M3">
+            <v>0</v>
+          </cell>
+          <cell r="N3">
+            <v>0</v>
+          </cell>
+          <cell r="O3">
+            <v>0</v>
+          </cell>
+          <cell r="P3">
+            <v>0</v>
+          </cell>
+          <cell r="Q3">
+            <v>0</v>
+          </cell>
+          <cell r="R3">
+            <v>1</v>
+          </cell>
+          <cell r="S3">
+            <v>0</v>
+          </cell>
+          <cell r="T3">
+            <v>0</v>
+          </cell>
+          <cell r="U3">
+            <v>0</v>
+          </cell>
+          <cell r="V3">
+            <v>0</v>
+          </cell>
+          <cell r="W3">
+            <v>1</v>
+          </cell>
+          <cell r="X3">
+            <v>0</v>
+          </cell>
+          <cell r="Y3">
+            <v>0</v>
+          </cell>
+          <cell r="Z3">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+          <cell r="B4">
+            <v>0</v>
+          </cell>
+          <cell r="C4">
+            <v>0</v>
+          </cell>
+          <cell r="D4">
+            <v>0</v>
+          </cell>
+          <cell r="E4">
+            <v>0</v>
+          </cell>
+          <cell r="F4">
+            <v>0</v>
+          </cell>
+          <cell r="G4">
+            <v>1</v>
+          </cell>
+          <cell r="H4">
+            <v>0</v>
+          </cell>
+          <cell r="I4">
+            <v>0</v>
+          </cell>
+          <cell r="J4">
+            <v>0</v>
+          </cell>
+          <cell r="K4">
+            <v>1</v>
+          </cell>
+          <cell r="L4">
+            <v>0</v>
+          </cell>
+          <cell r="M4">
+            <v>0</v>
+          </cell>
+          <cell r="N4">
+            <v>0</v>
+          </cell>
+          <cell r="O4">
+            <v>0</v>
+          </cell>
+          <cell r="P4">
+            <v>0</v>
+          </cell>
+          <cell r="Q4">
+            <v>0</v>
+          </cell>
+          <cell r="R4">
+            <v>1</v>
+          </cell>
+          <cell r="S4">
+            <v>0</v>
+          </cell>
+          <cell r="T4">
+            <v>0</v>
+          </cell>
+          <cell r="U4">
+            <v>0</v>
+          </cell>
+          <cell r="V4">
+            <v>1</v>
+          </cell>
+          <cell r="W4">
+            <v>1</v>
+          </cell>
+          <cell r="X4">
+            <v>0</v>
+          </cell>
+          <cell r="Y4">
+            <v>0</v>
+          </cell>
+          <cell r="Z4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+          <cell r="B5">
+            <v>0</v>
+          </cell>
+          <cell r="C5">
+            <v>0</v>
+          </cell>
+          <cell r="D5">
+            <v>0</v>
+          </cell>
+          <cell r="E5">
+            <v>0</v>
+          </cell>
+          <cell r="F5">
+            <v>0</v>
+          </cell>
+          <cell r="G5">
+            <v>1</v>
+          </cell>
+          <cell r="H5">
+            <v>0</v>
+          </cell>
+          <cell r="I5">
+            <v>0</v>
+          </cell>
+          <cell r="J5">
+            <v>0</v>
+          </cell>
+          <cell r="K5">
+            <v>1</v>
+          </cell>
+          <cell r="L5">
+            <v>0</v>
+          </cell>
+          <cell r="M5">
+            <v>0</v>
+          </cell>
+          <cell r="N5">
+            <v>0</v>
+          </cell>
+          <cell r="O5">
+            <v>0</v>
+          </cell>
+          <cell r="P5">
+            <v>0</v>
+          </cell>
+          <cell r="Q5">
+            <v>0</v>
+          </cell>
+          <cell r="R5">
+            <v>0</v>
+          </cell>
+          <cell r="S5">
+            <v>1</v>
+          </cell>
+          <cell r="T5">
+            <v>0</v>
+          </cell>
+          <cell r="U5">
+            <v>0</v>
+          </cell>
+          <cell r="V5">
+            <v>1</v>
+          </cell>
+          <cell r="W5">
+            <v>1</v>
+          </cell>
+          <cell r="X5">
+            <v>0</v>
+          </cell>
+          <cell r="Y5">
+            <v>0</v>
+          </cell>
+          <cell r="Z5">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+          <cell r="B6">
+            <v>0</v>
+          </cell>
+          <cell r="C6">
+            <v>0</v>
+          </cell>
+          <cell r="D6">
+            <v>0</v>
+          </cell>
+          <cell r="E6">
+            <v>0</v>
+          </cell>
+          <cell r="F6">
+            <v>1</v>
+          </cell>
+          <cell r="G6">
+            <v>0</v>
+          </cell>
+          <cell r="H6">
+            <v>0</v>
+          </cell>
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+          <cell r="J6">
+            <v>0</v>
+          </cell>
+          <cell r="K6">
+            <v>1</v>
+          </cell>
+          <cell r="L6">
+            <v>1</v>
+          </cell>
+          <cell r="M6">
+            <v>0</v>
+          </cell>
+          <cell r="N6">
+            <v>0</v>
+          </cell>
+          <cell r="O6">
+            <v>0</v>
+          </cell>
+          <cell r="P6">
+            <v>0</v>
+          </cell>
+          <cell r="Q6">
+            <v>0</v>
+          </cell>
+          <cell r="R6">
+            <v>0</v>
+          </cell>
+          <cell r="S6">
+            <v>1</v>
+          </cell>
+          <cell r="T6">
+            <v>0</v>
+          </cell>
+          <cell r="U6">
+            <v>0</v>
+          </cell>
+          <cell r="V6">
+            <v>1</v>
+          </cell>
+          <cell r="W6">
+            <v>1</v>
+          </cell>
+          <cell r="X6">
+            <v>1</v>
+          </cell>
+          <cell r="Y6">
+            <v>0</v>
+          </cell>
+          <cell r="Z6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+          <cell r="B7">
+            <v>0</v>
+          </cell>
+          <cell r="C7">
+            <v>0</v>
+          </cell>
+          <cell r="D7">
+            <v>0</v>
+          </cell>
+          <cell r="E7">
+            <v>0</v>
+          </cell>
+          <cell r="F7">
+            <v>1</v>
+          </cell>
+          <cell r="G7">
+            <v>0</v>
+          </cell>
+          <cell r="H7">
+            <v>0</v>
+          </cell>
+          <cell r="I7">
+            <v>0</v>
+          </cell>
+          <cell r="J7">
+            <v>0</v>
+          </cell>
+          <cell r="K7">
+            <v>1</v>
+          </cell>
+          <cell r="L7">
+            <v>1</v>
+          </cell>
+          <cell r="M7">
+            <v>0</v>
+          </cell>
+          <cell r="N7">
+            <v>0</v>
+          </cell>
+          <cell r="O7">
+            <v>0</v>
+          </cell>
+          <cell r="P7">
+            <v>0</v>
+          </cell>
+          <cell r="Q7">
+            <v>0</v>
+          </cell>
+          <cell r="R7">
+            <v>0</v>
+          </cell>
+          <cell r="S7">
+            <v>1</v>
+          </cell>
+          <cell r="T7">
+            <v>0</v>
+          </cell>
+          <cell r="U7">
+            <v>0</v>
+          </cell>
+          <cell r="V7">
+            <v>2</v>
+          </cell>
+          <cell r="W7">
+            <v>2</v>
+          </cell>
+          <cell r="X7">
+            <v>0</v>
+          </cell>
+          <cell r="Y7">
+            <v>0</v>
+          </cell>
+          <cell r="Z7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+          <cell r="B8">
+            <v>0</v>
+          </cell>
+          <cell r="C8">
+            <v>0</v>
+          </cell>
+          <cell r="D8">
+            <v>0</v>
+          </cell>
+          <cell r="E8">
+            <v>0</v>
+          </cell>
+          <cell r="F8">
+            <v>2</v>
+          </cell>
+          <cell r="G8">
+            <v>0</v>
+          </cell>
+          <cell r="H8">
+            <v>0</v>
+          </cell>
+          <cell r="I8">
+            <v>0</v>
+          </cell>
+          <cell r="J8">
+            <v>0</v>
+          </cell>
+          <cell r="K8">
+            <v>1</v>
+          </cell>
+          <cell r="L8">
+            <v>1</v>
+          </cell>
+          <cell r="M8">
+            <v>0</v>
+          </cell>
+          <cell r="N8">
+            <v>0</v>
+          </cell>
+          <cell r="O8">
+            <v>0</v>
+          </cell>
+          <cell r="P8">
+            <v>0</v>
+          </cell>
+          <cell r="Q8">
+            <v>0</v>
+          </cell>
+          <cell r="R8">
+            <v>0</v>
+          </cell>
+          <cell r="S8">
+            <v>0</v>
+          </cell>
+          <cell r="T8">
+            <v>0</v>
+          </cell>
+          <cell r="U8">
+            <v>0</v>
+          </cell>
+          <cell r="V8">
+            <v>2</v>
+          </cell>
+          <cell r="W8">
+            <v>1</v>
+          </cell>
+          <cell r="X8">
+            <v>1</v>
+          </cell>
+          <cell r="Y8">
+            <v>0</v>
+          </cell>
+          <cell r="Z8">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+          <cell r="B9">
+            <v>0</v>
+          </cell>
+          <cell r="C9">
+            <v>0</v>
+          </cell>
+          <cell r="D9">
+            <v>0</v>
+          </cell>
+          <cell r="E9">
+            <v>0</v>
+          </cell>
+          <cell r="F9">
+            <v>3</v>
+          </cell>
+          <cell r="G9">
+            <v>0</v>
+          </cell>
+          <cell r="H9">
+            <v>0</v>
+          </cell>
+          <cell r="I9">
+            <v>0</v>
+          </cell>
+          <cell r="J9">
+            <v>0</v>
+          </cell>
+          <cell r="K9">
+            <v>1</v>
+          </cell>
+          <cell r="L9">
+            <v>1</v>
+          </cell>
+          <cell r="M9">
+            <v>0</v>
+          </cell>
+          <cell r="N9">
+            <v>0</v>
+          </cell>
+          <cell r="O9">
+            <v>0</v>
+          </cell>
+          <cell r="P9">
+            <v>0</v>
+          </cell>
+          <cell r="Q9">
+            <v>0</v>
+          </cell>
+          <cell r="R9">
+            <v>0</v>
+          </cell>
+          <cell r="S9">
+            <v>0</v>
+          </cell>
+          <cell r="T9">
+            <v>0</v>
+          </cell>
+          <cell r="U9">
+            <v>0</v>
+          </cell>
+          <cell r="V9">
+            <v>2</v>
+          </cell>
+          <cell r="W9">
+            <v>1</v>
+          </cell>
+          <cell r="X9">
+            <v>0</v>
+          </cell>
+          <cell r="Y9">
+            <v>0</v>
+          </cell>
+          <cell r="Z9">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+          <cell r="B10">
+            <v>0</v>
+          </cell>
+          <cell r="C10">
+            <v>0</v>
+          </cell>
+          <cell r="D10">
+            <v>0</v>
+          </cell>
+          <cell r="E10">
+            <v>0</v>
+          </cell>
+          <cell r="F10">
+            <v>1</v>
+          </cell>
+          <cell r="G10">
+            <v>0</v>
+          </cell>
+          <cell r="H10">
+            <v>0</v>
+          </cell>
+          <cell r="I10">
+            <v>0</v>
+          </cell>
+          <cell r="J10">
+            <v>0</v>
+          </cell>
+          <cell r="K10">
+            <v>2</v>
+          </cell>
+          <cell r="L10">
+            <v>0</v>
+          </cell>
+          <cell r="M10">
+            <v>0</v>
+          </cell>
+          <cell r="N10">
+            <v>0</v>
+          </cell>
+          <cell r="O10">
+            <v>0</v>
+          </cell>
+          <cell r="P10">
+            <v>0</v>
+          </cell>
+          <cell r="Q10">
+            <v>0</v>
+          </cell>
+          <cell r="R10">
+            <v>0</v>
+          </cell>
+          <cell r="S10">
+            <v>1</v>
+          </cell>
+          <cell r="T10">
+            <v>0</v>
+          </cell>
+          <cell r="U10">
+            <v>0</v>
+          </cell>
+          <cell r="V10">
+            <v>1</v>
+          </cell>
+          <cell r="W10">
+            <v>1</v>
+          </cell>
+          <cell r="X10">
+            <v>1</v>
+          </cell>
+          <cell r="Y10">
+            <v>0</v>
+          </cell>
+          <cell r="Z10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+          <cell r="B11">
+            <v>0</v>
+          </cell>
+          <cell r="C11">
+            <v>0</v>
+          </cell>
+          <cell r="D11">
+            <v>0</v>
+          </cell>
+          <cell r="E11">
+            <v>0</v>
+          </cell>
+          <cell r="F11">
+            <v>3</v>
+          </cell>
+          <cell r="G11">
+            <v>0</v>
+          </cell>
+          <cell r="H11">
+            <v>0</v>
+          </cell>
+          <cell r="I11">
+            <v>0</v>
+          </cell>
+          <cell r="J11">
+            <v>0</v>
+          </cell>
+          <cell r="K11">
+            <v>2</v>
+          </cell>
+          <cell r="L11">
+            <v>0</v>
+          </cell>
+          <cell r="M11">
+            <v>0</v>
+          </cell>
+          <cell r="N11">
+            <v>0</v>
+          </cell>
+          <cell r="O11">
+            <v>0</v>
+          </cell>
+          <cell r="P11">
+            <v>0</v>
+          </cell>
+          <cell r="Q11">
+            <v>0</v>
+          </cell>
+          <cell r="R11">
+            <v>0</v>
+          </cell>
+          <cell r="S11">
+            <v>0</v>
+          </cell>
+          <cell r="T11">
+            <v>0</v>
+          </cell>
+          <cell r="U11">
+            <v>0</v>
+          </cell>
+          <cell r="V11">
+            <v>1</v>
+          </cell>
+          <cell r="W11">
+            <v>1</v>
+          </cell>
+          <cell r="X11">
+            <v>1</v>
+          </cell>
+          <cell r="Y11">
+            <v>0</v>
+          </cell>
+          <cell r="Z11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+          <cell r="B12">
+            <v>0</v>
+          </cell>
+          <cell r="C12">
+            <v>0</v>
+          </cell>
+          <cell r="D12">
+            <v>0</v>
+          </cell>
+          <cell r="E12">
+            <v>1</v>
+          </cell>
+          <cell r="F12">
+            <v>2</v>
+          </cell>
+          <cell r="G12">
+            <v>0</v>
+          </cell>
+          <cell r="H12">
+            <v>0</v>
+          </cell>
+          <cell r="I12">
+            <v>0</v>
+          </cell>
+          <cell r="J12">
+            <v>0</v>
+          </cell>
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+          <cell r="L12">
+            <v>0</v>
+          </cell>
+          <cell r="M12">
+            <v>0</v>
+          </cell>
+          <cell r="N12">
+            <v>0</v>
+          </cell>
+          <cell r="O12">
+            <v>0</v>
+          </cell>
+          <cell r="P12">
+            <v>0</v>
+          </cell>
+          <cell r="Q12">
+            <v>0</v>
+          </cell>
+          <cell r="R12">
+            <v>0</v>
+          </cell>
+          <cell r="S12">
+            <v>0</v>
+          </cell>
+          <cell r="T12">
+            <v>0</v>
+          </cell>
+          <cell r="U12">
+            <v>0</v>
+          </cell>
+          <cell r="V12">
+            <v>1</v>
+          </cell>
+          <cell r="W12">
+            <v>1</v>
+          </cell>
+          <cell r="X12">
+            <v>1</v>
+          </cell>
+          <cell r="Y12">
+            <v>0</v>
+          </cell>
+          <cell r="Z12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+          <cell r="B13">
+            <v>0</v>
+          </cell>
+          <cell r="C13">
+            <v>0</v>
+          </cell>
+          <cell r="D13">
+            <v>0</v>
+          </cell>
+          <cell r="E13">
+            <v>0</v>
+          </cell>
+          <cell r="F13">
+            <v>1</v>
+          </cell>
+          <cell r="G13">
+            <v>0</v>
+          </cell>
+          <cell r="H13">
+            <v>0</v>
+          </cell>
+          <cell r="I13">
+            <v>0</v>
+          </cell>
+          <cell r="J13">
+            <v>1</v>
+          </cell>
+          <cell r="K13">
+            <v>2</v>
+          </cell>
+          <cell r="L13">
+            <v>0</v>
+          </cell>
+          <cell r="M13">
+            <v>0</v>
+          </cell>
+          <cell r="N13">
+            <v>0</v>
+          </cell>
+          <cell r="O13">
+            <v>0</v>
+          </cell>
+          <cell r="P13">
+            <v>0</v>
+          </cell>
+          <cell r="Q13">
+            <v>0</v>
+          </cell>
+          <cell r="R13">
+            <v>0</v>
+          </cell>
+          <cell r="S13">
+            <v>0</v>
+          </cell>
+          <cell r="T13">
+            <v>0</v>
+          </cell>
+          <cell r="U13">
+            <v>0</v>
+          </cell>
+          <cell r="V13">
+            <v>1</v>
+          </cell>
+          <cell r="W13">
+            <v>2</v>
+          </cell>
+          <cell r="X13">
+            <v>0</v>
+          </cell>
+          <cell r="Y13">
+            <v>0</v>
+          </cell>
+          <cell r="Z13">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+          <cell r="B14">
+            <v>0</v>
+          </cell>
+          <cell r="C14">
+            <v>0</v>
+          </cell>
+          <cell r="D14">
+            <v>0</v>
+          </cell>
+          <cell r="E14">
+            <v>0</v>
+          </cell>
+          <cell r="F14">
+            <v>1</v>
+          </cell>
+          <cell r="G14">
+            <v>0</v>
+          </cell>
+          <cell r="H14">
+            <v>0</v>
+          </cell>
+          <cell r="I14">
+            <v>0</v>
+          </cell>
+          <cell r="J14">
+            <v>0</v>
+          </cell>
+          <cell r="K14">
+            <v>1</v>
+          </cell>
+          <cell r="L14">
+            <v>0</v>
+          </cell>
+          <cell r="M14">
+            <v>0</v>
+          </cell>
+          <cell r="N14">
+            <v>0</v>
+          </cell>
+          <cell r="O14">
+            <v>0</v>
+          </cell>
+          <cell r="P14">
+            <v>0</v>
+          </cell>
+          <cell r="Q14">
+            <v>0</v>
+          </cell>
+          <cell r="R14">
+            <v>0</v>
+          </cell>
+          <cell r="S14">
+            <v>1</v>
+          </cell>
+          <cell r="T14">
+            <v>0</v>
+          </cell>
+          <cell r="U14">
+            <v>0</v>
+          </cell>
+          <cell r="V14">
+            <v>1</v>
+          </cell>
+          <cell r="W14">
+            <v>1</v>
+          </cell>
+          <cell r="X14">
+            <v>0</v>
+          </cell>
+          <cell r="Y14">
+            <v>0</v>
+          </cell>
+          <cell r="Z14">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+          <cell r="B15">
+            <v>0</v>
+          </cell>
+          <cell r="C15">
+            <v>0</v>
+          </cell>
+          <cell r="D15">
+            <v>0</v>
+          </cell>
+          <cell r="E15">
+            <v>0</v>
+          </cell>
+          <cell r="F15">
+            <v>1</v>
+          </cell>
+          <cell r="G15">
+            <v>0</v>
+          </cell>
+          <cell r="H15">
+            <v>0</v>
+          </cell>
+          <cell r="I15">
+            <v>0</v>
+          </cell>
+          <cell r="J15">
+            <v>0</v>
+          </cell>
+          <cell r="K15">
+            <v>1</v>
+          </cell>
+          <cell r="L15">
+            <v>0</v>
+          </cell>
+          <cell r="M15">
+            <v>0</v>
+          </cell>
+          <cell r="N15">
+            <v>0</v>
+          </cell>
+          <cell r="O15">
+            <v>0</v>
+          </cell>
+          <cell r="P15">
+            <v>0</v>
+          </cell>
+          <cell r="Q15">
+            <v>0</v>
+          </cell>
+          <cell r="R15">
+            <v>0</v>
+          </cell>
+          <cell r="S15">
+            <v>1</v>
+          </cell>
+          <cell r="T15">
+            <v>0</v>
+          </cell>
+          <cell r="U15">
+            <v>0</v>
+          </cell>
+          <cell r="V15">
+            <v>1</v>
+          </cell>
+          <cell r="W15">
+            <v>1</v>
+          </cell>
+          <cell r="X15">
+            <v>1</v>
+          </cell>
+          <cell r="Y15">
+            <v>0</v>
+          </cell>
+          <cell r="Z15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+          <cell r="B16">
+            <v>0</v>
+          </cell>
+          <cell r="C16">
+            <v>0</v>
+          </cell>
+          <cell r="D16">
+            <v>0</v>
+          </cell>
+          <cell r="E16">
+            <v>0</v>
+          </cell>
+          <cell r="F16">
+            <v>0</v>
+          </cell>
+          <cell r="G16">
+            <v>0</v>
+          </cell>
+          <cell r="H16">
+            <v>0</v>
+          </cell>
+          <cell r="I16">
+            <v>0</v>
+          </cell>
+          <cell r="J16">
+            <v>0</v>
+          </cell>
+          <cell r="K16">
+            <v>0</v>
+          </cell>
+          <cell r="L16">
+            <v>0</v>
+          </cell>
+          <cell r="M16">
+            <v>0</v>
+          </cell>
+          <cell r="N16">
+            <v>0</v>
+          </cell>
+          <cell r="O16">
+            <v>0</v>
+          </cell>
+          <cell r="P16">
+            <v>0</v>
+          </cell>
+          <cell r="Q16">
+            <v>1</v>
+          </cell>
+          <cell r="R16">
+            <v>1</v>
+          </cell>
+          <cell r="S16">
+            <v>1</v>
+          </cell>
+          <cell r="T16">
+            <v>0</v>
+          </cell>
+          <cell r="U16">
+            <v>0</v>
+          </cell>
+          <cell r="V16">
+            <v>1</v>
+          </cell>
+          <cell r="W16">
+            <v>1</v>
+          </cell>
+          <cell r="X16">
+            <v>0</v>
+          </cell>
+          <cell r="Y16">
+            <v>0</v>
+          </cell>
+          <cell r="Z16">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+          <cell r="B17">
+            <v>0</v>
+          </cell>
+          <cell r="C17">
+            <v>0</v>
+          </cell>
+          <cell r="D17">
+            <v>0</v>
+          </cell>
+          <cell r="E17">
+            <v>0</v>
+          </cell>
+          <cell r="F17">
+            <v>0</v>
+          </cell>
+          <cell r="G17">
+            <v>0</v>
+          </cell>
+          <cell r="H17">
+            <v>0</v>
+          </cell>
+          <cell r="I17">
+            <v>0</v>
+          </cell>
+          <cell r="J17">
+            <v>0</v>
+          </cell>
+          <cell r="K17">
+            <v>0</v>
+          </cell>
+          <cell r="L17">
+            <v>0</v>
+          </cell>
+          <cell r="M17">
+            <v>0</v>
+          </cell>
+          <cell r="N17">
+            <v>0</v>
+          </cell>
+          <cell r="O17">
+            <v>0</v>
+          </cell>
+          <cell r="P17">
+            <v>0</v>
+          </cell>
+          <cell r="Q17">
+            <v>0</v>
+          </cell>
+          <cell r="R17">
+            <v>1</v>
+          </cell>
+          <cell r="S17">
+            <v>1</v>
+          </cell>
+          <cell r="T17">
+            <v>0</v>
+          </cell>
+          <cell r="U17">
+            <v>0</v>
+          </cell>
+          <cell r="V17">
+            <v>0</v>
+          </cell>
+          <cell r="W17">
+            <v>1</v>
+          </cell>
+          <cell r="X17">
+            <v>1</v>
+          </cell>
+          <cell r="Y17">
+            <v>0</v>
+          </cell>
+          <cell r="Z17">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+          <cell r="B18">
+            <v>0</v>
+          </cell>
+          <cell r="C18">
+            <v>0</v>
+          </cell>
+          <cell r="D18">
+            <v>0</v>
+          </cell>
+          <cell r="E18">
+            <v>0</v>
+          </cell>
+          <cell r="F18">
+            <v>0</v>
+          </cell>
+          <cell r="G18">
+            <v>0</v>
+          </cell>
+          <cell r="H18">
+            <v>0</v>
+          </cell>
+          <cell r="I18">
+            <v>0</v>
+          </cell>
+          <cell r="J18">
+            <v>0</v>
+          </cell>
+          <cell r="K18">
+            <v>0</v>
+          </cell>
+          <cell r="L18">
+            <v>1</v>
+          </cell>
+          <cell r="M18">
+            <v>0</v>
+          </cell>
+          <cell r="N18">
+            <v>0</v>
+          </cell>
+          <cell r="O18">
+            <v>0</v>
+          </cell>
+          <cell r="P18">
+            <v>0</v>
+          </cell>
+          <cell r="Q18">
+            <v>0</v>
+          </cell>
+          <cell r="R18">
+            <v>1</v>
+          </cell>
+          <cell r="S18">
+            <v>1</v>
+          </cell>
+          <cell r="T18">
+            <v>0</v>
+          </cell>
+          <cell r="U18">
+            <v>0</v>
+          </cell>
+          <cell r="V18">
+            <v>1</v>
+          </cell>
+          <cell r="W18">
+            <v>2</v>
+          </cell>
+          <cell r="X18">
+            <v>1</v>
+          </cell>
+          <cell r="Y18">
+            <v>0</v>
+          </cell>
+          <cell r="Z18">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+          <cell r="B19">
+            <v>0</v>
+          </cell>
+          <cell r="C19">
+            <v>0</v>
+          </cell>
+          <cell r="D19">
+            <v>0</v>
+          </cell>
+          <cell r="E19">
+            <v>0</v>
+          </cell>
+          <cell r="F19">
+            <v>0</v>
+          </cell>
+          <cell r="G19">
+            <v>0</v>
+          </cell>
+          <cell r="H19">
+            <v>0</v>
+          </cell>
+          <cell r="I19">
+            <v>0</v>
+          </cell>
+          <cell r="J19">
+            <v>0</v>
+          </cell>
+          <cell r="K19">
+            <v>0</v>
+          </cell>
+          <cell r="L19">
+            <v>1</v>
+          </cell>
+          <cell r="M19">
+            <v>0</v>
+          </cell>
+          <cell r="N19">
+            <v>0</v>
+          </cell>
+          <cell r="O19">
+            <v>0</v>
+          </cell>
+          <cell r="P19">
+            <v>0</v>
+          </cell>
+          <cell r="Q19">
+            <v>1</v>
+          </cell>
+          <cell r="R19">
+            <v>0</v>
+          </cell>
+          <cell r="S19">
+            <v>0</v>
+          </cell>
+          <cell r="T19">
+            <v>0</v>
+          </cell>
+          <cell r="U19">
+            <v>0</v>
+          </cell>
+          <cell r="V19">
+            <v>0</v>
+          </cell>
+          <cell r="W19">
+            <v>1</v>
+          </cell>
+          <cell r="X19">
+            <v>1</v>
+          </cell>
+          <cell r="Y19">
+            <v>0</v>
+          </cell>
+          <cell r="Z19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+          <cell r="B20">
+            <v>0</v>
+          </cell>
+          <cell r="C20">
+            <v>0</v>
+          </cell>
+          <cell r="D20">
+            <v>0</v>
+          </cell>
+          <cell r="E20">
+            <v>0</v>
+          </cell>
+          <cell r="F20">
+            <v>0</v>
+          </cell>
+          <cell r="G20">
+            <v>0</v>
+          </cell>
+          <cell r="H20">
+            <v>0</v>
+          </cell>
+          <cell r="I20">
+            <v>0</v>
+          </cell>
+          <cell r="J20">
+            <v>0</v>
+          </cell>
+          <cell r="K20">
+            <v>0</v>
+          </cell>
+          <cell r="L20">
+            <v>0</v>
+          </cell>
+          <cell r="M20">
+            <v>0</v>
+          </cell>
+          <cell r="N20">
+            <v>0</v>
+          </cell>
+          <cell r="O20">
+            <v>0</v>
+          </cell>
+          <cell r="P20">
+            <v>0</v>
+          </cell>
+          <cell r="Q20">
+            <v>0</v>
+          </cell>
+          <cell r="R20">
+            <v>1</v>
+          </cell>
+          <cell r="S20">
+            <v>1</v>
+          </cell>
+          <cell r="T20">
+            <v>0</v>
+          </cell>
+          <cell r="U20">
+            <v>0</v>
+          </cell>
+          <cell r="V20">
+            <v>1</v>
+          </cell>
+          <cell r="W20">
+            <v>1</v>
+          </cell>
+          <cell r="X20">
+            <v>1</v>
+          </cell>
+          <cell r="Y20">
+            <v>0</v>
+          </cell>
+          <cell r="Z20">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>20</v>
+          </cell>
+          <cell r="B21">
+            <v>0</v>
+          </cell>
+          <cell r="C21">
+            <v>0</v>
+          </cell>
+          <cell r="D21">
+            <v>0</v>
+          </cell>
+          <cell r="E21">
+            <v>0</v>
+          </cell>
+          <cell r="F21">
+            <v>1</v>
+          </cell>
+          <cell r="G21">
+            <v>1</v>
+          </cell>
+          <cell r="H21">
+            <v>0</v>
+          </cell>
+          <cell r="I21">
+            <v>0</v>
+          </cell>
+          <cell r="J21">
+            <v>0</v>
+          </cell>
+          <cell r="K21">
+            <v>1</v>
+          </cell>
+          <cell r="L21">
+            <v>1</v>
+          </cell>
+          <cell r="M21">
+            <v>0</v>
+          </cell>
+          <cell r="N21">
+            <v>0</v>
+          </cell>
+          <cell r="O21">
+            <v>0</v>
+          </cell>
+          <cell r="P21">
+            <v>0</v>
+          </cell>
+          <cell r="Q21">
+            <v>0</v>
+          </cell>
+          <cell r="R21">
+            <v>0</v>
+          </cell>
+          <cell r="S21">
+            <v>0</v>
+          </cell>
+          <cell r="T21">
+            <v>1</v>
+          </cell>
+          <cell r="U21">
+            <v>0</v>
+          </cell>
+          <cell r="V21">
+            <v>1</v>
+          </cell>
+          <cell r="W21">
+            <v>1</v>
+          </cell>
+          <cell r="X21">
+            <v>1</v>
+          </cell>
+          <cell r="Y21">
+            <v>0</v>
+          </cell>
+          <cell r="Z21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>21</v>
+          </cell>
+          <cell r="B22">
+            <v>0</v>
+          </cell>
+          <cell r="C22">
+            <v>0</v>
+          </cell>
+          <cell r="D22">
+            <v>0</v>
+          </cell>
+          <cell r="E22">
+            <v>0</v>
+          </cell>
+          <cell r="F22">
+            <v>0</v>
+          </cell>
+          <cell r="G22">
+            <v>0</v>
+          </cell>
+          <cell r="H22">
+            <v>0</v>
+          </cell>
+          <cell r="I22">
+            <v>0</v>
+          </cell>
+          <cell r="J22">
+            <v>0</v>
+          </cell>
+          <cell r="K22">
+            <v>0</v>
+          </cell>
+          <cell r="L22">
+            <v>1</v>
+          </cell>
+          <cell r="M22">
+            <v>0</v>
+          </cell>
+          <cell r="N22">
+            <v>0</v>
+          </cell>
+          <cell r="O22">
+            <v>0</v>
+          </cell>
+          <cell r="P22">
+            <v>0</v>
+          </cell>
+          <cell r="Q22">
+            <v>0</v>
+          </cell>
+          <cell r="R22">
+            <v>1</v>
+          </cell>
+          <cell r="S22">
+            <v>0</v>
+          </cell>
+          <cell r="T22">
+            <v>0</v>
+          </cell>
+          <cell r="U22">
+            <v>0</v>
+          </cell>
+          <cell r="V22">
+            <v>1</v>
+          </cell>
+          <cell r="W22">
+            <v>1</v>
+          </cell>
+          <cell r="X22">
+            <v>1</v>
+          </cell>
+          <cell r="Y22">
+            <v>0</v>
+          </cell>
+          <cell r="Z22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>22</v>
+          </cell>
+          <cell r="B23">
+            <v>0</v>
+          </cell>
+          <cell r="C23">
+            <v>0</v>
+          </cell>
+          <cell r="D23">
+            <v>0</v>
+          </cell>
+          <cell r="E23">
+            <v>0</v>
+          </cell>
+          <cell r="F23">
+            <v>0</v>
+          </cell>
+          <cell r="G23">
+            <v>0</v>
+          </cell>
+          <cell r="H23">
+            <v>0</v>
+          </cell>
+          <cell r="I23">
+            <v>0</v>
+          </cell>
+          <cell r="J23">
+            <v>0</v>
+          </cell>
+          <cell r="K23">
+            <v>0</v>
+          </cell>
+          <cell r="L23">
+            <v>1</v>
+          </cell>
+          <cell r="M23">
+            <v>0</v>
+          </cell>
+          <cell r="N23">
+            <v>0</v>
+          </cell>
+          <cell r="O23">
+            <v>0</v>
+          </cell>
+          <cell r="P23">
+            <v>0</v>
+          </cell>
+          <cell r="Q23">
+            <v>1</v>
+          </cell>
+          <cell r="R23">
+            <v>0</v>
+          </cell>
+          <cell r="S23">
+            <v>0</v>
+          </cell>
+          <cell r="T23">
+            <v>0</v>
+          </cell>
+          <cell r="U23">
+            <v>0</v>
+          </cell>
+          <cell r="V23">
+            <v>1</v>
+          </cell>
+          <cell r="W23">
+            <v>1</v>
+          </cell>
+          <cell r="X23">
+            <v>0</v>
+          </cell>
+          <cell r="Y23">
+            <v>0</v>
+          </cell>
+          <cell r="Z23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>23</v>
+          </cell>
+          <cell r="B24">
+            <v>0</v>
+          </cell>
+          <cell r="C24">
+            <v>0</v>
+          </cell>
+          <cell r="D24">
+            <v>0</v>
+          </cell>
+          <cell r="E24">
+            <v>0</v>
+          </cell>
+          <cell r="F24">
+            <v>1</v>
+          </cell>
+          <cell r="G24">
+            <v>0</v>
+          </cell>
+          <cell r="H24">
+            <v>0</v>
+          </cell>
+          <cell r="I24">
+            <v>0</v>
+          </cell>
+          <cell r="J24">
+            <v>0</v>
+          </cell>
+          <cell r="K24">
+            <v>0</v>
+          </cell>
+          <cell r="L24">
+            <v>0</v>
+          </cell>
+          <cell r="M24">
+            <v>0</v>
+          </cell>
+          <cell r="N24">
+            <v>0</v>
+          </cell>
+          <cell r="O24">
+            <v>0</v>
+          </cell>
+          <cell r="P24">
+            <v>0</v>
+          </cell>
+          <cell r="Q24">
+            <v>1</v>
+          </cell>
+          <cell r="R24">
+            <v>1</v>
+          </cell>
+          <cell r="S24">
+            <v>0</v>
+          </cell>
+          <cell r="T24">
+            <v>0</v>
+          </cell>
+          <cell r="U24">
+            <v>0</v>
+          </cell>
+          <cell r="V24">
+            <v>1</v>
+          </cell>
+          <cell r="W24">
+            <v>2</v>
+          </cell>
+          <cell r="X24">
+            <v>1</v>
+          </cell>
+          <cell r="Y24">
+            <v>0</v>
+          </cell>
+          <cell r="Z24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>24</v>
+          </cell>
+          <cell r="B25">
+            <v>0</v>
+          </cell>
+          <cell r="C25">
+            <v>0</v>
+          </cell>
+          <cell r="D25">
+            <v>0</v>
+          </cell>
+          <cell r="E25">
+            <v>0</v>
+          </cell>
+          <cell r="F25">
+            <v>1</v>
+          </cell>
+          <cell r="G25">
+            <v>0</v>
+          </cell>
+          <cell r="H25">
+            <v>0</v>
+          </cell>
+          <cell r="I25">
+            <v>0</v>
+          </cell>
+          <cell r="J25">
+            <v>0</v>
+          </cell>
+          <cell r="K25">
+            <v>0</v>
+          </cell>
+          <cell r="L25">
+            <v>0</v>
+          </cell>
+          <cell r="M25">
+            <v>0</v>
+          </cell>
+          <cell r="N25">
+            <v>0</v>
+          </cell>
+          <cell r="O25">
+            <v>0</v>
+          </cell>
+          <cell r="P25">
+            <v>0</v>
+          </cell>
+          <cell r="Q25">
+            <v>1</v>
+          </cell>
+          <cell r="R25">
+            <v>0</v>
+          </cell>
+          <cell r="S25">
+            <v>1</v>
+          </cell>
+          <cell r="T25">
+            <v>0</v>
+          </cell>
+          <cell r="U25">
+            <v>0</v>
+          </cell>
+          <cell r="V25">
+            <v>1</v>
+          </cell>
+          <cell r="W25">
+            <v>1</v>
+          </cell>
+          <cell r="X25">
+            <v>0</v>
+          </cell>
+          <cell r="Y25">
+            <v>0</v>
+          </cell>
+          <cell r="Z25">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>25</v>
+          </cell>
+          <cell r="B26">
+            <v>0</v>
+          </cell>
+          <cell r="C26">
+            <v>0</v>
+          </cell>
+          <cell r="D26">
+            <v>0</v>
+          </cell>
+          <cell r="E26">
+            <v>0</v>
+          </cell>
+          <cell r="F26">
+            <v>0</v>
+          </cell>
+          <cell r="G26">
+            <v>0</v>
+          </cell>
+          <cell r="H26">
+            <v>0</v>
+          </cell>
+          <cell r="I26">
+            <v>0</v>
+          </cell>
+          <cell r="J26">
+            <v>0</v>
+          </cell>
+          <cell r="K26">
+            <v>0</v>
+          </cell>
+          <cell r="L26">
+            <v>1</v>
+          </cell>
+          <cell r="M26">
+            <v>0</v>
+          </cell>
+          <cell r="N26">
+            <v>0</v>
+          </cell>
+          <cell r="O26">
+            <v>0</v>
+          </cell>
+          <cell r="P26">
+            <v>0</v>
+          </cell>
+          <cell r="Q26">
+            <v>0</v>
+          </cell>
+          <cell r="R26">
+            <v>0</v>
+          </cell>
+          <cell r="S26">
+            <v>1</v>
+          </cell>
+          <cell r="T26">
+            <v>0</v>
+          </cell>
+          <cell r="U26">
+            <v>0</v>
+          </cell>
+          <cell r="V26">
+            <v>1</v>
+          </cell>
+          <cell r="W26">
+            <v>0</v>
+          </cell>
+          <cell r="X26">
+            <v>1</v>
+          </cell>
+          <cell r="Y26">
+            <v>0</v>
+          </cell>
+          <cell r="Z26">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>26</v>
+          </cell>
+          <cell r="B27">
+            <v>0</v>
+          </cell>
+          <cell r="C27">
+            <v>0</v>
+          </cell>
+          <cell r="D27">
+            <v>0</v>
+          </cell>
+          <cell r="E27">
+            <v>0</v>
+          </cell>
+          <cell r="F27">
+            <v>1</v>
+          </cell>
+          <cell r="G27">
+            <v>0</v>
+          </cell>
+          <cell r="H27">
+            <v>0</v>
+          </cell>
+          <cell r="I27">
+            <v>0</v>
+          </cell>
+          <cell r="J27">
+            <v>0</v>
+          </cell>
+          <cell r="K27">
+            <v>0</v>
+          </cell>
+          <cell r="L27">
+            <v>0</v>
+          </cell>
+          <cell r="M27">
+            <v>0</v>
+          </cell>
+          <cell r="N27">
+            <v>0</v>
+          </cell>
+          <cell r="O27">
+            <v>0</v>
+          </cell>
+          <cell r="P27">
+            <v>0</v>
+          </cell>
+          <cell r="Q27">
+            <v>0</v>
+          </cell>
+          <cell r="R27">
+            <v>0</v>
+          </cell>
+          <cell r="S27">
+            <v>1</v>
+          </cell>
+          <cell r="T27">
+            <v>0</v>
+          </cell>
+          <cell r="U27">
+            <v>0</v>
+          </cell>
+          <cell r="V27">
+            <v>1</v>
+          </cell>
+          <cell r="W27">
+            <v>1</v>
+          </cell>
+          <cell r="X27">
+            <v>1</v>
+          </cell>
+          <cell r="Y27">
+            <v>0</v>
+          </cell>
+          <cell r="Z27">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>27</v>
+          </cell>
+          <cell r="B28">
+            <v>0</v>
+          </cell>
+          <cell r="C28">
+            <v>0</v>
+          </cell>
+          <cell r="D28">
+            <v>0</v>
+          </cell>
+          <cell r="E28">
+            <v>0</v>
+          </cell>
+          <cell r="F28">
+            <v>0</v>
+          </cell>
+          <cell r="G28">
+            <v>0</v>
+          </cell>
+          <cell r="H28">
+            <v>0</v>
+          </cell>
+          <cell r="I28">
+            <v>0</v>
+          </cell>
+          <cell r="J28">
+            <v>0</v>
+          </cell>
+          <cell r="K28">
+            <v>0</v>
+          </cell>
+          <cell r="L28">
+            <v>1</v>
+          </cell>
+          <cell r="M28">
+            <v>0</v>
+          </cell>
+          <cell r="N28">
+            <v>0</v>
+          </cell>
+          <cell r="O28">
+            <v>0</v>
+          </cell>
+          <cell r="P28">
+            <v>0</v>
+          </cell>
+          <cell r="Q28">
+            <v>0</v>
+          </cell>
+          <cell r="R28">
+            <v>0</v>
+          </cell>
+          <cell r="S28">
+            <v>1</v>
+          </cell>
+          <cell r="T28">
+            <v>0</v>
+          </cell>
+          <cell r="U28">
+            <v>0</v>
+          </cell>
+          <cell r="V28">
+            <v>0</v>
+          </cell>
+          <cell r="W28">
+            <v>1</v>
+          </cell>
+          <cell r="X28">
+            <v>0</v>
+          </cell>
+          <cell r="Y28">
+            <v>0</v>
+          </cell>
+          <cell r="Z28">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>28</v>
+          </cell>
+          <cell r="B29">
+            <v>0</v>
+          </cell>
+          <cell r="C29">
+            <v>0</v>
+          </cell>
+          <cell r="D29">
+            <v>0</v>
+          </cell>
+          <cell r="E29">
+            <v>0</v>
+          </cell>
+          <cell r="F29">
+            <v>0</v>
+          </cell>
+          <cell r="G29">
+            <v>0</v>
+          </cell>
+          <cell r="H29">
+            <v>0</v>
+          </cell>
+          <cell r="I29">
+            <v>0</v>
+          </cell>
+          <cell r="J29">
+            <v>0</v>
+          </cell>
+          <cell r="K29">
+            <v>0</v>
+          </cell>
+          <cell r="L29">
+            <v>0</v>
+          </cell>
+          <cell r="M29">
+            <v>0</v>
+          </cell>
+          <cell r="N29">
+            <v>0</v>
+          </cell>
+          <cell r="O29">
+            <v>0</v>
+          </cell>
+          <cell r="P29">
+            <v>0</v>
+          </cell>
+          <cell r="Q29">
+            <v>0</v>
+          </cell>
+          <cell r="R29">
+            <v>1</v>
+          </cell>
+          <cell r="S29">
+            <v>1</v>
+          </cell>
+          <cell r="T29">
+            <v>0</v>
+          </cell>
+          <cell r="U29">
+            <v>0</v>
+          </cell>
+          <cell r="V29">
+            <v>0</v>
+          </cell>
+          <cell r="W29">
+            <v>1</v>
+          </cell>
+          <cell r="X29">
+            <v>0</v>
+          </cell>
+          <cell r="Y29">
+            <v>0</v>
+          </cell>
+          <cell r="Z29">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -26443,43 +31119,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C27">
-    <cfRule type="cellIs" dxfId="141" priority="155" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="141" priority="149" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="149" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="140" priority="150" operator="equal">
+      <formula>"p6"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="139" priority="151" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="150" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="152" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="152" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="153" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="153" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="154" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="154" operator="equal">
       <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="135" priority="155" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:G27">
-    <cfRule type="cellIs" dxfId="134" priority="111" operator="equal">
-      <formula>"p3"</formula>
+    <cfRule type="cellIs" dxfId="134" priority="107" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="110" operator="equal">
-      <formula>"p4"</formula>
+    <cfRule type="cellIs" dxfId="133" priority="108" operator="equal">
+      <formula>"p6"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="132" priority="109" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="108" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="131" priority="110" operator="equal">
+      <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="107" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="130" priority="111" operator="equal">
+      <formula>"p3"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="129" priority="112" operator="equal">
       <formula>"p2"</formula>
@@ -26500,31 +31176,31 @@
     <cfRule type="cellIs" dxfId="125" priority="143" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="148" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="124" priority="144" operator="equal">
+      <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="147" operator="equal">
-      <formula>"p2"</formula>
+    <cfRule type="cellIs" dxfId="123" priority="145" operator="equal">
+      <formula>"p4"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="122" priority="146" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="145" operator="equal">
-      <formula>"p4"</formula>
+    <cfRule type="cellIs" dxfId="121" priority="147" operator="equal">
+      <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="144" operator="equal">
-      <formula>"p5"</formula>
+    <cfRule type="cellIs" dxfId="120" priority="148" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:K27 AD5:AE27">
-    <cfRule type="cellIs" dxfId="119" priority="95" operator="equal">
-      <formula>"p11"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="93" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="93" operator="equal">
       <formula>"p13"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="94" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="94" operator="equal">
       <formula>"p12"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="95" operator="equal">
+      <formula>"p11"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="116" priority="96" operator="equal">
       <formula>"p10"</formula>
@@ -26534,69 +31210,69 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K27 AE5:AE27">
-    <cfRule type="cellIs" dxfId="114" priority="105" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="114" priority="98" operator="equal">
+      <formula>"p8"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="102" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="99" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="100" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="101" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="110" priority="102" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="104" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="103" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="104" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="103" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="101" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="100" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="99" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="98" operator="equal">
-      <formula>"p8"</formula>
+    <cfRule type="cellIs" dxfId="107" priority="105" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:O4">
-    <cfRule type="cellIs" dxfId="106" priority="138" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="135" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="136" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="104" priority="137" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="138" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="141" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="102" priority="139" operator="equal">
+      <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="140" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="140" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="139" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="136" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="135" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="137" operator="equal">
-      <formula>"p5"</formula>
+    <cfRule type="cellIs" dxfId="100" priority="141" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O27">
-    <cfRule type="cellIs" dxfId="99" priority="84" operator="equal">
-      <formula>"p9"</formula>
+    <cfRule type="cellIs" dxfId="99" priority="80" operator="equal">
+      <formula>"p13"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="81" operator="equal">
+      <formula>"p12"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="82" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="81" operator="equal">
-      <formula>"p12"</formula>
+    <cfRule type="cellIs" dxfId="96" priority="83" operator="equal">
+      <formula>"p10"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="80" operator="equal">
-      <formula>"p13"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="83" operator="equal">
-      <formula>"p10"</formula>
+    <cfRule type="cellIs" dxfId="95" priority="84" operator="equal">
+      <formula>"p9"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O5:O27">
@@ -26629,106 +31305,106 @@
     <cfRule type="cellIs" dxfId="86" priority="128" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="134" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="85" priority="129" operator="equal">
+      <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="133" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="130" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="83" priority="131" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="132" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="133" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="132" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="131" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="130" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="129" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="80" priority="134" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:S27">
-    <cfRule type="cellIs" dxfId="79" priority="71" operator="equal">
-      <formula>"p9"</formula>
+    <cfRule type="cellIs" dxfId="79" priority="67" operator="equal">
+      <formula>"p13"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="78" priority="68" operator="equal">
       <formula>"p12"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="70" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="69" operator="equal">
+      <formula>"p11"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="70" operator="equal">
       <formula>"p10"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="69" operator="equal">
-      <formula>"p11"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="67" operator="equal">
-      <formula>"p13"</formula>
+    <cfRule type="cellIs" dxfId="75" priority="71" operator="equal">
+      <formula>"p9"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:S27">
-    <cfRule type="cellIs" dxfId="74" priority="76" operator="equal">
-      <formula>"p4"</formula>
+    <cfRule type="cellIs" dxfId="74" priority="72" operator="equal">
+      <formula>"p8"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="75" operator="equal">
-      <formula>"p5"</formula>
+    <cfRule type="cellIs" dxfId="73" priority="73" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="72" priority="74" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="73" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="71" priority="75" operator="equal">
+      <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="72" operator="equal">
-      <formula>"p8"</formula>
+    <cfRule type="cellIs" dxfId="70" priority="76" operator="equal">
+      <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="79" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="69" priority="77" operator="equal">
+      <formula>"p3"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="68" priority="78" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="77" operator="equal">
-      <formula>"p3"</formula>
+    <cfRule type="cellIs" dxfId="67" priority="79" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V4:W4">
-    <cfRule type="cellIs" dxfId="66" priority="122" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="121" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="65" priority="122" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="127" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="64" priority="123" operator="equal">
+      <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="126" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="124" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="125" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="126" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="125" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="124" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="123" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="121" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="60" priority="127" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W27">
     <cfRule type="cellIs" dxfId="59" priority="54" operator="equal">
       <formula>"p13"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="55" operator="equal">
+      <formula>"p12"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="56" operator="equal">
+      <formula>"p11"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="56" priority="57" operator="equal">
       <formula>"p10"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="58" operator="equal">
       <formula>"p9"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="56" operator="equal">
-      <formula>"p11"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="55" operator="equal">
-      <formula>"p12"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W27">
@@ -26750,22 +31426,22 @@
     <cfRule type="cellIs" dxfId="49" priority="64" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="65" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="66" operator="equal">
       <formula>"p1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="65" operator="equal">
-      <formula>"p2"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z4:AA4">
-    <cfRule type="cellIs" dxfId="46" priority="116" operator="equal">
-      <formula>"p5"</formula>
+    <cfRule type="cellIs" dxfId="46" priority="114" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="45" priority="115" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="114" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="44" priority="116" operator="equal">
+      <formula>"p5"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="43" priority="117" operator="equal">
       <formula>"p4"</formula>
@@ -26790,126 +31466,126 @@
     <cfRule type="cellIs" dxfId="37" priority="43" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="44" operator="equal">
+      <formula>"p10"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="45" operator="equal">
       <formula>"p9"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="44" operator="equal">
-      <formula>"p10"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA5:AA27">
-    <cfRule type="cellIs" dxfId="34" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="46" operator="equal">
+      <formula>"p8"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="47" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="48" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="53" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="31" priority="49" operator="equal">
+      <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="50" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="51" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="52" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="51" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="49" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="47" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="46" operator="equal">
-      <formula>"p8"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="50" operator="equal">
-      <formula>"p4"</formula>
+    <cfRule type="cellIs" dxfId="27" priority="53" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD4:AE4">
-    <cfRule type="cellIs" dxfId="26" priority="38" operator="equal">
-      <formula>"p3"</formula>
+    <cfRule type="cellIs" dxfId="26" priority="34" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="37" operator="equal">
-      <formula>"p4"</formula>
+    <cfRule type="cellIs" dxfId="25" priority="35" operator="equal">
+      <formula>"p6"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="24" priority="36" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="35" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="23" priority="37" operator="equal">
+      <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="34" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="22" priority="38" operator="equal">
+      <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="39" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="40" operator="equal">
       <formula>"p1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="39" operator="equal">
-      <formula>"p2"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH4:AI4">
-    <cfRule type="cellIs" dxfId="19" priority="19" operator="equal">
-      <formula>"p2"</formula>
+    <cfRule type="cellIs" dxfId="19" priority="14" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="17" operator="equal">
-      <formula>"p4"</formula>
+    <cfRule type="cellIs" dxfId="18" priority="15" operator="equal">
+      <formula>"p6"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="14" priority="19" operator="equal">
+      <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="20" operator="equal">
       <formula>"p1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
-      <formula>"p7"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH5:AI27">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+      <formula>"p13"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"p12"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
       <formula>"p10"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>"p9"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
-      <formula>"p13"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI5:AI27">
     <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"p8"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
+      <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="10" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="11" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="12" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="10" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
-      <formula>"p5"</formula>
+    <cfRule type="cellIs" dxfId="0" priority="13" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -26920,7 +31596,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE4FFD-F878-482C-A0A8-BDAA2E8CFFC3}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
@@ -27330,41 +32006,93 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="37"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="40"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="37"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -27432,20 +32160,42 @@
       <c r="I22" s="39"/>
       <c r="J22" s="40"/>
     </row>
-    <row r="23" spans="2:10" ht="141" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="43"/>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="40"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="40"/>
+    </row>
+    <row r="25" spans="2:10" ht="141" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:J23"/>
+    <mergeCell ref="B16:J25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -27455,7 +32205,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BB08D38-758B-4C93-953E-47B034B6B7A0}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
@@ -27777,35 +32527,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="37"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="40"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="37"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -27834,7 +32624,7 @@
       <c r="G19" s="39"/>
       <c r="H19" s="40"/>
     </row>
-    <row r="20" spans="2:8" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -27852,7 +32642,7 @@
       <c r="G21" s="39"/>
       <c r="H21" s="40"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="87" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -27861,18 +32651,36 @@
       <c r="G22" s="39"/>
       <c r="H22" s="40"/>
     </row>
-    <row r="23" spans="2:8" ht="74.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="43"/>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="40"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+    </row>
+    <row r="25" spans="2:8" ht="74.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:H23"/>
+    <mergeCell ref="B16:H25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -27882,7 +32690,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07F82A79-2B4A-4137-852C-755DEDCA5B93}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
@@ -28333,44 +33141,102 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="37"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -28444,21 +33310,45 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="43"/>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="40"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="40"/>
+    </row>
+    <row r="25" spans="2:11" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:K23"/>
+    <mergeCell ref="B16:K25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -28468,7 +33358,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C74488B-26AE-49B8-83E1-BFE79ADC2E4A}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
@@ -28918,44 +33808,102 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="J13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="J14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="37"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -28993,7 +33941,7 @@
       <c r="J19" s="39"/>
       <c r="K19" s="40"/>
     </row>
-    <row r="20" spans="2:11" ht="69.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -29017,7 +33965,7 @@
       <c r="J21" s="39"/>
       <c r="K21" s="40"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:11" ht="69.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -29029,21 +33977,45 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" ht="62.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="43"/>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="40"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="40"/>
+    </row>
+    <row r="25" spans="2:11" ht="62.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:K23"/>
+    <mergeCell ref="B16:K25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -29053,7 +34025,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617D1657-68E6-425A-BEC6-156568C1CA34}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
@@ -29418,38 +34390,84 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="37"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="37"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -29511,19 +34529,39 @@
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
     </row>
-    <row r="23" spans="2:9" ht="131" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="43"/>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="40"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="40"/>
+    </row>
+    <row r="25" spans="2:9" ht="131" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:I23"/>
+    <mergeCell ref="B16:I25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -29533,7 +34571,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD025208-EBF5-4B5B-AA05-51C599203D1C}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
@@ -29897,38 +34935,84 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="37"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="37"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -29990,19 +35074,39 @@
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
     </row>
-    <row r="23" spans="2:9" ht="112.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="43"/>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="40"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="40"/>
+    </row>
+    <row r="25" spans="2:9" ht="112.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:I23"/>
+    <mergeCell ref="B16:I25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -30012,7 +35116,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B9D3998-67DE-4085-A6E8-30E813E46135}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
@@ -30420,41 +35524,93 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="37"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="40"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="37"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -30522,20 +35678,42 @@
       <c r="I22" s="39"/>
       <c r="J22" s="40"/>
     </row>
-    <row r="23" spans="2:10" ht="140.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="43"/>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="40"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="40"/>
+    </row>
+    <row r="25" spans="2:10" ht="140.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:J23"/>
+    <mergeCell ref="B16:J25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -30545,7 +35723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89480051-BCA3-405F-B673-471E1D4EE818}">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
@@ -31123,53 +36301,129 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="6.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="L13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(L$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(M$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="N13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(N$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="L14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(L$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(M$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="N14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(N$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="6.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="37"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="40"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="37"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -31261,24 +36515,54 @@
       <c r="M22" s="39"/>
       <c r="N22" s="40"/>
     </row>
-    <row r="23" spans="2:14" ht="131" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="43"/>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="40"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="40"/>
+    </row>
+    <row r="25" spans="2:14" ht="131" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:N23"/>
+    <mergeCell ref="B16:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -31288,7 +36572,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DB6AE84-88BE-4054-A4FA-FD43BA13B48C}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
@@ -31738,44 +37022,102 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="37"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -31849,21 +37191,45 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" ht="105" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="43"/>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="40"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="40"/>
+    </row>
+    <row r="25" spans="2:11" ht="105" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:K23"/>
+    <mergeCell ref="B16:K25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -31873,7 +37239,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A45733F-34D0-4D88-A6B5-E28376F26D12}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
@@ -32326,44 +37692,102 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="K13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="K14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="37"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -32437,21 +37861,45 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" ht="98.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="43"/>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="40"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="40"/>
+    </row>
+    <row r="25" spans="2:11" ht="98.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:K23"/>
+    <mergeCell ref="B16:K25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -32461,7 +37909,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81B720F0-81EA-4B55-8BF5-5CBED46DDED6}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
@@ -32913,44 +38361,102 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="K13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="K14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="37"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -33024,21 +38530,45 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" ht="146" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="43"/>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="40"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="40"/>
+    </row>
+    <row r="25" spans="2:11" ht="146" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:K23"/>
+    <mergeCell ref="B16:K25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -33048,7 +38578,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FCF9B40-470A-4DE1-8AB1-26EEC2BE06FE}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
@@ -33458,41 +38988,93 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="J14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="37"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="40"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="37"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -33560,20 +39142,42 @@
       <c r="I22" s="39"/>
       <c r="J22" s="40"/>
     </row>
-    <row r="23" spans="2:10" ht="116.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="43"/>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="40"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="40"/>
+    </row>
+    <row r="25" spans="2:10" ht="116.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:J23"/>
+    <mergeCell ref="B16:J25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -33583,7 +39187,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A80A2506-0B9F-4B14-ADA0-702CD03037C2}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
@@ -34034,44 +39638,102 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="J13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="J14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="37"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -34145,21 +39807,45 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" ht="116.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="43"/>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="40"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="40"/>
+    </row>
+    <row r="25" spans="2:11" ht="116.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:K23"/>
+    <mergeCell ref="B16:K25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -34169,7 +39855,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6FB0C85-64F4-4D82-8FA2-89FE65C5C7BA}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
@@ -34621,44 +40307,102 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="J13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="J14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="37"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -34696,7 +40440,7 @@
       <c r="J19" s="39"/>
       <c r="K19" s="40"/>
     </row>
-    <row r="20" spans="2:11" ht="74" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -34720,7 +40464,7 @@
       <c r="J21" s="39"/>
       <c r="K21" s="40"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:11" ht="74" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -34732,21 +40476,45 @@
       <c r="J22" s="39"/>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="2:11" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="43"/>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="40"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="40"/>
+    </row>
+    <row r="25" spans="2:11" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:K23"/>
+    <mergeCell ref="B16:K25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -34756,7 +40524,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E45570FC-AD57-4C4E-AD9C-A3B1E85C5742}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
@@ -35080,35 +40848,75 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="35" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="6">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="37"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="40"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="37"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B17" s="38"/>
@@ -35137,7 +40945,7 @@
       <c r="G19" s="39"/>
       <c r="H19" s="40"/>
     </row>
-    <row r="20" spans="2:8" ht="71" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B20" s="38"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -35155,7 +40963,7 @@
       <c r="G21" s="39"/>
       <c r="H21" s="40"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="71" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -35164,18 +40972,36 @@
       <c r="G22" s="39"/>
       <c r="H22" s="40"/>
     </row>
-    <row r="23" spans="2:8" ht="89" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="43"/>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="40"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+    </row>
+    <row r="25" spans="2:8" ht="89" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:H23"/>
+    <mergeCell ref="B16:H25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Resultados/Entregable/Reporte_Dip_vf_2.xlsx
+++ b/Resultados/Entregable/Reporte_Dip_vf_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Desktop\Ivan\Laboral\EstrategiaSur\GitProjects\Proyeccion-electoral-congreso\Resultados\Entregable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C686FC-F065-42BC-AF4E-B1E40E13F657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4AB356-2311-485D-8F36-FC8B758ED072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1665" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="6" activeTab="9" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen de Pactos" sheetId="33" r:id="rId1"/>
@@ -54,9 +54,10 @@
     <externalReference r:id="rId37"/>
     <externalReference r:id="rId38"/>
     <externalReference r:id="rId39"/>
+    <externalReference r:id="rId40"/>
+    <externalReference r:id="rId41"/>
   </externalReferences>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="83">
   <si>
     <t>Esc</t>
   </si>
@@ -910,6 +911,12 @@
       </rPr>
       <t>- El modelo se ajusto acotando el factor de incumbencia en 1,5 para aquellos partidos que tuviesen 2 o más incumbentes en un distrito, razón por la cual se denomina incumbencia corregida. En el caso de este distrito esta corrección no aplica puesto que ningún partido cuenta con dos o mas incumbencias</t>
     </r>
+  </si>
+  <si>
+    <t>Personalizado 4 CHV+</t>
+  </si>
+  <si>
+    <t>Personalizado 4 CHV</t>
   </si>
 </sst>
 </file>
@@ -2823,13 +2830,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>106642</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>519392</xdr:colOff>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8381,7 +8388,7 @@
       <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>Distrito</v>
@@ -10727,7 +10734,7 @@
             <v>AH</v>
           </cell>
           <cell r="C1" t="str">
-            <v>AMARILLOS</v>
+            <v>AMA</v>
           </cell>
           <cell r="D1" t="str">
             <v>DEM</v>
@@ -10804,25 +10811,25 @@
             <v>1</v>
           </cell>
           <cell r="B2">
-            <v>2.14211112417604E-2</v>
+            <v>2.1421111E-2</v>
           </cell>
           <cell r="C2">
             <v>0</v>
           </cell>
           <cell r="D2">
-            <v>5.1652752512501898E-2</v>
+            <v>5.1652753000000003E-2</v>
           </cell>
           <cell r="E2">
-            <v>2.62144047808434E-3</v>
+            <v>2.6214400000000001E-3</v>
           </cell>
           <cell r="F2">
-            <v>2.3835049835035999E-2</v>
+            <v>2.383505E-2</v>
           </cell>
           <cell r="G2">
-            <v>3.01154402152486E-2</v>
+            <v>3.011544E-2</v>
           </cell>
           <cell r="H2">
-            <v>4.8952000202890696E-3</v>
+            <v>4.8951999999999997E-3</v>
           </cell>
           <cell r="I2">
             <v>0</v>
@@ -10831,52 +10838,52 @@
             <v>0</v>
           </cell>
           <cell r="K2">
-            <v>4.60654184275507E-2</v>
+            <v>4.6065417999999997E-2</v>
           </cell>
           <cell r="L2">
-            <v>3.9657760224655302E-2</v>
+            <v>3.965776E-2</v>
           </cell>
           <cell r="M2">
-            <v>4.8129370508448698E-2</v>
+            <v>4.8129370999999997E-2</v>
           </cell>
           <cell r="N2">
-            <v>3.87664243505767E-2</v>
+            <v>3.8766424000000001E-2</v>
           </cell>
           <cell r="O2">
-            <v>3.4632064574586501E-2</v>
+            <v>3.4632064999999997E-2</v>
           </cell>
           <cell r="P2">
-            <v>9.8752452556999607E-3</v>
+            <v>9.8752449999999995E-3</v>
           </cell>
           <cell r="Q2">
-            <v>1.5119970673066901E-2</v>
+            <v>1.5119970999999999E-2</v>
           </cell>
           <cell r="R2">
-            <v>3.10256818166098E-2</v>
+            <v>3.1025681999999999E-2</v>
           </cell>
           <cell r="S2">
-            <v>4.1724478997350899E-2</v>
+            <v>4.1724479000000002E-2</v>
           </cell>
           <cell r="T2">
-            <v>2.3828133105542298E-2</v>
+            <v>2.3828133000000001E-2</v>
           </cell>
           <cell r="U2">
             <v>0</v>
           </cell>
           <cell r="V2">
-            <v>0.14936815676075699</v>
+            <v>0.149368157</v>
           </cell>
           <cell r="W2">
-            <v>7.9214536198703805E-2</v>
+            <v>7.9214536000000002E-2</v>
           </cell>
           <cell r="X2">
-            <v>5.1171348139745602E-2</v>
+            <v>5.1171347999999998E-2</v>
           </cell>
           <cell r="Y2">
-            <v>0.100797498910615</v>
+            <v>0.100797499</v>
           </cell>
           <cell r="Z2">
-            <v>0.15608291775316899</v>
+            <v>0.15608291799999999</v>
           </cell>
         </row>
         <row r="3">
@@ -10884,79 +10891,79 @@
             <v>2</v>
           </cell>
           <cell r="B3">
-            <v>2.8733392238045701E-2</v>
+            <v>2.8733392E-2</v>
           </cell>
           <cell r="C3">
             <v>0</v>
           </cell>
           <cell r="D3">
-            <v>3.92678810832209E-2</v>
+            <v>3.9267880999999998E-2</v>
           </cell>
           <cell r="E3">
-            <v>7.3562871257833199E-3</v>
+            <v>7.3562870000000004E-3</v>
           </cell>
           <cell r="F3">
-            <v>3.69222355766778E-2</v>
+            <v>3.6922235999999997E-2</v>
           </cell>
           <cell r="G3">
-            <v>3.5416288309319102E-2</v>
+            <v>3.5416287999999997E-2</v>
           </cell>
           <cell r="H3">
-            <v>3.7165744665076301E-3</v>
+            <v>3.7165739999999998E-3</v>
           </cell>
           <cell r="I3">
-            <v>5.458548699437E-4</v>
+            <v>5.4585500000000004E-4</v>
           </cell>
           <cell r="J3">
             <v>0</v>
           </cell>
           <cell r="K3">
-            <v>2.9251699292123099E-2</v>
+            <v>2.9251698999999999E-2</v>
           </cell>
           <cell r="L3">
-            <v>5.5966958945591998E-2</v>
+            <v>5.5966958999999997E-2</v>
           </cell>
           <cell r="M3">
-            <v>5.7784094503292402E-2</v>
+            <v>5.7784095000000001E-2</v>
           </cell>
           <cell r="N3">
-            <v>5.9714142096395596E-3</v>
+            <v>5.9714140000000004E-3</v>
           </cell>
           <cell r="O3">
-            <v>1.8499888788447001E-2</v>
+            <v>1.8499888999999999E-2</v>
           </cell>
           <cell r="P3">
-            <v>9.9811518524035598E-3</v>
+            <v>9.9811520000000001E-3</v>
           </cell>
           <cell r="Q3">
-            <v>3.4978584123887602E-2</v>
+            <v>3.4978584E-2</v>
           </cell>
           <cell r="R3">
-            <v>4.3899995306668403E-2</v>
+            <v>4.3899994999999997E-2</v>
           </cell>
           <cell r="S3">
-            <v>2.9376174608259802E-2</v>
+            <v>2.9376175000000001E-2</v>
           </cell>
           <cell r="T3">
-            <v>3.71089485508828E-2</v>
+            <v>3.7108949000000002E-2</v>
           </cell>
           <cell r="U3">
             <v>0</v>
           </cell>
           <cell r="V3">
-            <v>0.118930042831752</v>
+            <v>0.118930043</v>
           </cell>
           <cell r="W3">
-            <v>9.0656801147621605E-2</v>
+            <v>9.0656800999999995E-2</v>
           </cell>
           <cell r="X3">
-            <v>5.9099247638539999E-2</v>
+            <v>5.9099248E-2</v>
           </cell>
           <cell r="Y3">
-            <v>0.108783263987658</v>
+            <v>0.108783264</v>
           </cell>
           <cell r="Z3">
-            <v>0.14775322054373199</v>
+            <v>0.14775322099999999</v>
           </cell>
         </row>
         <row r="4">
@@ -10964,25 +10971,25 @@
             <v>3</v>
           </cell>
           <cell r="B4">
-            <v>1.1644213188464E-2</v>
+            <v>1.1644213E-2</v>
           </cell>
           <cell r="C4">
             <v>0</v>
           </cell>
           <cell r="D4">
-            <v>3.2988518322921899E-2</v>
+            <v>3.2988518000000001E-2</v>
           </cell>
           <cell r="E4">
-            <v>3.5122528030903898E-2</v>
+            <v>3.5122528E-2</v>
           </cell>
           <cell r="F4">
-            <v>4.0888614897775802E-2</v>
+            <v>4.0888615000000003E-2</v>
           </cell>
           <cell r="G4">
-            <v>5.99500503914542E-2</v>
+            <v>5.9950049999999998E-2</v>
           </cell>
           <cell r="H4">
-            <v>2.41612470429649E-3</v>
+            <v>2.4161249999999999E-3</v>
           </cell>
           <cell r="I4">
             <v>0</v>
@@ -10991,52 +10998,52 @@
             <v>0</v>
           </cell>
           <cell r="K4">
-            <v>5.22682466509145E-2</v>
+            <v>5.2268246999999997E-2</v>
           </cell>
           <cell r="L4">
-            <v>4.3295096143528299E-2</v>
+            <v>4.3295095999999998E-2</v>
           </cell>
           <cell r="M4">
-            <v>5.48309519250798E-2</v>
+            <v>5.4830952000000002E-2</v>
           </cell>
           <cell r="N4">
-            <v>2.1583813577568801E-3</v>
+            <v>2.158381E-3</v>
           </cell>
           <cell r="O4">
-            <v>1.8237708798410999E-2</v>
+            <v>1.8237709000000001E-2</v>
           </cell>
           <cell r="P4">
-            <v>1.28257998635187E-3</v>
+            <v>1.28258E-3</v>
           </cell>
           <cell r="Q4">
-            <v>2.1355877284710601E-2</v>
+            <v>2.1355876999999999E-2</v>
           </cell>
           <cell r="R4">
-            <v>4.5316014383130702E-2</v>
+            <v>4.5316014000000002E-2</v>
           </cell>
           <cell r="S4">
-            <v>3.8294349213830098E-2</v>
+            <v>3.8294348999999998E-2</v>
           </cell>
           <cell r="T4">
-            <v>3.9898670044331799E-2</v>
+            <v>3.9898669999999997E-2</v>
           </cell>
           <cell r="U4">
             <v>0</v>
           </cell>
           <cell r="V4">
-            <v>9.9653571901977503E-2</v>
+            <v>9.9653571999999996E-2</v>
           </cell>
           <cell r="W4">
-            <v>6.4025025300928504E-2</v>
+            <v>6.4025024999999999E-2</v>
           </cell>
           <cell r="X4">
-            <v>4.07024084800717E-2</v>
+            <v>4.0702408000000002E-2</v>
           </cell>
           <cell r="Y4">
-            <v>0.117907060905278</v>
+            <v>0.11790706099999999</v>
           </cell>
           <cell r="Z4">
-            <v>0.17776400808788101</v>
+            <v>0.177764008</v>
           </cell>
         </row>
         <row r="5">
@@ -11047,76 +11054,76 @@
             <v>0</v>
           </cell>
           <cell r="C5">
-            <v>2.2339755491591499E-2</v>
+            <v>2.2339754999999999E-2</v>
           </cell>
           <cell r="D5">
-            <v>1.10088279886013E-2</v>
+            <v>1.1008828E-2</v>
           </cell>
           <cell r="E5">
             <v>0</v>
           </cell>
           <cell r="F5">
-            <v>3.9026356767269697E-2</v>
+            <v>3.9026356999999998E-2</v>
           </cell>
           <cell r="G5">
-            <v>8.6418068756962493E-2</v>
+            <v>8.6418069E-2</v>
           </cell>
           <cell r="H5">
-            <v>1.54135901376E-2</v>
+            <v>1.541359E-2</v>
           </cell>
           <cell r="I5">
-            <v>7.1805624226807302E-4</v>
+            <v>7.1805600000000001E-4</v>
           </cell>
           <cell r="J5">
             <v>0</v>
           </cell>
           <cell r="K5">
-            <v>7.5816481237190397E-2</v>
+            <v>7.5816481000000005E-2</v>
           </cell>
           <cell r="L5">
-            <v>1.9479840058101001E-2</v>
+            <v>1.9479839999999998E-2</v>
           </cell>
           <cell r="M5">
-            <v>2.6814271675553399E-2</v>
+            <v>2.6814272E-2</v>
           </cell>
           <cell r="N5">
-            <v>6.0275692565245603E-3</v>
+            <v>6.027569E-3</v>
           </cell>
           <cell r="O5">
-            <v>1.43200930600889E-2</v>
+            <v>1.4320093000000001E-2</v>
           </cell>
           <cell r="P5">
-            <v>1.2838845611753099E-2</v>
+            <v>1.2838845999999999E-2</v>
           </cell>
           <cell r="Q5">
-            <v>3.7569728390097298E-2</v>
+            <v>3.7569727999999997E-2</v>
           </cell>
           <cell r="R5">
-            <v>4.69198464590595E-2</v>
+            <v>4.6919846000000001E-2</v>
           </cell>
           <cell r="S5">
-            <v>8.1845076288346696E-2</v>
+            <v>8.1845076000000003E-2</v>
           </cell>
           <cell r="T5">
-            <v>2.5435603690398701E-2</v>
+            <v>2.5435604000000001E-2</v>
           </cell>
           <cell r="U5">
             <v>0</v>
           </cell>
           <cell r="V5">
-            <v>7.8710247893530705E-2</v>
+            <v>7.8710247999999997E-2</v>
           </cell>
           <cell r="W5">
-            <v>0.109131213494533</v>
+            <v>0.109131213</v>
           </cell>
           <cell r="X5">
-            <v>5.4464565976033302E-2</v>
+            <v>5.4464565999999999E-2</v>
           </cell>
           <cell r="Y5">
-            <v>0.10167676390515901</v>
+            <v>0.101676764</v>
           </cell>
           <cell r="Z5">
-            <v>0.13402519761933501</v>
+            <v>0.13402519800000001</v>
           </cell>
         </row>
         <row r="6">
@@ -11124,79 +11131,79 @@
             <v>5</v>
           </cell>
           <cell r="B6">
-            <v>8.2651865922530598E-3</v>
+            <v>8.2651870000000002E-3</v>
           </cell>
           <cell r="C6">
-            <v>1.2370970399822399E-2</v>
+            <v>1.237097E-2</v>
           </cell>
           <cell r="D6">
-            <v>3.022751961829E-2</v>
+            <v>3.0227520000000001E-2</v>
           </cell>
           <cell r="E6">
-            <v>1.1546310531803701E-2</v>
+            <v>1.1546311E-2</v>
           </cell>
           <cell r="F6">
-            <v>4.94845965189845E-2</v>
+            <v>4.9484596999999998E-2</v>
           </cell>
           <cell r="G6">
-            <v>2.04113147480426E-2</v>
+            <v>2.0411314999999999E-2</v>
           </cell>
           <cell r="H6">
-            <v>1.7181903333086601E-3</v>
+            <v>1.7181900000000001E-3</v>
           </cell>
           <cell r="I6">
-            <v>6.3806582766074297E-3</v>
+            <v>6.380658E-3</v>
           </cell>
           <cell r="J6">
             <v>0</v>
           </cell>
           <cell r="K6">
-            <v>7.6278714302719097E-2</v>
+            <v>7.6278713999999997E-2</v>
           </cell>
           <cell r="L6">
-            <v>6.26180287733729E-2</v>
+            <v>6.2618029000000006E-2</v>
           </cell>
           <cell r="M6">
-            <v>3.9467499214481901E-2</v>
+            <v>3.9467499000000003E-2</v>
           </cell>
           <cell r="N6">
-            <v>1.7181903333086601E-3</v>
+            <v>1.7181900000000001E-3</v>
           </cell>
           <cell r="O6">
-            <v>1.1204936377509E-2</v>
+            <v>1.1204936E-2</v>
           </cell>
           <cell r="P6">
-            <v>1.7181903333086601E-3</v>
+            <v>1.7181900000000001E-3</v>
           </cell>
           <cell r="Q6">
-            <v>2.78675697055638E-2</v>
+            <v>2.7867570000000001E-2</v>
           </cell>
           <cell r="R6">
-            <v>3.1660218686785403E-2</v>
+            <v>3.1660219000000003E-2</v>
           </cell>
           <cell r="S6">
-            <v>6.00285896385973E-2</v>
+            <v>6.002859E-2</v>
           </cell>
           <cell r="T6">
-            <v>2.8225744472687699E-2</v>
+            <v>2.8225744000000001E-2</v>
           </cell>
           <cell r="U6">
             <v>0</v>
           </cell>
           <cell r="V6">
-            <v>8.3010040689654396E-2</v>
+            <v>8.3010041000000007E-2</v>
           </cell>
           <cell r="W6">
-            <v>8.6440225385582894E-2</v>
+            <v>8.6440224999999996E-2</v>
           </cell>
           <cell r="X6">
-            <v>9.4297192832072094E-2</v>
+            <v>9.4297193000000001E-2</v>
           </cell>
           <cell r="Y6">
-            <v>0.115193223133228</v>
+            <v>0.115193223</v>
           </cell>
           <cell r="Z6">
-            <v>0.139866889102014</v>
+            <v>0.13986688899999999</v>
           </cell>
         </row>
         <row r="7">
@@ -11207,76 +11214,76 @@
             <v>0</v>
           </cell>
           <cell r="C7">
-            <v>8.4679268527256494E-3</v>
+            <v>8.4679270000000001E-3</v>
           </cell>
           <cell r="D7">
-            <v>1.3054156487423601E-2</v>
+            <v>1.3054156000000001E-2</v>
           </cell>
           <cell r="E7">
-            <v>4.7873231547483699E-3</v>
+            <v>4.7873229999999996E-3</v>
           </cell>
           <cell r="F7">
-            <v>6.2424166872084699E-2</v>
+            <v>6.2424167000000003E-2</v>
           </cell>
           <cell r="G7">
-            <v>2.64913213903149E-2</v>
+            <v>2.6491321000000002E-2</v>
           </cell>
           <cell r="H7">
-            <v>5.8641465201795702E-3</v>
+            <v>5.8641470000000001E-3</v>
           </cell>
           <cell r="I7">
-            <v>1.38720684203074E-2</v>
+            <v>1.3872068E-2</v>
           </cell>
           <cell r="J7">
             <v>0</v>
           </cell>
           <cell r="K7">
-            <v>5.9324562685052498E-2</v>
+            <v>5.9324562999999997E-2</v>
           </cell>
           <cell r="L7">
-            <v>4.6771870824066003E-2</v>
+            <v>4.6771871E-2</v>
           </cell>
           <cell r="M7">
-            <v>1.5639886349726701E-2</v>
+            <v>1.5639885999999999E-2</v>
           </cell>
           <cell r="N7">
-            <v>5.8641465201795702E-3</v>
+            <v>5.8641470000000001E-3</v>
           </cell>
           <cell r="O7">
-            <v>1.7106487056966699E-2</v>
+            <v>1.7106487E-2</v>
           </cell>
           <cell r="P7">
-            <v>1.33917566886863E-2</v>
+            <v>1.3391757000000001E-2</v>
           </cell>
           <cell r="Q7">
-            <v>3.8530703003767403E-2</v>
+            <v>3.8530702999999999E-2</v>
           </cell>
           <cell r="R7">
-            <v>4.1236581308625203E-2</v>
+            <v>4.1236581000000001E-2</v>
           </cell>
           <cell r="S7">
-            <v>5.2488793196326503E-2</v>
+            <v>5.2488792999999999E-2</v>
           </cell>
           <cell r="T7">
-            <v>2.2965274843792901E-2</v>
+            <v>2.2965275E-2</v>
           </cell>
           <cell r="U7">
             <v>0</v>
           </cell>
           <cell r="V7">
-            <v>0.13512017946679999</v>
+            <v>0.13512017900000001</v>
           </cell>
           <cell r="W7">
-            <v>0.127718076474201</v>
+            <v>0.12771807600000001</v>
           </cell>
           <cell r="X7">
-            <v>5.7587769001363302E-2</v>
+            <v>5.7587768999999997E-2</v>
           </cell>
           <cell r="Y7">
-            <v>9.2426868801849194E-2</v>
+            <v>9.2426868999999995E-2</v>
           </cell>
           <cell r="Z7">
-            <v>0.13886593408080999</v>
+            <v>0.138865934</v>
           </cell>
         </row>
         <row r="8">
@@ -11287,76 +11294,76 @@
             <v>0</v>
           </cell>
           <cell r="C8">
-            <v>4.0683463052404297E-3</v>
+            <v>4.0683459999999996E-3</v>
           </cell>
           <cell r="D8">
-            <v>7.3163289428187003E-3</v>
+            <v>7.3163289999999999E-3</v>
           </cell>
           <cell r="E8">
-            <v>1.7359134293681799E-2</v>
+            <v>1.7359133999999998E-2</v>
           </cell>
           <cell r="F8">
-            <v>0.10629133758727</v>
+            <v>0.106291338</v>
           </cell>
           <cell r="G8">
-            <v>1.21342097028849E-2</v>
+            <v>1.2134209999999999E-2</v>
           </cell>
           <cell r="H8">
-            <v>5.9560295036047602E-3</v>
+            <v>5.9560300000000002E-3</v>
           </cell>
           <cell r="I8">
-            <v>1.07887535164313E-3</v>
+            <v>1.078875E-3</v>
           </cell>
           <cell r="J8">
             <v>0</v>
           </cell>
           <cell r="K8">
-            <v>6.3228371612488302E-2</v>
+            <v>6.3228372000000005E-2</v>
           </cell>
           <cell r="L8">
-            <v>4.2710911912666599E-2</v>
+            <v>4.2710911999999997E-2</v>
           </cell>
           <cell r="M8">
-            <v>3.1641531261832799E-2</v>
+            <v>3.1641531000000001E-2</v>
           </cell>
           <cell r="N8">
-            <v>5.9560295036047602E-3</v>
+            <v>5.9560300000000002E-3</v>
           </cell>
           <cell r="O8">
-            <v>1.13093631736508E-2</v>
+            <v>1.1309362999999999E-2</v>
           </cell>
           <cell r="P8">
-            <v>1.7595032431511001E-2</v>
+            <v>1.7595032E-2</v>
           </cell>
           <cell r="Q8">
-            <v>3.0007677647585499E-2</v>
+            <v>3.0007677999999999E-2</v>
           </cell>
           <cell r="R8">
-            <v>3.20025510470918E-2</v>
+            <v>3.2002550999999997E-2</v>
           </cell>
           <cell r="S8">
-            <v>3.4268488142980502E-2</v>
+            <v>3.4268488E-2</v>
           </cell>
           <cell r="T8">
-            <v>2.5098346511451999E-2</v>
+            <v>2.5098347E-2</v>
           </cell>
           <cell r="U8">
             <v>0</v>
           </cell>
           <cell r="V8">
-            <v>0.152693437718259</v>
+            <v>0.15269343799999999</v>
           </cell>
           <cell r="W8">
-            <v>8.2577597586666399E-2</v>
+            <v>8.2577598000000002E-2</v>
           </cell>
           <cell r="X8">
-            <v>6.7865742479924995E-2</v>
+            <v>6.7865742000000007E-2</v>
           </cell>
           <cell r="Y8">
-            <v>9.5277245562489996E-2</v>
+            <v>9.5277245999999996E-2</v>
           </cell>
           <cell r="Z8">
-            <v>0.15356341172064999</v>
+            <v>0.15356341200000001</v>
           </cell>
         </row>
         <row r="9">
@@ -11364,79 +11371,79 @@
             <v>8</v>
           </cell>
           <cell r="B9">
-            <v>4.8985471717335497E-3</v>
+            <v>4.8985469999999996E-3</v>
           </cell>
           <cell r="C9">
             <v>0</v>
           </cell>
           <cell r="D9">
-            <v>2.0322503003270601E-2</v>
+            <v>2.0322502999999999E-2</v>
           </cell>
           <cell r="E9">
-            <v>1.45862694730854E-2</v>
+            <v>1.4586269000000001E-2</v>
           </cell>
           <cell r="F9">
-            <v>0.137276543372437</v>
+            <v>0.137276543</v>
           </cell>
           <cell r="G9">
-            <v>1.8069224830557999E-2</v>
+            <v>1.8069225000000001E-2</v>
           </cell>
           <cell r="H9">
-            <v>3.0548045520417898E-3</v>
+            <v>3.0548049999999998E-3</v>
           </cell>
           <cell r="I9">
-            <v>2.43990648601188E-3</v>
+            <v>2.4399059999999999E-3</v>
           </cell>
           <cell r="J9">
-            <v>3.1033647871625401E-2</v>
+            <v>3.1033648E-2</v>
           </cell>
           <cell r="K9">
-            <v>7.2019616312884699E-2</v>
+            <v>7.2019615999999995E-2</v>
           </cell>
           <cell r="L9">
-            <v>4.0093506851275197E-2</v>
+            <v>4.0093507E-2</v>
           </cell>
           <cell r="M9">
-            <v>3.0648793883301599E-2</v>
+            <v>3.0648794E-2</v>
           </cell>
           <cell r="N9">
-            <v>2.1141336214712699E-2</v>
+            <v>2.1141336E-2</v>
           </cell>
           <cell r="O9">
-            <v>2.72213274411598E-2</v>
+            <v>2.7221327E-2</v>
           </cell>
           <cell r="P9">
-            <v>3.0548045520417898E-3</v>
+            <v>3.0548049999999998E-3</v>
           </cell>
           <cell r="Q9">
-            <v>2.1918299976644701E-2</v>
+            <v>2.1918300000000002E-2</v>
           </cell>
           <cell r="R9">
-            <v>2.7566750399618301E-2</v>
+            <v>2.7566750000000001E-2</v>
           </cell>
           <cell r="S9">
-            <v>3.5892942434443201E-2</v>
+            <v>3.5892941999999997E-2</v>
           </cell>
           <cell r="T9">
-            <v>1.18095042341967E-2</v>
+            <v>1.1809504E-2</v>
           </cell>
           <cell r="U9">
             <v>0</v>
           </cell>
           <cell r="V9">
-            <v>0.136010825155855</v>
+            <v>0.136010825</v>
           </cell>
           <cell r="W9">
-            <v>7.1687039662798602E-2</v>
+            <v>7.1687039999999994E-2</v>
           </cell>
           <cell r="X9">
-            <v>5.7095239140274999E-2</v>
+            <v>5.7095238999999999E-2</v>
           </cell>
           <cell r="Y9">
-            <v>8.3908696290610596E-2</v>
+            <v>8.3908696000000005E-2</v>
           </cell>
           <cell r="Z9">
-            <v>0.12824987068941601</v>
+            <v>0.12824987099999999</v>
           </cell>
         </row>
         <row r="10">
@@ -11444,79 +11451,79 @@
             <v>9</v>
           </cell>
           <cell r="B10">
-            <v>5.07818480744982E-3</v>
+            <v>5.0781849999999998E-3</v>
           </cell>
           <cell r="C10">
             <v>0</v>
           </cell>
           <cell r="D10">
-            <v>2.8896354528642601E-2</v>
+            <v>2.8896354999999999E-2</v>
           </cell>
           <cell r="E10">
-            <v>1.4803022274807599E-2</v>
+            <v>1.4803022000000001E-2</v>
           </cell>
           <cell r="F10">
-            <v>7.4110235488295303E-2</v>
+            <v>7.4110234999999997E-2</v>
           </cell>
           <cell r="G10">
-            <v>1.99028504902766E-2</v>
+            <v>1.990285E-2</v>
           </cell>
           <cell r="H10">
-            <v>1.0809234556381801E-3</v>
+            <v>1.0809229999999999E-3</v>
           </cell>
           <cell r="I10">
             <v>0</v>
           </cell>
           <cell r="J10">
-            <v>2.7561944903364801E-2</v>
+            <v>2.7561945000000001E-2</v>
           </cell>
           <cell r="K10">
-            <v>9.98383691665337E-2</v>
+            <v>9.9838368999999996E-2</v>
           </cell>
           <cell r="L10">
-            <v>2.9824883452919799E-2</v>
+            <v>2.9824883E-2</v>
           </cell>
           <cell r="M10">
-            <v>3.1645067347071197E-2</v>
+            <v>3.1645066999999999E-2</v>
           </cell>
           <cell r="N10">
-            <v>1.74831531007477E-2</v>
+            <v>1.7483153000000001E-2</v>
           </cell>
           <cell r="O10">
-            <v>7.4284985967857098E-3</v>
+            <v>7.4284989999999999E-3</v>
           </cell>
           <cell r="P10">
-            <v>1.0809234556381801E-3</v>
+            <v>1.0809229999999999E-3</v>
           </cell>
           <cell r="Q10">
-            <v>4.2835243698094203E-2</v>
+            <v>4.2835244000000001E-2</v>
           </cell>
           <cell r="R10">
-            <v>2.6434350065825299E-2</v>
+            <v>2.6434349999999999E-2</v>
           </cell>
           <cell r="S10">
-            <v>5.2144046766862198E-2</v>
+            <v>5.2144046999999999E-2</v>
           </cell>
           <cell r="T10">
-            <v>2.4456783859041001E-2</v>
+            <v>2.4456783999999999E-2</v>
           </cell>
           <cell r="U10">
             <v>0</v>
           </cell>
           <cell r="V10">
-            <v>9.8133349579249393E-2</v>
+            <v>9.8133349999999994E-2</v>
           </cell>
           <cell r="W10">
-            <v>9.05081898923146E-2</v>
+            <v>9.0508190000000002E-2</v>
           </cell>
           <cell r="X10">
-            <v>6.2312707699896198E-2</v>
+            <v>6.2312708000000001E-2</v>
           </cell>
           <cell r="Y10">
-            <v>9.2223630379756297E-2</v>
+            <v>9.2223630000000001E-2</v>
           </cell>
           <cell r="Z10">
-            <v>0.15221728699078799</v>
+            <v>0.15221728700000001</v>
           </cell>
         </row>
         <row r="11">
@@ -11524,79 +11531,79 @@
             <v>10</v>
           </cell>
           <cell r="B11">
-            <v>8.4008583481277495E-3</v>
+            <v>8.4008580000000006E-3</v>
           </cell>
           <cell r="C11">
             <v>0</v>
           </cell>
           <cell r="D11">
-            <v>1.19203707021515E-2</v>
+            <v>1.1920371000000001E-2</v>
           </cell>
           <cell r="E11">
-            <v>2.9660447578871901E-2</v>
+            <v>2.9660447999999999E-2</v>
           </cell>
           <cell r="F11">
-            <v>0.162897209961398</v>
+            <v>0.16289720999999999</v>
           </cell>
           <cell r="G11">
-            <v>1.98087854455429E-2</v>
+            <v>1.9808784999999999E-2</v>
           </cell>
           <cell r="H11">
-            <v>2.2074911369176502E-3</v>
+            <v>2.2074909999999998E-3</v>
           </cell>
           <cell r="I11">
-            <v>2.8777871882991E-3</v>
+            <v>2.8777870000000001E-3</v>
           </cell>
           <cell r="J11">
-            <v>3.67967897454273E-2</v>
+            <v>3.6796790000000003E-2</v>
           </cell>
           <cell r="K11">
-            <v>9.7689015749955199E-2</v>
+            <v>9.7689016000000004E-2</v>
           </cell>
           <cell r="L11">
-            <v>3.4845350750036599E-2</v>
+            <v>3.4845350999999997E-2</v>
           </cell>
           <cell r="M11">
-            <v>1.30725035425183E-2</v>
+            <v>1.3072504E-2</v>
           </cell>
           <cell r="N11">
-            <v>8.7071979629840708E-3</v>
+            <v>8.7071979999999993E-3</v>
           </cell>
           <cell r="O11">
-            <v>1.5867224782969799E-2</v>
+            <v>1.5867224999999999E-2</v>
           </cell>
           <cell r="P11">
-            <v>2.2074911369176502E-3</v>
+            <v>2.2074909999999998E-3</v>
           </cell>
           <cell r="Q11">
-            <v>2.2478296985194698E-2</v>
+            <v>2.2478297000000001E-2</v>
           </cell>
           <cell r="R11">
-            <v>1.3061305926999601E-2</v>
+            <v>1.3061306E-2</v>
           </cell>
           <cell r="S11">
-            <v>4.7347793866149797E-2</v>
+            <v>4.7347793999999999E-2</v>
           </cell>
           <cell r="T11">
-            <v>1.2762227796146299E-2</v>
+            <v>1.2762228E-2</v>
           </cell>
           <cell r="U11">
             <v>0</v>
           </cell>
           <cell r="V11">
-            <v>0.112442993957359</v>
+            <v>0.112442994</v>
           </cell>
           <cell r="W11">
-            <v>9.5315528446015194E-2</v>
+            <v>9.5315527999999997E-2</v>
           </cell>
           <cell r="X11">
-            <v>7.6341067153118197E-2</v>
+            <v>7.6341066999999999E-2</v>
           </cell>
           <cell r="Y11">
-            <v>6.7329226183689694E-2</v>
+            <v>6.7329226000000006E-2</v>
           </cell>
           <cell r="Z11">
-            <v>0.105963035653207</v>
+            <v>0.105963036</v>
           </cell>
         </row>
         <row r="12">
@@ -11604,79 +11611,79 @@
             <v>11</v>
           </cell>
           <cell r="B12">
-            <v>2.2687785839561599E-2</v>
+            <v>2.2687786000000001E-2</v>
           </cell>
           <cell r="C12">
             <v>0</v>
           </cell>
           <cell r="D12">
-            <v>1.0441272575784E-2</v>
+            <v>1.0441272999999999E-2</v>
           </cell>
           <cell r="E12">
-            <v>8.3051347045999105E-2</v>
+            <v>8.3051346999999998E-2</v>
           </cell>
           <cell r="F12">
-            <v>7.5916110474036402E-2</v>
+            <v>7.5916109999999995E-2</v>
           </cell>
           <cell r="G12">
-            <v>1.13437461283767E-2</v>
+            <v>1.1343746E-2</v>
           </cell>
           <cell r="H12">
-            <v>2.0938325885137398E-3</v>
+            <v>2.0938329999999998E-3</v>
           </cell>
           <cell r="I12">
-            <v>4.4125496081550203E-3</v>
+            <v>4.4125500000000003E-3</v>
           </cell>
           <cell r="J12">
-            <v>2.5073146156678099E-2</v>
+            <v>2.5073146000000001E-2</v>
           </cell>
           <cell r="K12">
-            <v>2.7953487088521599E-2</v>
+            <v>2.7953486999999999E-2</v>
           </cell>
           <cell r="L12">
-            <v>3.1199045033841199E-2</v>
+            <v>3.1199045000000002E-2</v>
           </cell>
           <cell r="M12">
-            <v>2.3926998873229099E-3</v>
+            <v>2.3927000000000002E-3</v>
           </cell>
           <cell r="N12">
-            <v>7.8950288797408393E-3</v>
+            <v>7.8950289999999996E-3</v>
           </cell>
           <cell r="O12">
-            <v>7.37157073261241E-3</v>
+            <v>7.3715710000000004E-3</v>
           </cell>
           <cell r="P12">
-            <v>2.0938325885137398E-3</v>
+            <v>2.0938329999999998E-3</v>
           </cell>
           <cell r="Q12">
-            <v>2.2648739326063001E-2</v>
+            <v>2.2648739000000001E-2</v>
           </cell>
           <cell r="R12">
-            <v>9.5112022392147902E-3</v>
+            <v>9.5112019999999999E-3</v>
           </cell>
           <cell r="S12">
-            <v>3.0585456964576801E-2</v>
+            <v>3.0585457E-2</v>
           </cell>
           <cell r="T12">
-            <v>1.44372281790174E-2</v>
+            <v>1.4437228E-2</v>
           </cell>
           <cell r="U12">
             <v>0</v>
           </cell>
           <cell r="V12">
-            <v>0.19387915074713799</v>
+            <v>0.193879151</v>
           </cell>
           <cell r="W12">
-            <v>0.13586836216609999</v>
+            <v>0.13586836199999999</v>
           </cell>
           <cell r="X12">
-            <v>0.12403873649005299</v>
+            <v>0.124038736</v>
           </cell>
           <cell r="Y12">
-            <v>6.69588989940091E-2</v>
+            <v>6.6958899000000002E-2</v>
           </cell>
           <cell r="Z12">
-            <v>8.8146770266168004E-2</v>
+            <v>8.8146769999999999E-2</v>
           </cell>
         </row>
         <row r="13">
@@ -11684,79 +11691,79 @@
             <v>12</v>
           </cell>
           <cell r="B13">
-            <v>1.5211849459784699E-2</v>
+            <v>1.5211849E-2</v>
           </cell>
           <cell r="C13">
             <v>0</v>
           </cell>
           <cell r="D13">
-            <v>2.54804387907616E-2</v>
+            <v>2.5480439000000001E-2</v>
           </cell>
           <cell r="E13">
-            <v>1.80586163508289E-2</v>
+            <v>1.8058616E-2</v>
           </cell>
           <cell r="F13">
-            <v>5.9320712553139601E-2</v>
+            <v>5.9320712999999997E-2</v>
           </cell>
           <cell r="G13">
-            <v>1.6918545873744899E-2</v>
+            <v>1.6918546E-2</v>
           </cell>
           <cell r="H13">
-            <v>3.4171809408823999E-3</v>
+            <v>3.417181E-3</v>
           </cell>
           <cell r="I13">
-            <v>1.1247286195873899E-2</v>
+            <v>1.1247286E-2</v>
           </cell>
           <cell r="J13">
-            <v>4.4920276889843999E-2</v>
+            <v>4.4920277000000002E-2</v>
           </cell>
           <cell r="K13">
-            <v>9.71635064713091E-2</v>
+            <v>9.7163505999999997E-2</v>
           </cell>
           <cell r="L13">
-            <v>2.45458355607437E-2</v>
+            <v>2.4545836000000001E-2</v>
           </cell>
           <cell r="M13">
-            <v>2.27204954488095E-2</v>
+            <v>2.2720495E-2</v>
           </cell>
           <cell r="N13">
-            <v>3.5270286405583801E-2</v>
+            <v>3.5270285999999998E-2</v>
           </cell>
           <cell r="O13">
-            <v>1.5862798791198E-2</v>
+            <v>1.5862799E-2</v>
           </cell>
           <cell r="P13">
-            <v>3.4171809408823999E-3</v>
+            <v>3.417181E-3</v>
           </cell>
           <cell r="Q13">
-            <v>2.4901993941443601E-2</v>
+            <v>2.4901994E-2</v>
           </cell>
           <cell r="R13">
-            <v>1.8880030765538201E-2</v>
+            <v>1.8880030999999999E-2</v>
           </cell>
           <cell r="S13">
-            <v>4.1048219344468499E-2</v>
+            <v>4.1048218999999997E-2</v>
           </cell>
           <cell r="T13">
-            <v>3.1617863649752803E-2</v>
+            <v>3.1617864000000002E-2</v>
           </cell>
           <cell r="U13">
             <v>0</v>
           </cell>
           <cell r="V13">
-            <v>9.3772160460828397E-2</v>
+            <v>9.3772159999999993E-2</v>
           </cell>
           <cell r="W13">
-            <v>0.117121103850056</v>
+            <v>0.117121104</v>
           </cell>
           <cell r="X13">
-            <v>4.3340179211078501E-2</v>
+            <v>4.3340179E-2</v>
           </cell>
           <cell r="Y13">
-            <v>9.3881939974471099E-2</v>
+            <v>9.3881939999999997E-2</v>
           </cell>
           <cell r="Z13">
-            <v>0.14188149812897499</v>
+            <v>0.14188149799999999</v>
           </cell>
         </row>
         <row r="14">
@@ -11764,79 +11771,79 @@
             <v>13</v>
           </cell>
           <cell r="B14">
-            <v>1.21801169720484E-2</v>
+            <v>1.2180117000000001E-2</v>
           </cell>
           <cell r="C14">
             <v>0</v>
           </cell>
           <cell r="D14">
-            <v>2.5604704045175401E-2</v>
+            <v>2.5604703999999999E-2</v>
           </cell>
           <cell r="E14">
-            <v>1.6346112927428099E-2</v>
+            <v>1.6346112999999999E-2</v>
           </cell>
           <cell r="F14">
-            <v>9.0928837995008005E-2</v>
+            <v>9.0928837999999998E-2</v>
           </cell>
           <cell r="G14">
-            <v>2.5328278483026798E-2</v>
+            <v>2.5328277999999999E-2</v>
           </cell>
           <cell r="H14">
-            <v>3.30230484151786E-3</v>
+            <v>3.3023050000000002E-3</v>
           </cell>
           <cell r="I14">
-            <v>9.8395658601479006E-3</v>
+            <v>9.8395659999999992E-3</v>
           </cell>
           <cell r="J14">
-            <v>3.1465147991289001E-2</v>
+            <v>3.1465147999999998E-2</v>
           </cell>
           <cell r="K14">
-            <v>9.9967990882026903E-2</v>
+            <v>9.9967991000000006E-2</v>
           </cell>
           <cell r="L14">
-            <v>3.0337612933903899E-2</v>
+            <v>3.0337612999999999E-2</v>
           </cell>
           <cell r="M14">
-            <v>7.0816010479748202E-3</v>
+            <v>7.0816009999999999E-3</v>
           </cell>
           <cell r="N14">
-            <v>1.16838831315648E-2</v>
+            <v>1.1683883000000001E-2</v>
           </cell>
           <cell r="O14">
-            <v>7.8897850208429297E-3</v>
+            <v>7.8897849999999999E-3</v>
           </cell>
           <cell r="P14">
-            <v>3.30230484151786E-3</v>
+            <v>3.3023050000000002E-3</v>
           </cell>
           <cell r="Q14">
-            <v>2.05953695942983E-2</v>
+            <v>2.0595370000000002E-2</v>
           </cell>
           <cell r="R14">
-            <v>3.3089286936764398E-2</v>
+            <v>3.3089287000000002E-2</v>
           </cell>
           <cell r="S14">
-            <v>8.0669268101341202E-2</v>
+            <v>8.0669268000000002E-2</v>
           </cell>
           <cell r="T14">
-            <v>2.5916654177559902E-2</v>
+            <v>2.5916654000000001E-2</v>
           </cell>
           <cell r="U14">
             <v>0</v>
           </cell>
           <cell r="V14">
-            <v>0.10105186032183</v>
+            <v>0.10105185999999999</v>
           </cell>
           <cell r="W14">
-            <v>9.2068584623411803E-2</v>
+            <v>9.2068584999999994E-2</v>
           </cell>
           <cell r="X14">
-            <v>4.5647592562783203E-2</v>
+            <v>4.5647593E-2</v>
           </cell>
           <cell r="Y14">
-            <v>8.9088961294870497E-2</v>
+            <v>8.9088960999999994E-2</v>
           </cell>
           <cell r="Z14">
-            <v>0.13661417541366599</v>
+            <v>0.136614175</v>
           </cell>
         </row>
         <row r="15">
@@ -11844,79 +11851,79 @@
             <v>14</v>
           </cell>
           <cell r="B15">
-            <v>4.5862756994439402E-3</v>
+            <v>4.5862760000000002E-3</v>
           </cell>
           <cell r="C15">
             <v>0</v>
           </cell>
           <cell r="D15">
-            <v>1.0615910981567001E-2</v>
+            <v>1.0615911E-2</v>
           </cell>
           <cell r="E15">
-            <v>1.9774951994345601E-2</v>
+            <v>1.9774951999999998E-2</v>
           </cell>
           <cell r="F15">
-            <v>7.0075870825697203E-2</v>
+            <v>7.0075870999999998E-2</v>
           </cell>
           <cell r="G15">
-            <v>2.0116714724444401E-2</v>
+            <v>2.0116715E-2</v>
           </cell>
           <cell r="H15">
             <v>0</v>
           </cell>
           <cell r="I15">
-            <v>1.24820956110009E-2</v>
+            <v>1.2482096E-2</v>
           </cell>
           <cell r="J15">
-            <v>2.8019289829056E-2</v>
+            <v>2.8019289999999999E-2</v>
           </cell>
           <cell r="K15">
-            <v>5.4328765238276899E-2</v>
+            <v>5.4328765000000001E-2</v>
           </cell>
           <cell r="L15">
-            <v>3.7997210355460699E-2</v>
+            <v>3.7997209999999997E-2</v>
           </cell>
           <cell r="M15">
-            <v>2.9571232885280501E-2</v>
+            <v>2.9571232999999999E-2</v>
           </cell>
           <cell r="N15">
-            <v>1.0518085778442101E-2</v>
+            <v>1.0518085999999999E-2</v>
           </cell>
           <cell r="O15">
-            <v>1.2997491821838E-2</v>
+            <v>1.2997491999999999E-2</v>
           </cell>
           <cell r="P15">
             <v>0</v>
           </cell>
           <cell r="Q15">
-            <v>2.7546176122894402E-2</v>
+            <v>2.7546175999999999E-2</v>
           </cell>
           <cell r="R15">
-            <v>3.3917824327451697E-2</v>
+            <v>3.3917823999999999E-2</v>
           </cell>
           <cell r="S15">
-            <v>8.1659275568092896E-2</v>
+            <v>8.1659276000000003E-2</v>
           </cell>
           <cell r="T15">
-            <v>2.3261131995221299E-2</v>
+            <v>2.3261132E-2</v>
           </cell>
           <cell r="U15">
             <v>0</v>
           </cell>
           <cell r="V15">
-            <v>0.13019533766583</v>
+            <v>0.13019533799999999</v>
           </cell>
           <cell r="W15">
-            <v>6.4444791933799095E-2</v>
+            <v>6.4444792000000001E-2</v>
           </cell>
           <cell r="X15">
-            <v>0.11550329315661401</v>
+            <v>0.11550329300000001</v>
           </cell>
           <cell r="Y15">
-            <v>8.9645164720378798E-2</v>
+            <v>8.9645164999999999E-2</v>
           </cell>
           <cell r="Z15">
-            <v>0.122743108764862</v>
+            <v>0.122743109</v>
           </cell>
         </row>
         <row r="16">
@@ -11927,76 +11934,76 @@
             <v>0</v>
           </cell>
           <cell r="C16">
-            <v>3.59135236418868E-3</v>
+            <v>3.5913519999999999E-3</v>
           </cell>
           <cell r="D16">
-            <v>1.8761419425748601E-2</v>
+            <v>1.8761419000000001E-2</v>
           </cell>
           <cell r="E16">
-            <v>4.0881797663491698E-3</v>
+            <v>4.0881800000000003E-3</v>
           </cell>
           <cell r="F16">
-            <v>5.6560453755508201E-2</v>
+            <v>5.6560454000000003E-2</v>
           </cell>
           <cell r="G16">
-            <v>2.9950378095792301E-2</v>
+            <v>2.9950378E-2</v>
           </cell>
           <cell r="H16">
             <v>0</v>
           </cell>
           <cell r="I16">
-            <v>3.5690458277651401E-3</v>
+            <v>3.5690460000000002E-3</v>
           </cell>
           <cell r="J16">
-            <v>2.6070257478266301E-2</v>
+            <v>2.6070256999999999E-2</v>
           </cell>
           <cell r="K16">
-            <v>4.6960126052209401E-2</v>
+            <v>4.6960125999999998E-2</v>
           </cell>
           <cell r="L16">
-            <v>3.99579014821679E-2</v>
+            <v>3.9957900999999997E-2</v>
           </cell>
           <cell r="M16">
-            <v>2.8543038434162199E-2</v>
+            <v>2.8543038E-2</v>
           </cell>
           <cell r="N16">
             <v>0</v>
           </cell>
           <cell r="O16">
-            <v>4.6081248517122197E-3</v>
+            <v>4.6081250000000002E-3</v>
           </cell>
           <cell r="P16">
             <v>0</v>
           </cell>
           <cell r="Q16">
-            <v>8.3031012169229507E-2</v>
+            <v>8.3031012000000001E-2</v>
           </cell>
           <cell r="R16">
-            <v>5.7822192570301002E-2</v>
+            <v>5.7822193000000001E-2</v>
           </cell>
           <cell r="S16">
-            <v>6.0306329581103497E-2</v>
+            <v>6.0306329999999998E-2</v>
           </cell>
           <cell r="T16">
-            <v>1.53424357521054E-2</v>
+            <v>1.5342435999999999E-2</v>
           </cell>
           <cell r="U16">
             <v>0</v>
           </cell>
           <cell r="V16">
-            <v>0.13144592996964199</v>
+            <v>0.13144592999999999</v>
           </cell>
           <cell r="W16">
-            <v>9.8629770303510805E-2</v>
+            <v>9.8629770000000005E-2</v>
           </cell>
           <cell r="X16">
-            <v>8.3731031839538894E-2</v>
+            <v>8.3731031999999997E-2</v>
           </cell>
           <cell r="Y16">
-            <v>7.8843466922448202E-2</v>
+            <v>7.8843467E-2</v>
           </cell>
           <cell r="Z16">
-            <v>0.128187553358249</v>
+            <v>0.12818755300000001</v>
           </cell>
         </row>
         <row r="17">
@@ -12007,76 +12014,76 @@
             <v>0</v>
           </cell>
           <cell r="C17">
-            <v>6.4233143796226799E-3</v>
+            <v>6.4233140000000003E-3</v>
           </cell>
           <cell r="D17">
-            <v>3.3814107915729301E-2</v>
+            <v>3.3814108000000002E-2</v>
           </cell>
           <cell r="E17">
-            <v>1.63095010407843E-2</v>
+            <v>1.6309501000000001E-2</v>
           </cell>
           <cell r="F17">
-            <v>5.3663894952119803E-2</v>
+            <v>5.3663895000000003E-2</v>
           </cell>
           <cell r="G17">
-            <v>3.7330613227929202E-2</v>
+            <v>3.7330612999999999E-2</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>1.6990539335780201E-2</v>
+            <v>1.6990538999999999E-2</v>
           </cell>
           <cell r="J17">
-            <v>8.3374064078316299E-3</v>
+            <v>8.3374060000000003E-3</v>
           </cell>
           <cell r="K17">
-            <v>3.5836983921222101E-2</v>
+            <v>3.5836984000000002E-2</v>
           </cell>
           <cell r="L17">
-            <v>6.9167888589016097E-2</v>
+            <v>6.9167888999999996E-2</v>
           </cell>
           <cell r="M17">
-            <v>1.5490332393237299E-2</v>
+            <v>1.5490332000000001E-2</v>
           </cell>
           <cell r="N17">
             <v>0</v>
           </cell>
           <cell r="O17">
-            <v>6.4309039594331796E-3</v>
+            <v>6.4309040000000003E-3</v>
           </cell>
           <cell r="P17">
             <v>0</v>
           </cell>
           <cell r="Q17">
-            <v>2.37164249638483E-2</v>
+            <v>2.3716424999999999E-2</v>
           </cell>
           <cell r="R17">
-            <v>7.0856317110859393E-2</v>
+            <v>7.0856317000000002E-2</v>
           </cell>
           <cell r="S17">
-            <v>8.6578384674310796E-2</v>
+            <v>8.6578384999999994E-2</v>
           </cell>
           <cell r="T17">
-            <v>1.02221520607733E-2</v>
+            <v>1.0222152E-2</v>
           </cell>
           <cell r="U17">
             <v>0</v>
           </cell>
           <cell r="V17">
-            <v>9.4064240227404006E-2</v>
+            <v>9.4064239999999993E-2</v>
           </cell>
           <cell r="W17">
-            <v>0.115176427372274</v>
+            <v>0.115176427</v>
           </cell>
           <cell r="X17">
-            <v>0.138317056214499</v>
+            <v>0.13831705599999999</v>
           </cell>
           <cell r="Y17">
-            <v>7.8805137032393294E-2</v>
+            <v>7.8805136999999997E-2</v>
           </cell>
           <cell r="Z17">
-            <v>8.2468374220929605E-2</v>
+            <v>8.2468373999999997E-2</v>
           </cell>
         </row>
         <row r="18">
@@ -12084,79 +12091,79 @@
             <v>17</v>
           </cell>
           <cell r="B18">
-            <v>6.3784891365126998E-3</v>
+            <v>6.3784890000000002E-3</v>
           </cell>
           <cell r="C18">
-            <v>1.1086713952516E-2</v>
+            <v>1.1086713999999999E-2</v>
           </cell>
           <cell r="D18">
-            <v>3.4763852016785099E-2</v>
+            <v>3.4763851999999998E-2</v>
           </cell>
           <cell r="E18">
-            <v>4.1414054274617203E-2</v>
+            <v>4.1414053999999999E-2</v>
           </cell>
           <cell r="F18">
-            <v>3.8775320010679598E-2</v>
+            <v>3.8775320000000002E-2</v>
           </cell>
           <cell r="G18">
-            <v>2.87619201144532E-2</v>
+            <v>2.876192E-2</v>
           </cell>
           <cell r="H18">
             <v>0</v>
           </cell>
           <cell r="I18">
-            <v>3.58138673813277E-3</v>
+            <v>3.5813870000000001E-3</v>
           </cell>
           <cell r="J18">
-            <v>7.0887843876096196E-3</v>
+            <v>7.0887839999999999E-3</v>
           </cell>
           <cell r="K18">
-            <v>3.7228475786992003E-2</v>
+            <v>3.7228476000000003E-2</v>
           </cell>
           <cell r="L18">
-            <v>6.2802253298339106E-2</v>
+            <v>6.2802253000000002E-2</v>
           </cell>
           <cell r="M18">
-            <v>2.1811668488582299E-2</v>
+            <v>2.1811667999999999E-2</v>
           </cell>
           <cell r="N18">
             <v>0</v>
           </cell>
           <cell r="O18">
-            <v>1.20334594401261E-3</v>
+            <v>1.2033460000000001E-3</v>
           </cell>
           <cell r="P18">
             <v>0</v>
           </cell>
           <cell r="Q18">
-            <v>2.7079691600884501E-2</v>
+            <v>2.7079691999999999E-2</v>
           </cell>
           <cell r="R18">
-            <v>9.00582593232548E-2</v>
+            <v>9.0058259000000002E-2</v>
           </cell>
           <cell r="S18">
-            <v>4.6422328458659297E-2</v>
+            <v>4.6422327999999999E-2</v>
           </cell>
           <cell r="T18">
-            <v>2.5505770519220702E-2</v>
+            <v>2.5505771E-2</v>
           </cell>
           <cell r="U18">
             <v>0</v>
           </cell>
           <cell r="V18">
-            <v>9.1292775138658702E-2</v>
+            <v>9.1292775000000007E-2</v>
           </cell>
           <cell r="W18">
-            <v>0.113671168561626</v>
+            <v>0.113671169</v>
           </cell>
           <cell r="X18">
-            <v>0.108318451556352</v>
+            <v>0.108318452</v>
           </cell>
           <cell r="Y18">
-            <v>8.7803008931584894E-2</v>
+            <v>8.7803009000000001E-2</v>
           </cell>
           <cell r="Z18">
-            <v>0.11495228176052399</v>
+            <v>0.114952282</v>
           </cell>
         </row>
         <row r="19">
@@ -12167,37 +12174,37 @@
             <v>0</v>
           </cell>
           <cell r="C19">
-            <v>5.9670510291354797E-3</v>
+            <v>5.9670510000000001E-3</v>
           </cell>
           <cell r="D19">
-            <v>1.8335120434979899E-2</v>
+            <v>1.833512E-2</v>
           </cell>
           <cell r="E19">
-            <v>1.46855755883723E-2</v>
+            <v>1.4685576000000001E-2</v>
           </cell>
           <cell r="F19">
-            <v>5.28415518913442E-2</v>
+            <v>5.2841552E-2</v>
           </cell>
           <cell r="G19">
-            <v>8.7818114640913093E-3</v>
+            <v>8.7818110000000005E-3</v>
           </cell>
           <cell r="H19">
             <v>0</v>
           </cell>
           <cell r="I19">
-            <v>8.1368877670029306E-3</v>
+            <v>8.1368880000000001E-3</v>
           </cell>
           <cell r="J19">
-            <v>1.7792661250513001E-3</v>
+            <v>1.7792660000000001E-3</v>
           </cell>
           <cell r="K19">
-            <v>4.5773911450168098E-2</v>
+            <v>4.5773911E-2</v>
           </cell>
           <cell r="L19">
-            <v>5.5204263005910997E-2</v>
+            <v>5.5204263000000003E-2</v>
           </cell>
           <cell r="M19">
-            <v>1.0033686715355299E-2</v>
+            <v>1.0033686999999999E-2</v>
           </cell>
           <cell r="N19">
             <v>0</v>
@@ -12209,34 +12216,34 @@
             <v>0</v>
           </cell>
           <cell r="Q19">
-            <v>6.6359032035831197E-2</v>
+            <v>6.6359031999999998E-2</v>
           </cell>
           <cell r="R19">
-            <v>4.5420710247837497E-2</v>
+            <v>4.5420710000000003E-2</v>
           </cell>
           <cell r="S19">
-            <v>4.2913343350746203E-2</v>
+            <v>4.2913343E-2</v>
           </cell>
           <cell r="T19">
-            <v>2.40351609988722E-2</v>
+            <v>2.4035160999999999E-2</v>
           </cell>
           <cell r="U19">
             <v>0</v>
           </cell>
           <cell r="V19">
-            <v>0.10860334239240101</v>
+            <v>0.10860334200000001</v>
           </cell>
           <cell r="W19">
-            <v>0.188348458903593</v>
+            <v>0.188348459</v>
           </cell>
           <cell r="X19">
-            <v>0.14619998300294501</v>
+            <v>0.14619998300000001</v>
           </cell>
           <cell r="Y19">
-            <v>6.9802442392341402E-2</v>
+            <v>6.9802442000000006E-2</v>
           </cell>
           <cell r="Z19">
-            <v>8.6778401204018293E-2</v>
+            <v>8.6778401000000005E-2</v>
           </cell>
         </row>
         <row r="20">
@@ -12247,76 +12254,76 @@
             <v>0</v>
           </cell>
           <cell r="C20">
-            <v>1.39604910175571E-2</v>
+            <v>1.3960491E-2</v>
           </cell>
           <cell r="D20">
-            <v>2.04449792156579E-2</v>
+            <v>2.0444978999999999E-2</v>
           </cell>
           <cell r="E20">
-            <v>2.49686557658143E-2</v>
+            <v>2.4968655999999999E-2</v>
           </cell>
           <cell r="F20">
-            <v>2.9270592007416298E-2</v>
+            <v>2.9270592000000002E-2</v>
           </cell>
           <cell r="G20">
-            <v>1.20384512506763E-2</v>
+            <v>1.2038451E-2</v>
           </cell>
           <cell r="H20">
             <v>0</v>
           </cell>
           <cell r="I20">
-            <v>1.2727196688445699E-2</v>
+            <v>1.2727197000000001E-2</v>
           </cell>
           <cell r="J20">
-            <v>1.7538395053230699E-2</v>
+            <v>1.7538394999999998E-2</v>
           </cell>
           <cell r="K20">
-            <v>3.9665812523578897E-2</v>
+            <v>3.9665813000000001E-2</v>
           </cell>
           <cell r="L20">
-            <v>4.89623511965699E-2</v>
+            <v>4.8962351000000001E-2</v>
           </cell>
           <cell r="M20">
-            <v>2.2478542595485498E-2</v>
+            <v>2.2478543E-2</v>
           </cell>
           <cell r="N20">
             <v>0</v>
           </cell>
           <cell r="O20">
-            <v>1.34956640839075E-2</v>
+            <v>1.3495663999999999E-2</v>
           </cell>
           <cell r="P20">
             <v>0</v>
           </cell>
           <cell r="Q20">
-            <v>4.43964176524453E-2</v>
+            <v>4.4396418E-2</v>
           </cell>
           <cell r="R20">
-            <v>8.2600225312549194E-2</v>
+            <v>8.2600224999999999E-2</v>
           </cell>
           <cell r="S20">
-            <v>7.07778510619574E-2</v>
+            <v>7.0777851000000003E-2</v>
           </cell>
           <cell r="T20">
-            <v>3.0466857011916398E-2</v>
+            <v>3.0466857E-2</v>
           </cell>
           <cell r="U20">
             <v>0</v>
           </cell>
           <cell r="V20">
-            <v>9.1188850426795601E-2</v>
+            <v>9.1188850000000002E-2</v>
           </cell>
           <cell r="W20">
-            <v>9.4416064976444905E-2</v>
+            <v>9.4416064999999993E-2</v>
           </cell>
           <cell r="X20">
-            <v>0.146667055837607</v>
+            <v>0.14666705599999999</v>
           </cell>
           <cell r="Y20">
-            <v>8.7347820366825493E-2</v>
+            <v>8.7347820000000007E-2</v>
           </cell>
           <cell r="Z20">
-            <v>9.6587725955116902E-2</v>
+            <v>9.6587725999999999E-2</v>
           </cell>
         </row>
         <row r="21">
@@ -12327,76 +12334,76 @@
             <v>0</v>
           </cell>
           <cell r="C21">
-            <v>1.2264229451373201E-2</v>
+            <v>1.2264229E-2</v>
           </cell>
           <cell r="D21">
-            <v>3.04630202510302E-2</v>
+            <v>3.046302E-2</v>
           </cell>
           <cell r="E21">
-            <v>2.2164331122616902E-2</v>
+            <v>2.2164330999999999E-2</v>
           </cell>
           <cell r="F21">
-            <v>4.9659226454302798E-2</v>
+            <v>4.9659226000000001E-2</v>
           </cell>
           <cell r="G21">
-            <v>4.8840549820718497E-2</v>
+            <v>4.8840550000000003E-2</v>
           </cell>
           <cell r="H21">
-            <v>2.70131127360821E-2</v>
+            <v>2.7013112999999998E-2</v>
           </cell>
           <cell r="I21">
-            <v>8.8030653337240906E-3</v>
+            <v>8.8030650000000005E-3</v>
           </cell>
           <cell r="J21">
             <v>0</v>
           </cell>
           <cell r="K21">
-            <v>5.0904849947475801E-2</v>
+            <v>5.0904850000000001E-2</v>
           </cell>
           <cell r="L21">
-            <v>5.8144373166028003E-2</v>
+            <v>5.8144372999999999E-2</v>
           </cell>
           <cell r="M21">
-            <v>3.1680180620230702E-2</v>
+            <v>3.1680181000000002E-2</v>
           </cell>
           <cell r="N21">
-            <v>4.6763143792244899E-4</v>
+            <v>4.6763099999999998E-4</v>
           </cell>
           <cell r="O21">
-            <v>1.0643278662426099E-2</v>
+            <v>1.0643279E-2</v>
           </cell>
           <cell r="P21">
-            <v>4.6763143792244899E-4</v>
+            <v>4.6763099999999998E-4</v>
           </cell>
           <cell r="Q21">
-            <v>2.6195963784292901E-2</v>
+            <v>2.6195963999999999E-2</v>
           </cell>
           <cell r="R21">
-            <v>3.79611237144859E-2</v>
+            <v>3.7961123999999999E-2</v>
           </cell>
           <cell r="S21">
-            <v>4.6987793420435298E-2</v>
+            <v>4.6987793E-2</v>
           </cell>
           <cell r="T21">
-            <v>8.7521694086544699E-2</v>
+            <v>8.7521693999999997E-2</v>
           </cell>
           <cell r="U21">
             <v>0</v>
           </cell>
           <cell r="V21">
-            <v>0.11290670005053401</v>
+            <v>0.1129067</v>
           </cell>
           <cell r="W21">
-            <v>5.0170356621234202E-2</v>
+            <v>5.0170356999999999E-2</v>
           </cell>
           <cell r="X21">
-            <v>7.7097919176788501E-2</v>
+            <v>7.7097919000000001E-2</v>
           </cell>
           <cell r="Y21">
-            <v>8.0129724305698702E-2</v>
+            <v>8.0129723999999999E-2</v>
           </cell>
           <cell r="Z21">
-            <v>0.129513244398131</v>
+            <v>0.129513244</v>
           </cell>
         </row>
         <row r="22">
@@ -12407,76 +12414,76 @@
             <v>0</v>
           </cell>
           <cell r="C22">
-            <v>4.4442027778345298E-3</v>
+            <v>4.4442029999999999E-3</v>
           </cell>
           <cell r="D22">
-            <v>6.3934594856126195E-2</v>
+            <v>6.3934594999999997E-2</v>
           </cell>
           <cell r="E22">
-            <v>1.22025090766399E-2</v>
+            <v>1.2202509E-2</v>
           </cell>
           <cell r="F22">
-            <v>3.6290628419000402E-2</v>
+            <v>3.6290627999999998E-2</v>
           </cell>
           <cell r="G22">
-            <v>9.9263790379921796E-3</v>
+            <v>9.9263790000000008E-3</v>
           </cell>
           <cell r="H22">
-            <v>1.06138589720633E-2</v>
+            <v>1.0613859E-2</v>
           </cell>
           <cell r="I22">
-            <v>6.3085375310361598E-3</v>
+            <v>6.3085379999999998E-3</v>
           </cell>
           <cell r="J22">
             <v>0</v>
           </cell>
           <cell r="K22">
-            <v>4.2595356237555601E-2</v>
+            <v>4.2595356000000001E-2</v>
           </cell>
           <cell r="L22">
-            <v>7.3139206547718202E-2</v>
+            <v>7.3139206999999998E-2</v>
           </cell>
           <cell r="M22">
-            <v>3.3950079605673901E-2</v>
+            <v>3.3950080000000001E-2</v>
           </cell>
           <cell r="N22">
-            <v>5.8046164710494699E-4</v>
+            <v>5.8046200000000001E-4</v>
           </cell>
           <cell r="O22">
-            <v>8.0111326725444704E-3</v>
+            <v>8.0111330000000001E-3</v>
           </cell>
           <cell r="P22">
-            <v>5.8046164710494699E-4</v>
+            <v>5.8046200000000001E-4</v>
           </cell>
           <cell r="Q22">
-            <v>2.4614898677233099E-2</v>
+            <v>2.4614898999999999E-2</v>
           </cell>
           <cell r="R22">
-            <v>7.2815727324331503E-2</v>
+            <v>7.2815726999999997E-2</v>
           </cell>
           <cell r="S22">
-            <v>5.23354057014771E-2</v>
+            <v>5.2335406000000001E-2</v>
           </cell>
           <cell r="T22">
-            <v>3.6136854569767403E-2</v>
+            <v>3.6136855000000002E-2</v>
           </cell>
           <cell r="U22">
             <v>0</v>
           </cell>
           <cell r="V22">
-            <v>0.119707400227959</v>
+            <v>0.11970740000000001</v>
           </cell>
           <cell r="W22">
-            <v>0.113243703497697</v>
+            <v>0.113243703</v>
           </cell>
           <cell r="X22">
-            <v>0.102412690914216</v>
+            <v>0.102412691</v>
           </cell>
           <cell r="Y22">
-            <v>8.1217875032425793E-2</v>
+            <v>8.1217874999999995E-2</v>
           </cell>
           <cell r="Z22">
-            <v>9.4938035026496503E-2</v>
+            <v>9.4938035000000004E-2</v>
           </cell>
         </row>
         <row r="23">
@@ -12487,76 +12494,76 @@
             <v>0</v>
           </cell>
           <cell r="C23">
-            <v>2.0631498319124999E-2</v>
+            <v>2.0631498000000002E-2</v>
           </cell>
           <cell r="D23">
-            <v>4.3826153562461799E-2</v>
+            <v>4.3826153999999999E-2</v>
           </cell>
           <cell r="E23">
-            <v>5.2991531794777197E-2</v>
+            <v>5.2991532000000001E-2</v>
           </cell>
           <cell r="F23">
-            <v>4.6685768592462297E-2</v>
+            <v>4.6685769000000002E-2</v>
           </cell>
           <cell r="G23">
-            <v>8.1086256542645899E-3</v>
+            <v>8.1086260000000007E-3</v>
           </cell>
           <cell r="H23">
             <v>0</v>
           </cell>
           <cell r="I23">
-            <v>9.2448119831486895E-3</v>
+            <v>9.2448119999999998E-3</v>
           </cell>
           <cell r="J23">
             <v>0</v>
           </cell>
           <cell r="K23">
-            <v>1.08831330940864E-2</v>
+            <v>1.0883133E-2</v>
           </cell>
           <cell r="L23">
-            <v>6.3518631469949904E-2</v>
+            <v>6.3518631000000006E-2</v>
           </cell>
           <cell r="M23">
-            <v>1.45363764025021E-2</v>
+            <v>1.4536376E-2</v>
           </cell>
           <cell r="N23">
             <v>0</v>
           </cell>
           <cell r="O23">
-            <v>1.86867898835444E-2</v>
+            <v>1.8686790000000002E-2</v>
           </cell>
           <cell r="P23">
             <v>0</v>
           </cell>
           <cell r="Q23">
-            <v>7.8136569313039902E-2</v>
+            <v>7.8136569000000003E-2</v>
           </cell>
           <cell r="R23">
-            <v>4.8229052894367297E-2</v>
+            <v>4.8229053000000001E-2</v>
           </cell>
           <cell r="S23">
-            <v>4.4089277862097299E-2</v>
+            <v>4.4089278000000003E-2</v>
           </cell>
           <cell r="T23">
-            <v>4.2084284883473502E-2</v>
+            <v>4.2084284999999999E-2</v>
           </cell>
           <cell r="U23">
             <v>0</v>
           </cell>
           <cell r="V23">
-            <v>9.9136157959687304E-2</v>
+            <v>9.9136158000000002E-2</v>
           </cell>
           <cell r="W23">
-            <v>0.14097221237180599</v>
+            <v>0.14097221200000001</v>
           </cell>
           <cell r="X23">
-            <v>7.9243677215279598E-2</v>
+            <v>7.9243676999999998E-2</v>
           </cell>
           <cell r="Y23">
-            <v>8.7994155945474398E-2</v>
+            <v>8.7994156000000004E-2</v>
           </cell>
           <cell r="Z23">
-            <v>9.1001290798450998E-2</v>
+            <v>9.1001290999999998E-2</v>
           </cell>
         </row>
         <row r="24">
@@ -12567,76 +12574,76 @@
             <v>0</v>
           </cell>
           <cell r="C24">
-            <v>2.9855546919722999E-2</v>
+            <v>2.9855547E-2</v>
           </cell>
           <cell r="D24">
-            <v>2.1929720063800701E-2</v>
+            <v>2.192972E-2</v>
           </cell>
           <cell r="E24">
-            <v>2.1483153794589802E-2</v>
+            <v>2.1483154000000001E-2</v>
           </cell>
           <cell r="F24">
-            <v>5.8317304813192299E-2</v>
+            <v>5.8317305E-2</v>
           </cell>
           <cell r="G24">
-            <v>2.8248938640442301E-2</v>
+            <v>2.8248939000000001E-2</v>
           </cell>
           <cell r="H24">
             <v>0</v>
           </cell>
           <cell r="I24">
-            <v>1.94901868108729E-2</v>
+            <v>1.9490186999999999E-2</v>
           </cell>
           <cell r="J24">
             <v>0</v>
           </cell>
           <cell r="K24">
-            <v>2.5996467393579099E-2</v>
+            <v>2.5996466999999999E-2</v>
           </cell>
           <cell r="L24">
-            <v>4.1007146992100903E-2</v>
+            <v>4.1007147000000001E-2</v>
           </cell>
           <cell r="M24">
-            <v>2.6700928098001099E-2</v>
+            <v>2.6700927999999999E-2</v>
           </cell>
           <cell r="N24">
             <v>0</v>
           </cell>
           <cell r="O24">
-            <v>1.7397088529589599E-2</v>
+            <v>1.7397089000000001E-2</v>
           </cell>
           <cell r="P24">
             <v>0</v>
           </cell>
           <cell r="Q24">
-            <v>5.1067605690033401E-2</v>
+            <v>5.1067606000000001E-2</v>
           </cell>
           <cell r="R24">
-            <v>4.7362103748902901E-2</v>
+            <v>4.7362104000000002E-2</v>
           </cell>
           <cell r="S24">
-            <v>3.8243072427446602E-2</v>
+            <v>3.8243072000000003E-2</v>
           </cell>
           <cell r="T24">
-            <v>3.8482292858610101E-2</v>
+            <v>3.8482293000000001E-2</v>
           </cell>
           <cell r="U24">
             <v>0</v>
           </cell>
           <cell r="V24">
-            <v>0.116391847573763</v>
+            <v>0.11639184800000001</v>
           </cell>
           <cell r="W24">
-            <v>0.132313045852407</v>
+            <v>0.13231304599999999</v>
           </cell>
           <cell r="X24">
-            <v>9.3500094335916994E-2</v>
+            <v>9.3500094000000006E-2</v>
           </cell>
           <cell r="Y24">
-            <v>8.8788449935317093E-2</v>
+            <v>8.8788450000000005E-2</v>
           </cell>
           <cell r="Z24">
-            <v>0.103425005521709</v>
+            <v>0.103425006</v>
           </cell>
         </row>
         <row r="25">
@@ -12647,37 +12654,37 @@
             <v>0</v>
           </cell>
           <cell r="C25">
-            <v>1.5122388139513099E-2</v>
+            <v>1.5122388E-2</v>
           </cell>
           <cell r="D25">
             <v>0</v>
           </cell>
           <cell r="E25">
-            <v>2.17911046348408E-2</v>
+            <v>2.1791105000000002E-2</v>
           </cell>
           <cell r="F25">
-            <v>7.7380318971164194E-2</v>
+            <v>7.7380319000000003E-2</v>
           </cell>
           <cell r="G25">
-            <v>1.5825568493242199E-2</v>
+            <v>1.5825568000000002E-2</v>
           </cell>
           <cell r="H25">
             <v>0</v>
           </cell>
           <cell r="I25">
-            <v>3.19238533213908E-3</v>
+            <v>3.1923849999999998E-3</v>
           </cell>
           <cell r="J25">
             <v>0</v>
           </cell>
           <cell r="K25">
-            <v>3.8341242998275397E-2</v>
+            <v>3.8341242999999997E-2</v>
           </cell>
           <cell r="L25">
-            <v>5.96088392176784E-2</v>
+            <v>5.9608838999999997E-2</v>
           </cell>
           <cell r="M25">
-            <v>9.7402510594494802E-3</v>
+            <v>9.7402510000000001E-3</v>
           </cell>
           <cell r="N25">
             <v>0</v>
@@ -12689,34 +12696,34 @@
             <v>0</v>
           </cell>
           <cell r="Q25">
-            <v>7.8679732096306298E-2</v>
+            <v>7.8679732000000002E-2</v>
           </cell>
           <cell r="R25">
-            <v>3.3369249896394497E-2</v>
+            <v>3.3369250000000003E-2</v>
           </cell>
           <cell r="S25">
-            <v>0.143434888975041</v>
+            <v>0.14343488900000001</v>
           </cell>
           <cell r="T25">
-            <v>1.24920123524457E-2</v>
+            <v>1.2492012E-2</v>
           </cell>
           <cell r="U25">
             <v>0</v>
           </cell>
           <cell r="V25">
-            <v>0.113874042484927</v>
+            <v>0.11387404199999999</v>
           </cell>
           <cell r="W25">
-            <v>0.13081347004799199</v>
+            <v>0.13081346999999999</v>
           </cell>
           <cell r="X25">
-            <v>7.2336136251219804E-2</v>
+            <v>7.2336135999999995E-2</v>
           </cell>
           <cell r="Y25">
-            <v>7.8643904656230307E-2</v>
+            <v>7.8643905E-2</v>
           </cell>
           <cell r="Z25">
-            <v>9.5354464393139299E-2</v>
+            <v>9.5354464E-2</v>
           </cell>
         </row>
         <row r="26">
@@ -12727,76 +12734,76 @@
             <v>0</v>
           </cell>
           <cell r="C26">
-            <v>1.7673424780121499E-2</v>
+            <v>1.7673425E-2</v>
           </cell>
           <cell r="D26">
             <v>0</v>
           </cell>
           <cell r="E26">
-            <v>1.40813139050282E-2</v>
+            <v>1.4081313999999999E-2</v>
           </cell>
           <cell r="F26">
-            <v>5.4030611603983598E-2</v>
+            <v>5.4030611999999999E-2</v>
           </cell>
           <cell r="G26">
-            <v>1.7587285901518101E-2</v>
+            <v>1.7587286000000001E-2</v>
           </cell>
           <cell r="H26">
             <v>0</v>
           </cell>
           <cell r="I26">
-            <v>3.16530469534652E-2</v>
+            <v>3.1653046999999997E-2</v>
           </cell>
           <cell r="J26">
             <v>0</v>
           </cell>
           <cell r="K26">
-            <v>2.2967376694288898E-2</v>
+            <v>2.2967377000000001E-2</v>
           </cell>
           <cell r="L26">
-            <v>9.7671917349745896E-2</v>
+            <v>9.7671916999999997E-2</v>
           </cell>
           <cell r="M26">
-            <v>3.9414518827625901E-2</v>
+            <v>3.9414519000000002E-2</v>
           </cell>
           <cell r="N26">
             <v>0</v>
           </cell>
           <cell r="O26">
-            <v>2.0371844789704399E-2</v>
+            <v>2.0371845E-2</v>
           </cell>
           <cell r="P26">
             <v>0</v>
           </cell>
           <cell r="Q26">
-            <v>3.1937185615524999E-2</v>
+            <v>3.1937185999999999E-2</v>
           </cell>
           <cell r="R26">
-            <v>2.6191004588689799E-2</v>
+            <v>2.6191005E-2</v>
           </cell>
           <cell r="S26">
-            <v>7.7242048454315496E-2</v>
+            <v>7.7242047999999994E-2</v>
           </cell>
           <cell r="T26">
-            <v>3.2512042992871401E-2</v>
+            <v>3.2512042999999997E-2</v>
           </cell>
           <cell r="U26">
             <v>0</v>
           </cell>
           <cell r="V26">
-            <v>0.118255520216017</v>
+            <v>0.11825552</v>
           </cell>
           <cell r="W26">
-            <v>0.100071842217501</v>
+            <v>0.10007184199999999</v>
           </cell>
           <cell r="X26">
-            <v>0.100037147391397</v>
+            <v>0.10003714700000001</v>
           </cell>
           <cell r="Y26">
-            <v>9.0855580393594801E-2</v>
+            <v>9.0855580000000005E-2</v>
           </cell>
           <cell r="Z26">
-            <v>0.107446287324604</v>
+            <v>0.107446287</v>
           </cell>
         </row>
         <row r="27">
@@ -12807,76 +12814,76 @@
             <v>0</v>
           </cell>
           <cell r="C27">
-            <v>2.19690773085011E-2</v>
+            <v>2.1969077E-2</v>
           </cell>
           <cell r="D27">
             <v>0</v>
           </cell>
           <cell r="E27">
-            <v>8.35455018357412E-3</v>
+            <v>8.3545500000000005E-3</v>
           </cell>
           <cell r="F27">
-            <v>6.4591683821815599E-2</v>
+            <v>6.4591683999999996E-2</v>
           </cell>
           <cell r="G27">
-            <v>2.66725273322953E-2</v>
+            <v>2.6672527000000001E-2</v>
           </cell>
           <cell r="H27">
             <v>0</v>
           </cell>
           <cell r="I27">
-            <v>4.3356814397386796E-3</v>
+            <v>4.3356810000000001E-3</v>
           </cell>
           <cell r="J27">
             <v>0</v>
           </cell>
           <cell r="K27">
-            <v>2.91250563837979E-2</v>
+            <v>2.9125056E-2</v>
           </cell>
           <cell r="L27">
-            <v>5.59384878242013E-2</v>
+            <v>5.5938488000000001E-2</v>
           </cell>
           <cell r="M27">
-            <v>2.2506551154837601E-2</v>
+            <v>2.2506551E-2</v>
           </cell>
           <cell r="N27">
             <v>0</v>
           </cell>
           <cell r="O27">
-            <v>2.9275708574856799E-2</v>
+            <v>2.9275709E-2</v>
           </cell>
           <cell r="P27">
             <v>0</v>
           </cell>
           <cell r="Q27">
-            <v>4.0463406139697101E-2</v>
+            <v>4.0463406E-2</v>
           </cell>
           <cell r="R27">
-            <v>2.8003140655088798E-2</v>
+            <v>2.8003140999999999E-2</v>
           </cell>
           <cell r="S27">
-            <v>8.2063793227209206E-2</v>
+            <v>8.2063792999999996E-2</v>
           </cell>
           <cell r="T27">
-            <v>2.0939325273145699E-2</v>
+            <v>2.0939325000000002E-2</v>
           </cell>
           <cell r="U27">
             <v>0</v>
           </cell>
           <cell r="V27">
-            <v>0.11014624782994301</v>
+            <v>0.110146248</v>
           </cell>
           <cell r="W27">
-            <v>0.12848150567116801</v>
+            <v>0.128481506</v>
           </cell>
           <cell r="X27">
-            <v>0.10866542541077</v>
+            <v>0.108665425</v>
           </cell>
           <cell r="Y27">
-            <v>0.109499772692429</v>
+            <v>0.10949977299999999</v>
           </cell>
           <cell r="Z27">
-            <v>0.108968059076927</v>
+            <v>0.10896805900000001</v>
           </cell>
         </row>
         <row r="28">
@@ -12890,16 +12897,16 @@
             <v>0</v>
           </cell>
           <cell r="D28">
-            <v>2.5507284291764E-2</v>
+            <v>2.5507284000000002E-2</v>
           </cell>
           <cell r="E28">
-            <v>2.1828349057375001E-2</v>
+            <v>2.1828349E-2</v>
           </cell>
           <cell r="F28">
             <v>0</v>
           </cell>
           <cell r="G28">
-            <v>2.16064450273642E-2</v>
+            <v>2.1606444999999998E-2</v>
           </cell>
           <cell r="H28">
             <v>0</v>
@@ -12911,10 +12918,10 @@
             <v>0</v>
           </cell>
           <cell r="K28">
-            <v>6.0322858684506202E-2</v>
+            <v>6.0322859E-2</v>
           </cell>
           <cell r="L28">
-            <v>9.0279902735959899E-2</v>
+            <v>9.0279902999999995E-2</v>
           </cell>
           <cell r="M28">
             <v>0</v>
@@ -12929,34 +12936,34 @@
             <v>0</v>
           </cell>
           <cell r="Q28">
-            <v>5.9038151142338499E-2</v>
+            <v>5.9038150999999997E-2</v>
           </cell>
           <cell r="R28">
-            <v>6.4055518052476806E-2</v>
+            <v>6.4055518000000006E-2</v>
           </cell>
           <cell r="S28">
-            <v>8.3564386038265603E-2</v>
+            <v>8.3564386000000004E-2</v>
           </cell>
           <cell r="T28">
-            <v>2.0679119765108701E-2</v>
+            <v>2.0679119999999999E-2</v>
           </cell>
           <cell r="U28">
             <v>0</v>
           </cell>
           <cell r="V28">
-            <v>7.6732077745828797E-2</v>
+            <v>7.6732077999999995E-2</v>
           </cell>
           <cell r="W28">
-            <v>0.151712281570519</v>
+            <v>0.151712282</v>
           </cell>
           <cell r="X28">
-            <v>0.15381920193967399</v>
+            <v>0.15381920199999999</v>
           </cell>
           <cell r="Y28">
-            <v>8.2384790931366206E-2</v>
+            <v>8.2384790999999999E-2</v>
           </cell>
           <cell r="Z28">
-            <v>8.8469633017451005E-2</v>
+            <v>8.8469633000000006E-2</v>
           </cell>
         </row>
         <row r="29">
@@ -12973,10 +12980,10 @@
             <v>0</v>
           </cell>
           <cell r="E29">
-            <v>3.6327261851874397E-2</v>
+            <v>3.6327261999999999E-2</v>
           </cell>
           <cell r="F29">
-            <v>7.7847658371007794E-2</v>
+            <v>7.7847658E-2</v>
           </cell>
           <cell r="G29">
             <v>0</v>
@@ -12985,19 +12992,19 @@
             <v>0</v>
           </cell>
           <cell r="I29">
-            <v>0.142161517086385</v>
+            <v>0.14216151699999999</v>
           </cell>
           <cell r="J29">
             <v>0</v>
           </cell>
           <cell r="K29">
-            <v>5.7615194092863697E-2</v>
+            <v>5.7615194000000002E-2</v>
           </cell>
           <cell r="L29">
-            <v>4.45169383008562E-2</v>
+            <v>4.4516937999999999E-2</v>
           </cell>
           <cell r="M29">
-            <v>1.66958481055293E-2</v>
+            <v>1.6695847999999999E-2</v>
           </cell>
           <cell r="N29">
             <v>0</v>
@@ -13009,34 +13016,34 @@
             <v>0</v>
           </cell>
           <cell r="Q29">
-            <v>2.6694483401423299E-2</v>
+            <v>2.6694483000000001E-2</v>
           </cell>
           <cell r="R29">
-            <v>2.6257487724922101E-2</v>
+            <v>2.6257487999999999E-2</v>
           </cell>
           <cell r="S29">
-            <v>7.8123502817968704E-2</v>
+            <v>7.8123502999999997E-2</v>
           </cell>
           <cell r="T29">
-            <v>2.7421841653672899E-2</v>
+            <v>2.7421841999999998E-2</v>
           </cell>
           <cell r="U29">
             <v>0</v>
           </cell>
           <cell r="V29">
-            <v>9.5841427190132195E-2</v>
+            <v>9.5841427000000007E-2</v>
           </cell>
           <cell r="W29">
-            <v>8.2692357947368803E-2</v>
+            <v>8.2692357999999994E-2</v>
           </cell>
           <cell r="X29">
-            <v>5.0730697421870599E-2</v>
+            <v>5.0730696999999998E-2</v>
           </cell>
           <cell r="Y29">
-            <v>0.100552559981649</v>
+            <v>0.10055256</v>
           </cell>
           <cell r="Z29">
-            <v>0.13652122405247399</v>
+            <v>0.136521224</v>
           </cell>
         </row>
       </sheetData>
@@ -38752,6 +38759,4680 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="resultados_integracion_partido_"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Distrito</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>AH</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>AMA</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>DEM</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>EVO</v>
+          </cell>
+          <cell r="F1" t="str">
+            <v>FA</v>
+          </cell>
+          <cell r="G1" t="str">
+            <v>FREVS</v>
+          </cell>
+          <cell r="H1" t="str">
+            <v>IGU</v>
+          </cell>
+          <cell r="I1" t="str">
+            <v>IND</v>
+          </cell>
+          <cell r="J1" t="str">
+            <v>PAVP</v>
+          </cell>
+          <cell r="K1" t="str">
+            <v>PCCH</v>
+          </cell>
+          <cell r="L1" t="str">
+            <v>PDC</v>
+          </cell>
+          <cell r="M1" t="str">
+            <v>PDG</v>
+          </cell>
+          <cell r="N1" t="str">
+            <v>PH</v>
+          </cell>
+          <cell r="O1" t="str">
+            <v>PL</v>
+          </cell>
+          <cell r="P1" t="str">
+            <v>POP</v>
+          </cell>
+          <cell r="Q1" t="str">
+            <v>PPD</v>
+          </cell>
+          <cell r="R1" t="str">
+            <v>PR</v>
+          </cell>
+          <cell r="S1" t="str">
+            <v>PS</v>
+          </cell>
+          <cell r="T1" t="str">
+            <v>PSC</v>
+          </cell>
+          <cell r="U1" t="str">
+            <v>PTR</v>
+          </cell>
+          <cell r="V1" t="str">
+            <v>REP</v>
+          </cell>
+          <cell r="W1" t="str">
+            <v>RN</v>
+          </cell>
+          <cell r="X1" t="str">
+            <v>UDI</v>
+          </cell>
+          <cell r="Y1" t="str">
+            <v>Votos Blancos</v>
+          </cell>
+          <cell r="Z1" t="str">
+            <v>Votos Nulos</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+          <cell r="B2">
+            <v>0</v>
+          </cell>
+          <cell r="C2">
+            <v>0</v>
+          </cell>
+          <cell r="D2">
+            <v>0</v>
+          </cell>
+          <cell r="E2">
+            <v>0</v>
+          </cell>
+          <cell r="F2">
+            <v>0</v>
+          </cell>
+          <cell r="G2">
+            <v>0</v>
+          </cell>
+          <cell r="H2">
+            <v>0</v>
+          </cell>
+          <cell r="I2">
+            <v>0</v>
+          </cell>
+          <cell r="J2">
+            <v>0</v>
+          </cell>
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="L2">
+            <v>0</v>
+          </cell>
+          <cell r="M2">
+            <v>0</v>
+          </cell>
+          <cell r="N2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+          <cell r="P2">
+            <v>0</v>
+          </cell>
+          <cell r="Q2">
+            <v>0</v>
+          </cell>
+          <cell r="R2">
+            <v>0</v>
+          </cell>
+          <cell r="S2">
+            <v>1</v>
+          </cell>
+          <cell r="T2">
+            <v>0</v>
+          </cell>
+          <cell r="U2">
+            <v>0</v>
+          </cell>
+          <cell r="V2">
+            <v>1</v>
+          </cell>
+          <cell r="W2">
+            <v>1</v>
+          </cell>
+          <cell r="X2">
+            <v>0</v>
+          </cell>
+          <cell r="Y2">
+            <v>0</v>
+          </cell>
+          <cell r="Z2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+          <cell r="B3">
+            <v>0</v>
+          </cell>
+          <cell r="C3">
+            <v>0</v>
+          </cell>
+          <cell r="D3">
+            <v>0</v>
+          </cell>
+          <cell r="E3">
+            <v>0</v>
+          </cell>
+          <cell r="F3">
+            <v>0</v>
+          </cell>
+          <cell r="G3">
+            <v>0</v>
+          </cell>
+          <cell r="H3">
+            <v>0</v>
+          </cell>
+          <cell r="I3">
+            <v>0</v>
+          </cell>
+          <cell r="J3">
+            <v>0</v>
+          </cell>
+          <cell r="K3">
+            <v>0</v>
+          </cell>
+          <cell r="L3">
+            <v>1</v>
+          </cell>
+          <cell r="M3">
+            <v>0</v>
+          </cell>
+          <cell r="N3">
+            <v>0</v>
+          </cell>
+          <cell r="O3">
+            <v>0</v>
+          </cell>
+          <cell r="P3">
+            <v>0</v>
+          </cell>
+          <cell r="Q3">
+            <v>0</v>
+          </cell>
+          <cell r="R3">
+            <v>0</v>
+          </cell>
+          <cell r="S3">
+            <v>0</v>
+          </cell>
+          <cell r="T3">
+            <v>0</v>
+          </cell>
+          <cell r="U3">
+            <v>0</v>
+          </cell>
+          <cell r="V3">
+            <v>1</v>
+          </cell>
+          <cell r="W3">
+            <v>1</v>
+          </cell>
+          <cell r="X3">
+            <v>0</v>
+          </cell>
+          <cell r="Y3">
+            <v>0</v>
+          </cell>
+          <cell r="Z3">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+          <cell r="B4">
+            <v>0</v>
+          </cell>
+          <cell r="C4">
+            <v>0</v>
+          </cell>
+          <cell r="D4">
+            <v>0</v>
+          </cell>
+          <cell r="E4">
+            <v>0</v>
+          </cell>
+          <cell r="F4">
+            <v>0</v>
+          </cell>
+          <cell r="G4">
+            <v>1</v>
+          </cell>
+          <cell r="H4">
+            <v>0</v>
+          </cell>
+          <cell r="I4">
+            <v>0</v>
+          </cell>
+          <cell r="J4">
+            <v>0</v>
+          </cell>
+          <cell r="K4">
+            <v>1</v>
+          </cell>
+          <cell r="L4">
+            <v>0</v>
+          </cell>
+          <cell r="M4">
+            <v>0</v>
+          </cell>
+          <cell r="N4">
+            <v>0</v>
+          </cell>
+          <cell r="O4">
+            <v>0</v>
+          </cell>
+          <cell r="P4">
+            <v>0</v>
+          </cell>
+          <cell r="Q4">
+            <v>0</v>
+          </cell>
+          <cell r="R4">
+            <v>1</v>
+          </cell>
+          <cell r="S4">
+            <v>0</v>
+          </cell>
+          <cell r="T4">
+            <v>0</v>
+          </cell>
+          <cell r="U4">
+            <v>0</v>
+          </cell>
+          <cell r="V4">
+            <v>1</v>
+          </cell>
+          <cell r="W4">
+            <v>1</v>
+          </cell>
+          <cell r="X4">
+            <v>0</v>
+          </cell>
+          <cell r="Y4">
+            <v>0</v>
+          </cell>
+          <cell r="Z4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+          <cell r="B5">
+            <v>0</v>
+          </cell>
+          <cell r="C5">
+            <v>0</v>
+          </cell>
+          <cell r="D5">
+            <v>0</v>
+          </cell>
+          <cell r="E5">
+            <v>0</v>
+          </cell>
+          <cell r="F5">
+            <v>0</v>
+          </cell>
+          <cell r="G5">
+            <v>1</v>
+          </cell>
+          <cell r="H5">
+            <v>0</v>
+          </cell>
+          <cell r="I5">
+            <v>0</v>
+          </cell>
+          <cell r="J5">
+            <v>0</v>
+          </cell>
+          <cell r="K5">
+            <v>1</v>
+          </cell>
+          <cell r="L5">
+            <v>0</v>
+          </cell>
+          <cell r="M5">
+            <v>0</v>
+          </cell>
+          <cell r="N5">
+            <v>0</v>
+          </cell>
+          <cell r="O5">
+            <v>0</v>
+          </cell>
+          <cell r="P5">
+            <v>0</v>
+          </cell>
+          <cell r="Q5">
+            <v>0</v>
+          </cell>
+          <cell r="R5">
+            <v>0</v>
+          </cell>
+          <cell r="S5">
+            <v>1</v>
+          </cell>
+          <cell r="T5">
+            <v>0</v>
+          </cell>
+          <cell r="U5">
+            <v>0</v>
+          </cell>
+          <cell r="V5">
+            <v>1</v>
+          </cell>
+          <cell r="W5">
+            <v>1</v>
+          </cell>
+          <cell r="X5">
+            <v>0</v>
+          </cell>
+          <cell r="Y5">
+            <v>0</v>
+          </cell>
+          <cell r="Z5">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+          <cell r="B6">
+            <v>0</v>
+          </cell>
+          <cell r="C6">
+            <v>0</v>
+          </cell>
+          <cell r="D6">
+            <v>0</v>
+          </cell>
+          <cell r="E6">
+            <v>0</v>
+          </cell>
+          <cell r="F6">
+            <v>0</v>
+          </cell>
+          <cell r="G6">
+            <v>0</v>
+          </cell>
+          <cell r="H6">
+            <v>0</v>
+          </cell>
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+          <cell r="J6">
+            <v>0</v>
+          </cell>
+          <cell r="K6">
+            <v>1</v>
+          </cell>
+          <cell r="L6">
+            <v>1</v>
+          </cell>
+          <cell r="M6">
+            <v>0</v>
+          </cell>
+          <cell r="N6">
+            <v>0</v>
+          </cell>
+          <cell r="O6">
+            <v>0</v>
+          </cell>
+          <cell r="P6">
+            <v>0</v>
+          </cell>
+          <cell r="Q6">
+            <v>0</v>
+          </cell>
+          <cell r="R6">
+            <v>0</v>
+          </cell>
+          <cell r="S6">
+            <v>1</v>
+          </cell>
+          <cell r="T6">
+            <v>0</v>
+          </cell>
+          <cell r="U6">
+            <v>0</v>
+          </cell>
+          <cell r="V6">
+            <v>1</v>
+          </cell>
+          <cell r="W6">
+            <v>1</v>
+          </cell>
+          <cell r="X6">
+            <v>2</v>
+          </cell>
+          <cell r="Y6">
+            <v>0</v>
+          </cell>
+          <cell r="Z6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+          <cell r="B7">
+            <v>0</v>
+          </cell>
+          <cell r="C7">
+            <v>0</v>
+          </cell>
+          <cell r="D7">
+            <v>0</v>
+          </cell>
+          <cell r="E7">
+            <v>0</v>
+          </cell>
+          <cell r="F7">
+            <v>1</v>
+          </cell>
+          <cell r="G7">
+            <v>0</v>
+          </cell>
+          <cell r="H7">
+            <v>0</v>
+          </cell>
+          <cell r="I7">
+            <v>0</v>
+          </cell>
+          <cell r="J7">
+            <v>0</v>
+          </cell>
+          <cell r="K7">
+            <v>0</v>
+          </cell>
+          <cell r="L7">
+            <v>1</v>
+          </cell>
+          <cell r="M7">
+            <v>0</v>
+          </cell>
+          <cell r="N7">
+            <v>0</v>
+          </cell>
+          <cell r="O7">
+            <v>0</v>
+          </cell>
+          <cell r="P7">
+            <v>0</v>
+          </cell>
+          <cell r="Q7">
+            <v>0</v>
+          </cell>
+          <cell r="R7">
+            <v>1</v>
+          </cell>
+          <cell r="S7">
+            <v>1</v>
+          </cell>
+          <cell r="T7">
+            <v>0</v>
+          </cell>
+          <cell r="U7">
+            <v>0</v>
+          </cell>
+          <cell r="V7">
+            <v>2</v>
+          </cell>
+          <cell r="W7">
+            <v>2</v>
+          </cell>
+          <cell r="X7">
+            <v>0</v>
+          </cell>
+          <cell r="Y7">
+            <v>0</v>
+          </cell>
+          <cell r="Z7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+          <cell r="B8">
+            <v>0</v>
+          </cell>
+          <cell r="C8">
+            <v>0</v>
+          </cell>
+          <cell r="D8">
+            <v>0</v>
+          </cell>
+          <cell r="E8">
+            <v>0</v>
+          </cell>
+          <cell r="F8">
+            <v>1</v>
+          </cell>
+          <cell r="G8">
+            <v>0</v>
+          </cell>
+          <cell r="H8">
+            <v>0</v>
+          </cell>
+          <cell r="I8">
+            <v>0</v>
+          </cell>
+          <cell r="J8">
+            <v>0</v>
+          </cell>
+          <cell r="K8">
+            <v>1</v>
+          </cell>
+          <cell r="L8">
+            <v>1</v>
+          </cell>
+          <cell r="M8">
+            <v>0</v>
+          </cell>
+          <cell r="N8">
+            <v>0</v>
+          </cell>
+          <cell r="O8">
+            <v>0</v>
+          </cell>
+          <cell r="P8">
+            <v>0</v>
+          </cell>
+          <cell r="Q8">
+            <v>0</v>
+          </cell>
+          <cell r="R8">
+            <v>0</v>
+          </cell>
+          <cell r="S8">
+            <v>1</v>
+          </cell>
+          <cell r="T8">
+            <v>0</v>
+          </cell>
+          <cell r="U8">
+            <v>0</v>
+          </cell>
+          <cell r="V8">
+            <v>2</v>
+          </cell>
+          <cell r="W8">
+            <v>1</v>
+          </cell>
+          <cell r="X8">
+            <v>1</v>
+          </cell>
+          <cell r="Y8">
+            <v>0</v>
+          </cell>
+          <cell r="Z8">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+          <cell r="B9">
+            <v>0</v>
+          </cell>
+          <cell r="C9">
+            <v>0</v>
+          </cell>
+          <cell r="D9">
+            <v>0</v>
+          </cell>
+          <cell r="E9">
+            <v>0</v>
+          </cell>
+          <cell r="F9">
+            <v>2</v>
+          </cell>
+          <cell r="G9">
+            <v>0</v>
+          </cell>
+          <cell r="H9">
+            <v>0</v>
+          </cell>
+          <cell r="I9">
+            <v>0</v>
+          </cell>
+          <cell r="J9">
+            <v>0</v>
+          </cell>
+          <cell r="K9">
+            <v>1</v>
+          </cell>
+          <cell r="L9">
+            <v>1</v>
+          </cell>
+          <cell r="M9">
+            <v>0</v>
+          </cell>
+          <cell r="N9">
+            <v>0</v>
+          </cell>
+          <cell r="O9">
+            <v>0</v>
+          </cell>
+          <cell r="P9">
+            <v>0</v>
+          </cell>
+          <cell r="Q9">
+            <v>0</v>
+          </cell>
+          <cell r="R9">
+            <v>0</v>
+          </cell>
+          <cell r="S9">
+            <v>1</v>
+          </cell>
+          <cell r="T9">
+            <v>0</v>
+          </cell>
+          <cell r="U9">
+            <v>0</v>
+          </cell>
+          <cell r="V9">
+            <v>1</v>
+          </cell>
+          <cell r="W9">
+            <v>1</v>
+          </cell>
+          <cell r="X9">
+            <v>1</v>
+          </cell>
+          <cell r="Y9">
+            <v>0</v>
+          </cell>
+          <cell r="Z9">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+          <cell r="B10">
+            <v>0</v>
+          </cell>
+          <cell r="C10">
+            <v>0</v>
+          </cell>
+          <cell r="D10">
+            <v>0</v>
+          </cell>
+          <cell r="E10">
+            <v>0</v>
+          </cell>
+          <cell r="F10">
+            <v>1</v>
+          </cell>
+          <cell r="G10">
+            <v>0</v>
+          </cell>
+          <cell r="H10">
+            <v>0</v>
+          </cell>
+          <cell r="I10">
+            <v>0</v>
+          </cell>
+          <cell r="J10">
+            <v>0</v>
+          </cell>
+          <cell r="K10">
+            <v>1</v>
+          </cell>
+          <cell r="L10">
+            <v>0</v>
+          </cell>
+          <cell r="M10">
+            <v>0</v>
+          </cell>
+          <cell r="N10">
+            <v>0</v>
+          </cell>
+          <cell r="O10">
+            <v>0</v>
+          </cell>
+          <cell r="P10">
+            <v>0</v>
+          </cell>
+          <cell r="Q10">
+            <v>1</v>
+          </cell>
+          <cell r="R10">
+            <v>0</v>
+          </cell>
+          <cell r="S10">
+            <v>1</v>
+          </cell>
+          <cell r="T10">
+            <v>0</v>
+          </cell>
+          <cell r="U10">
+            <v>0</v>
+          </cell>
+          <cell r="V10">
+            <v>1</v>
+          </cell>
+          <cell r="W10">
+            <v>1</v>
+          </cell>
+          <cell r="X10">
+            <v>1</v>
+          </cell>
+          <cell r="Y10">
+            <v>0</v>
+          </cell>
+          <cell r="Z10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+          <cell r="B11">
+            <v>0</v>
+          </cell>
+          <cell r="C11">
+            <v>0</v>
+          </cell>
+          <cell r="D11">
+            <v>0</v>
+          </cell>
+          <cell r="E11">
+            <v>0</v>
+          </cell>
+          <cell r="F11">
+            <v>3</v>
+          </cell>
+          <cell r="G11">
+            <v>0</v>
+          </cell>
+          <cell r="H11">
+            <v>0</v>
+          </cell>
+          <cell r="I11">
+            <v>0</v>
+          </cell>
+          <cell r="J11">
+            <v>0</v>
+          </cell>
+          <cell r="K11">
+            <v>1</v>
+          </cell>
+          <cell r="L11">
+            <v>0</v>
+          </cell>
+          <cell r="M11">
+            <v>0</v>
+          </cell>
+          <cell r="N11">
+            <v>0</v>
+          </cell>
+          <cell r="O11">
+            <v>0</v>
+          </cell>
+          <cell r="P11">
+            <v>0</v>
+          </cell>
+          <cell r="Q11">
+            <v>0</v>
+          </cell>
+          <cell r="R11">
+            <v>0</v>
+          </cell>
+          <cell r="S11">
+            <v>1</v>
+          </cell>
+          <cell r="T11">
+            <v>0</v>
+          </cell>
+          <cell r="U11">
+            <v>0</v>
+          </cell>
+          <cell r="V11">
+            <v>1</v>
+          </cell>
+          <cell r="W11">
+            <v>1</v>
+          </cell>
+          <cell r="X11">
+            <v>1</v>
+          </cell>
+          <cell r="Y11">
+            <v>0</v>
+          </cell>
+          <cell r="Z11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+          <cell r="B12">
+            <v>0</v>
+          </cell>
+          <cell r="C12">
+            <v>0</v>
+          </cell>
+          <cell r="D12">
+            <v>0</v>
+          </cell>
+          <cell r="E12">
+            <v>1</v>
+          </cell>
+          <cell r="F12">
+            <v>1</v>
+          </cell>
+          <cell r="G12">
+            <v>0</v>
+          </cell>
+          <cell r="H12">
+            <v>0</v>
+          </cell>
+          <cell r="I12">
+            <v>0</v>
+          </cell>
+          <cell r="J12">
+            <v>0</v>
+          </cell>
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+          <cell r="L12">
+            <v>1</v>
+          </cell>
+          <cell r="M12">
+            <v>0</v>
+          </cell>
+          <cell r="N12">
+            <v>0</v>
+          </cell>
+          <cell r="O12">
+            <v>0</v>
+          </cell>
+          <cell r="P12">
+            <v>0</v>
+          </cell>
+          <cell r="Q12">
+            <v>0</v>
+          </cell>
+          <cell r="R12">
+            <v>0</v>
+          </cell>
+          <cell r="S12">
+            <v>0</v>
+          </cell>
+          <cell r="T12">
+            <v>0</v>
+          </cell>
+          <cell r="U12">
+            <v>0</v>
+          </cell>
+          <cell r="V12">
+            <v>1</v>
+          </cell>
+          <cell r="W12">
+            <v>1</v>
+          </cell>
+          <cell r="X12">
+            <v>1</v>
+          </cell>
+          <cell r="Y12">
+            <v>0</v>
+          </cell>
+          <cell r="Z12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+          <cell r="B13">
+            <v>0</v>
+          </cell>
+          <cell r="C13">
+            <v>0</v>
+          </cell>
+          <cell r="D13">
+            <v>0</v>
+          </cell>
+          <cell r="E13">
+            <v>0</v>
+          </cell>
+          <cell r="F13">
+            <v>1</v>
+          </cell>
+          <cell r="G13">
+            <v>0</v>
+          </cell>
+          <cell r="H13">
+            <v>0</v>
+          </cell>
+          <cell r="I13">
+            <v>0</v>
+          </cell>
+          <cell r="J13">
+            <v>0</v>
+          </cell>
+          <cell r="K13">
+            <v>2</v>
+          </cell>
+          <cell r="L13">
+            <v>0</v>
+          </cell>
+          <cell r="M13">
+            <v>0</v>
+          </cell>
+          <cell r="N13">
+            <v>0</v>
+          </cell>
+          <cell r="O13">
+            <v>0</v>
+          </cell>
+          <cell r="P13">
+            <v>0</v>
+          </cell>
+          <cell r="Q13">
+            <v>0</v>
+          </cell>
+          <cell r="R13">
+            <v>0</v>
+          </cell>
+          <cell r="S13">
+            <v>1</v>
+          </cell>
+          <cell r="T13">
+            <v>0</v>
+          </cell>
+          <cell r="U13">
+            <v>0</v>
+          </cell>
+          <cell r="V13">
+            <v>1</v>
+          </cell>
+          <cell r="W13">
+            <v>2</v>
+          </cell>
+          <cell r="X13">
+            <v>0</v>
+          </cell>
+          <cell r="Y13">
+            <v>0</v>
+          </cell>
+          <cell r="Z13">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+          <cell r="B14">
+            <v>0</v>
+          </cell>
+          <cell r="C14">
+            <v>0</v>
+          </cell>
+          <cell r="D14">
+            <v>0</v>
+          </cell>
+          <cell r="E14">
+            <v>0</v>
+          </cell>
+          <cell r="F14">
+            <v>1</v>
+          </cell>
+          <cell r="G14">
+            <v>0</v>
+          </cell>
+          <cell r="H14">
+            <v>0</v>
+          </cell>
+          <cell r="I14">
+            <v>0</v>
+          </cell>
+          <cell r="J14">
+            <v>0</v>
+          </cell>
+          <cell r="K14">
+            <v>1</v>
+          </cell>
+          <cell r="L14">
+            <v>0</v>
+          </cell>
+          <cell r="M14">
+            <v>0</v>
+          </cell>
+          <cell r="N14">
+            <v>0</v>
+          </cell>
+          <cell r="O14">
+            <v>0</v>
+          </cell>
+          <cell r="P14">
+            <v>0</v>
+          </cell>
+          <cell r="Q14">
+            <v>0</v>
+          </cell>
+          <cell r="R14">
+            <v>0</v>
+          </cell>
+          <cell r="S14">
+            <v>1</v>
+          </cell>
+          <cell r="T14">
+            <v>0</v>
+          </cell>
+          <cell r="U14">
+            <v>0</v>
+          </cell>
+          <cell r="V14">
+            <v>1</v>
+          </cell>
+          <cell r="W14">
+            <v>1</v>
+          </cell>
+          <cell r="X14">
+            <v>0</v>
+          </cell>
+          <cell r="Y14">
+            <v>0</v>
+          </cell>
+          <cell r="Z14">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+          <cell r="B15">
+            <v>0</v>
+          </cell>
+          <cell r="C15">
+            <v>0</v>
+          </cell>
+          <cell r="D15">
+            <v>0</v>
+          </cell>
+          <cell r="E15">
+            <v>0</v>
+          </cell>
+          <cell r="F15">
+            <v>1</v>
+          </cell>
+          <cell r="G15">
+            <v>0</v>
+          </cell>
+          <cell r="H15">
+            <v>0</v>
+          </cell>
+          <cell r="I15">
+            <v>0</v>
+          </cell>
+          <cell r="J15">
+            <v>0</v>
+          </cell>
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+          <cell r="L15">
+            <v>0</v>
+          </cell>
+          <cell r="M15">
+            <v>0</v>
+          </cell>
+          <cell r="N15">
+            <v>0</v>
+          </cell>
+          <cell r="O15">
+            <v>0</v>
+          </cell>
+          <cell r="P15">
+            <v>0</v>
+          </cell>
+          <cell r="Q15">
+            <v>0</v>
+          </cell>
+          <cell r="R15">
+            <v>0</v>
+          </cell>
+          <cell r="S15">
+            <v>2</v>
+          </cell>
+          <cell r="T15">
+            <v>0</v>
+          </cell>
+          <cell r="U15">
+            <v>0</v>
+          </cell>
+          <cell r="V15">
+            <v>1</v>
+          </cell>
+          <cell r="W15">
+            <v>1</v>
+          </cell>
+          <cell r="X15">
+            <v>1</v>
+          </cell>
+          <cell r="Y15">
+            <v>0</v>
+          </cell>
+          <cell r="Z15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+          <cell r="B16">
+            <v>0</v>
+          </cell>
+          <cell r="C16">
+            <v>0</v>
+          </cell>
+          <cell r="D16">
+            <v>0</v>
+          </cell>
+          <cell r="E16">
+            <v>0</v>
+          </cell>
+          <cell r="F16">
+            <v>1</v>
+          </cell>
+          <cell r="G16">
+            <v>0</v>
+          </cell>
+          <cell r="H16">
+            <v>0</v>
+          </cell>
+          <cell r="I16">
+            <v>0</v>
+          </cell>
+          <cell r="J16">
+            <v>0</v>
+          </cell>
+          <cell r="K16">
+            <v>0</v>
+          </cell>
+          <cell r="L16">
+            <v>0</v>
+          </cell>
+          <cell r="M16">
+            <v>0</v>
+          </cell>
+          <cell r="N16">
+            <v>0</v>
+          </cell>
+          <cell r="O16">
+            <v>0</v>
+          </cell>
+          <cell r="P16">
+            <v>0</v>
+          </cell>
+          <cell r="Q16">
+            <v>1</v>
+          </cell>
+          <cell r="R16">
+            <v>0</v>
+          </cell>
+          <cell r="S16">
+            <v>1</v>
+          </cell>
+          <cell r="T16">
+            <v>0</v>
+          </cell>
+          <cell r="U16">
+            <v>0</v>
+          </cell>
+          <cell r="V16">
+            <v>1</v>
+          </cell>
+          <cell r="W16">
+            <v>1</v>
+          </cell>
+          <cell r="X16">
+            <v>0</v>
+          </cell>
+          <cell r="Y16">
+            <v>0</v>
+          </cell>
+          <cell r="Z16">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+          <cell r="B17">
+            <v>0</v>
+          </cell>
+          <cell r="C17">
+            <v>0</v>
+          </cell>
+          <cell r="D17">
+            <v>0</v>
+          </cell>
+          <cell r="E17">
+            <v>0</v>
+          </cell>
+          <cell r="F17">
+            <v>0</v>
+          </cell>
+          <cell r="G17">
+            <v>0</v>
+          </cell>
+          <cell r="H17">
+            <v>0</v>
+          </cell>
+          <cell r="I17">
+            <v>0</v>
+          </cell>
+          <cell r="J17">
+            <v>0</v>
+          </cell>
+          <cell r="K17">
+            <v>0</v>
+          </cell>
+          <cell r="L17">
+            <v>0</v>
+          </cell>
+          <cell r="M17">
+            <v>0</v>
+          </cell>
+          <cell r="N17">
+            <v>0</v>
+          </cell>
+          <cell r="O17">
+            <v>0</v>
+          </cell>
+          <cell r="P17">
+            <v>0</v>
+          </cell>
+          <cell r="Q17">
+            <v>0</v>
+          </cell>
+          <cell r="R17">
+            <v>1</v>
+          </cell>
+          <cell r="S17">
+            <v>1</v>
+          </cell>
+          <cell r="T17">
+            <v>0</v>
+          </cell>
+          <cell r="U17">
+            <v>0</v>
+          </cell>
+          <cell r="V17">
+            <v>0</v>
+          </cell>
+          <cell r="W17">
+            <v>1</v>
+          </cell>
+          <cell r="X17">
+            <v>1</v>
+          </cell>
+          <cell r="Y17">
+            <v>0</v>
+          </cell>
+          <cell r="Z17">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+          <cell r="B18">
+            <v>0</v>
+          </cell>
+          <cell r="C18">
+            <v>0</v>
+          </cell>
+          <cell r="D18">
+            <v>0</v>
+          </cell>
+          <cell r="E18">
+            <v>0</v>
+          </cell>
+          <cell r="F18">
+            <v>1</v>
+          </cell>
+          <cell r="G18">
+            <v>0</v>
+          </cell>
+          <cell r="H18">
+            <v>0</v>
+          </cell>
+          <cell r="I18">
+            <v>0</v>
+          </cell>
+          <cell r="J18">
+            <v>0</v>
+          </cell>
+          <cell r="K18">
+            <v>0</v>
+          </cell>
+          <cell r="L18">
+            <v>1</v>
+          </cell>
+          <cell r="M18">
+            <v>0</v>
+          </cell>
+          <cell r="N18">
+            <v>0</v>
+          </cell>
+          <cell r="O18">
+            <v>0</v>
+          </cell>
+          <cell r="P18">
+            <v>0</v>
+          </cell>
+          <cell r="Q18">
+            <v>0</v>
+          </cell>
+          <cell r="R18">
+            <v>1</v>
+          </cell>
+          <cell r="S18">
+            <v>0</v>
+          </cell>
+          <cell r="T18">
+            <v>0</v>
+          </cell>
+          <cell r="U18">
+            <v>0</v>
+          </cell>
+          <cell r="V18">
+            <v>1</v>
+          </cell>
+          <cell r="W18">
+            <v>2</v>
+          </cell>
+          <cell r="X18">
+            <v>1</v>
+          </cell>
+          <cell r="Y18">
+            <v>0</v>
+          </cell>
+          <cell r="Z18">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+          <cell r="B19">
+            <v>0</v>
+          </cell>
+          <cell r="C19">
+            <v>0</v>
+          </cell>
+          <cell r="D19">
+            <v>0</v>
+          </cell>
+          <cell r="E19">
+            <v>0</v>
+          </cell>
+          <cell r="F19">
+            <v>0</v>
+          </cell>
+          <cell r="G19">
+            <v>0</v>
+          </cell>
+          <cell r="H19">
+            <v>0</v>
+          </cell>
+          <cell r="I19">
+            <v>0</v>
+          </cell>
+          <cell r="J19">
+            <v>0</v>
+          </cell>
+          <cell r="K19">
+            <v>0</v>
+          </cell>
+          <cell r="L19">
+            <v>0</v>
+          </cell>
+          <cell r="M19">
+            <v>0</v>
+          </cell>
+          <cell r="N19">
+            <v>0</v>
+          </cell>
+          <cell r="O19">
+            <v>0</v>
+          </cell>
+          <cell r="P19">
+            <v>0</v>
+          </cell>
+          <cell r="Q19">
+            <v>1</v>
+          </cell>
+          <cell r="R19">
+            <v>0</v>
+          </cell>
+          <cell r="S19">
+            <v>0</v>
+          </cell>
+          <cell r="T19">
+            <v>0</v>
+          </cell>
+          <cell r="U19">
+            <v>0</v>
+          </cell>
+          <cell r="V19">
+            <v>1</v>
+          </cell>
+          <cell r="W19">
+            <v>1</v>
+          </cell>
+          <cell r="X19">
+            <v>1</v>
+          </cell>
+          <cell r="Y19">
+            <v>0</v>
+          </cell>
+          <cell r="Z19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+          <cell r="B20">
+            <v>0</v>
+          </cell>
+          <cell r="C20">
+            <v>0</v>
+          </cell>
+          <cell r="D20">
+            <v>0</v>
+          </cell>
+          <cell r="E20">
+            <v>0</v>
+          </cell>
+          <cell r="F20">
+            <v>0</v>
+          </cell>
+          <cell r="G20">
+            <v>0</v>
+          </cell>
+          <cell r="H20">
+            <v>0</v>
+          </cell>
+          <cell r="I20">
+            <v>0</v>
+          </cell>
+          <cell r="J20">
+            <v>0</v>
+          </cell>
+          <cell r="K20">
+            <v>0</v>
+          </cell>
+          <cell r="L20">
+            <v>0</v>
+          </cell>
+          <cell r="M20">
+            <v>0</v>
+          </cell>
+          <cell r="N20">
+            <v>0</v>
+          </cell>
+          <cell r="O20">
+            <v>0</v>
+          </cell>
+          <cell r="P20">
+            <v>0</v>
+          </cell>
+          <cell r="Q20">
+            <v>0</v>
+          </cell>
+          <cell r="R20">
+            <v>1</v>
+          </cell>
+          <cell r="S20">
+            <v>1</v>
+          </cell>
+          <cell r="T20">
+            <v>0</v>
+          </cell>
+          <cell r="U20">
+            <v>0</v>
+          </cell>
+          <cell r="V20">
+            <v>1</v>
+          </cell>
+          <cell r="W20">
+            <v>1</v>
+          </cell>
+          <cell r="X20">
+            <v>1</v>
+          </cell>
+          <cell r="Y20">
+            <v>0</v>
+          </cell>
+          <cell r="Z20">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>20</v>
+          </cell>
+          <cell r="B21">
+            <v>0</v>
+          </cell>
+          <cell r="C21">
+            <v>0</v>
+          </cell>
+          <cell r="D21">
+            <v>0</v>
+          </cell>
+          <cell r="E21">
+            <v>0</v>
+          </cell>
+          <cell r="F21">
+            <v>0</v>
+          </cell>
+          <cell r="G21">
+            <v>1</v>
+          </cell>
+          <cell r="H21">
+            <v>0</v>
+          </cell>
+          <cell r="I21">
+            <v>0</v>
+          </cell>
+          <cell r="J21">
+            <v>0</v>
+          </cell>
+          <cell r="K21">
+            <v>1</v>
+          </cell>
+          <cell r="L21">
+            <v>1</v>
+          </cell>
+          <cell r="M21">
+            <v>0</v>
+          </cell>
+          <cell r="N21">
+            <v>0</v>
+          </cell>
+          <cell r="O21">
+            <v>0</v>
+          </cell>
+          <cell r="P21">
+            <v>0</v>
+          </cell>
+          <cell r="Q21">
+            <v>0</v>
+          </cell>
+          <cell r="R21">
+            <v>0</v>
+          </cell>
+          <cell r="S21">
+            <v>1</v>
+          </cell>
+          <cell r="T21">
+            <v>1</v>
+          </cell>
+          <cell r="U21">
+            <v>0</v>
+          </cell>
+          <cell r="V21">
+            <v>1</v>
+          </cell>
+          <cell r="W21">
+            <v>1</v>
+          </cell>
+          <cell r="X21">
+            <v>1</v>
+          </cell>
+          <cell r="Y21">
+            <v>0</v>
+          </cell>
+          <cell r="Z21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>21</v>
+          </cell>
+          <cell r="B22">
+            <v>0</v>
+          </cell>
+          <cell r="C22">
+            <v>0</v>
+          </cell>
+          <cell r="D22">
+            <v>0</v>
+          </cell>
+          <cell r="E22">
+            <v>0</v>
+          </cell>
+          <cell r="F22">
+            <v>0</v>
+          </cell>
+          <cell r="G22">
+            <v>0</v>
+          </cell>
+          <cell r="H22">
+            <v>0</v>
+          </cell>
+          <cell r="I22">
+            <v>0</v>
+          </cell>
+          <cell r="J22">
+            <v>0</v>
+          </cell>
+          <cell r="K22">
+            <v>0</v>
+          </cell>
+          <cell r="L22">
+            <v>1</v>
+          </cell>
+          <cell r="M22">
+            <v>0</v>
+          </cell>
+          <cell r="N22">
+            <v>0</v>
+          </cell>
+          <cell r="O22">
+            <v>0</v>
+          </cell>
+          <cell r="P22">
+            <v>0</v>
+          </cell>
+          <cell r="Q22">
+            <v>0</v>
+          </cell>
+          <cell r="R22">
+            <v>1</v>
+          </cell>
+          <cell r="S22">
+            <v>0</v>
+          </cell>
+          <cell r="T22">
+            <v>0</v>
+          </cell>
+          <cell r="U22">
+            <v>0</v>
+          </cell>
+          <cell r="V22">
+            <v>1</v>
+          </cell>
+          <cell r="W22">
+            <v>1</v>
+          </cell>
+          <cell r="X22">
+            <v>1</v>
+          </cell>
+          <cell r="Y22">
+            <v>0</v>
+          </cell>
+          <cell r="Z22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>22</v>
+          </cell>
+          <cell r="B23">
+            <v>0</v>
+          </cell>
+          <cell r="C23">
+            <v>0</v>
+          </cell>
+          <cell r="D23">
+            <v>0</v>
+          </cell>
+          <cell r="E23">
+            <v>0</v>
+          </cell>
+          <cell r="F23">
+            <v>0</v>
+          </cell>
+          <cell r="G23">
+            <v>0</v>
+          </cell>
+          <cell r="H23">
+            <v>0</v>
+          </cell>
+          <cell r="I23">
+            <v>0</v>
+          </cell>
+          <cell r="J23">
+            <v>0</v>
+          </cell>
+          <cell r="K23">
+            <v>0</v>
+          </cell>
+          <cell r="L23">
+            <v>0</v>
+          </cell>
+          <cell r="M23">
+            <v>0</v>
+          </cell>
+          <cell r="N23">
+            <v>0</v>
+          </cell>
+          <cell r="O23">
+            <v>0</v>
+          </cell>
+          <cell r="P23">
+            <v>0</v>
+          </cell>
+          <cell r="Q23">
+            <v>1</v>
+          </cell>
+          <cell r="R23">
+            <v>0</v>
+          </cell>
+          <cell r="S23">
+            <v>0</v>
+          </cell>
+          <cell r="T23">
+            <v>0</v>
+          </cell>
+          <cell r="U23">
+            <v>0</v>
+          </cell>
+          <cell r="V23">
+            <v>1</v>
+          </cell>
+          <cell r="W23">
+            <v>1</v>
+          </cell>
+          <cell r="X23">
+            <v>1</v>
+          </cell>
+          <cell r="Y23">
+            <v>0</v>
+          </cell>
+          <cell r="Z23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>23</v>
+          </cell>
+          <cell r="B24">
+            <v>0</v>
+          </cell>
+          <cell r="C24">
+            <v>0</v>
+          </cell>
+          <cell r="D24">
+            <v>0</v>
+          </cell>
+          <cell r="E24">
+            <v>0</v>
+          </cell>
+          <cell r="F24">
+            <v>1</v>
+          </cell>
+          <cell r="G24">
+            <v>0</v>
+          </cell>
+          <cell r="H24">
+            <v>0</v>
+          </cell>
+          <cell r="I24">
+            <v>0</v>
+          </cell>
+          <cell r="J24">
+            <v>0</v>
+          </cell>
+          <cell r="K24">
+            <v>0</v>
+          </cell>
+          <cell r="L24">
+            <v>0</v>
+          </cell>
+          <cell r="M24">
+            <v>0</v>
+          </cell>
+          <cell r="N24">
+            <v>0</v>
+          </cell>
+          <cell r="O24">
+            <v>0</v>
+          </cell>
+          <cell r="P24">
+            <v>0</v>
+          </cell>
+          <cell r="Q24">
+            <v>1</v>
+          </cell>
+          <cell r="R24">
+            <v>1</v>
+          </cell>
+          <cell r="S24">
+            <v>0</v>
+          </cell>
+          <cell r="T24">
+            <v>0</v>
+          </cell>
+          <cell r="U24">
+            <v>0</v>
+          </cell>
+          <cell r="V24">
+            <v>1</v>
+          </cell>
+          <cell r="W24">
+            <v>2</v>
+          </cell>
+          <cell r="X24">
+            <v>1</v>
+          </cell>
+          <cell r="Y24">
+            <v>0</v>
+          </cell>
+          <cell r="Z24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>24</v>
+          </cell>
+          <cell r="B25">
+            <v>0</v>
+          </cell>
+          <cell r="C25">
+            <v>0</v>
+          </cell>
+          <cell r="D25">
+            <v>0</v>
+          </cell>
+          <cell r="E25">
+            <v>0</v>
+          </cell>
+          <cell r="F25">
+            <v>0</v>
+          </cell>
+          <cell r="G25">
+            <v>0</v>
+          </cell>
+          <cell r="H25">
+            <v>0</v>
+          </cell>
+          <cell r="I25">
+            <v>0</v>
+          </cell>
+          <cell r="J25">
+            <v>0</v>
+          </cell>
+          <cell r="K25">
+            <v>0</v>
+          </cell>
+          <cell r="L25">
+            <v>0</v>
+          </cell>
+          <cell r="M25">
+            <v>0</v>
+          </cell>
+          <cell r="N25">
+            <v>0</v>
+          </cell>
+          <cell r="O25">
+            <v>0</v>
+          </cell>
+          <cell r="P25">
+            <v>0</v>
+          </cell>
+          <cell r="Q25">
+            <v>1</v>
+          </cell>
+          <cell r="R25">
+            <v>0</v>
+          </cell>
+          <cell r="S25">
+            <v>1</v>
+          </cell>
+          <cell r="T25">
+            <v>0</v>
+          </cell>
+          <cell r="U25">
+            <v>0</v>
+          </cell>
+          <cell r="V25">
+            <v>1</v>
+          </cell>
+          <cell r="W25">
+            <v>1</v>
+          </cell>
+          <cell r="X25">
+            <v>1</v>
+          </cell>
+          <cell r="Y25">
+            <v>0</v>
+          </cell>
+          <cell r="Z25">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>25</v>
+          </cell>
+          <cell r="B26">
+            <v>0</v>
+          </cell>
+          <cell r="C26">
+            <v>0</v>
+          </cell>
+          <cell r="D26">
+            <v>0</v>
+          </cell>
+          <cell r="E26">
+            <v>0</v>
+          </cell>
+          <cell r="F26">
+            <v>0</v>
+          </cell>
+          <cell r="G26">
+            <v>0</v>
+          </cell>
+          <cell r="H26">
+            <v>0</v>
+          </cell>
+          <cell r="I26">
+            <v>0</v>
+          </cell>
+          <cell r="J26">
+            <v>0</v>
+          </cell>
+          <cell r="K26">
+            <v>0</v>
+          </cell>
+          <cell r="L26">
+            <v>1</v>
+          </cell>
+          <cell r="M26">
+            <v>0</v>
+          </cell>
+          <cell r="N26">
+            <v>0</v>
+          </cell>
+          <cell r="O26">
+            <v>0</v>
+          </cell>
+          <cell r="P26">
+            <v>0</v>
+          </cell>
+          <cell r="Q26">
+            <v>0</v>
+          </cell>
+          <cell r="R26">
+            <v>0</v>
+          </cell>
+          <cell r="S26">
+            <v>1</v>
+          </cell>
+          <cell r="T26">
+            <v>0</v>
+          </cell>
+          <cell r="U26">
+            <v>0</v>
+          </cell>
+          <cell r="V26">
+            <v>1</v>
+          </cell>
+          <cell r="W26">
+            <v>1</v>
+          </cell>
+          <cell r="X26">
+            <v>0</v>
+          </cell>
+          <cell r="Y26">
+            <v>0</v>
+          </cell>
+          <cell r="Z26">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>26</v>
+          </cell>
+          <cell r="B27">
+            <v>0</v>
+          </cell>
+          <cell r="C27">
+            <v>0</v>
+          </cell>
+          <cell r="D27">
+            <v>0</v>
+          </cell>
+          <cell r="E27">
+            <v>0</v>
+          </cell>
+          <cell r="F27">
+            <v>0</v>
+          </cell>
+          <cell r="G27">
+            <v>0</v>
+          </cell>
+          <cell r="H27">
+            <v>0</v>
+          </cell>
+          <cell r="I27">
+            <v>0</v>
+          </cell>
+          <cell r="J27">
+            <v>0</v>
+          </cell>
+          <cell r="K27">
+            <v>0</v>
+          </cell>
+          <cell r="L27">
+            <v>1</v>
+          </cell>
+          <cell r="M27">
+            <v>0</v>
+          </cell>
+          <cell r="N27">
+            <v>0</v>
+          </cell>
+          <cell r="O27">
+            <v>0</v>
+          </cell>
+          <cell r="P27">
+            <v>0</v>
+          </cell>
+          <cell r="Q27">
+            <v>0</v>
+          </cell>
+          <cell r="R27">
+            <v>0</v>
+          </cell>
+          <cell r="S27">
+            <v>1</v>
+          </cell>
+          <cell r="T27">
+            <v>0</v>
+          </cell>
+          <cell r="U27">
+            <v>0</v>
+          </cell>
+          <cell r="V27">
+            <v>1</v>
+          </cell>
+          <cell r="W27">
+            <v>1</v>
+          </cell>
+          <cell r="X27">
+            <v>1</v>
+          </cell>
+          <cell r="Y27">
+            <v>0</v>
+          </cell>
+          <cell r="Z27">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>27</v>
+          </cell>
+          <cell r="B28">
+            <v>0</v>
+          </cell>
+          <cell r="C28">
+            <v>0</v>
+          </cell>
+          <cell r="D28">
+            <v>0</v>
+          </cell>
+          <cell r="E28">
+            <v>0</v>
+          </cell>
+          <cell r="F28">
+            <v>0</v>
+          </cell>
+          <cell r="G28">
+            <v>0</v>
+          </cell>
+          <cell r="H28">
+            <v>0</v>
+          </cell>
+          <cell r="I28">
+            <v>0</v>
+          </cell>
+          <cell r="J28">
+            <v>0</v>
+          </cell>
+          <cell r="K28">
+            <v>0</v>
+          </cell>
+          <cell r="L28">
+            <v>1</v>
+          </cell>
+          <cell r="M28">
+            <v>0</v>
+          </cell>
+          <cell r="N28">
+            <v>0</v>
+          </cell>
+          <cell r="O28">
+            <v>0</v>
+          </cell>
+          <cell r="P28">
+            <v>0</v>
+          </cell>
+          <cell r="Q28">
+            <v>0</v>
+          </cell>
+          <cell r="R28">
+            <v>0</v>
+          </cell>
+          <cell r="S28">
+            <v>0</v>
+          </cell>
+          <cell r="T28">
+            <v>0</v>
+          </cell>
+          <cell r="U28">
+            <v>0</v>
+          </cell>
+          <cell r="V28">
+            <v>0</v>
+          </cell>
+          <cell r="W28">
+            <v>1</v>
+          </cell>
+          <cell r="X28">
+            <v>1</v>
+          </cell>
+          <cell r="Y28">
+            <v>0</v>
+          </cell>
+          <cell r="Z28">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>28</v>
+          </cell>
+          <cell r="B29">
+            <v>0</v>
+          </cell>
+          <cell r="C29">
+            <v>0</v>
+          </cell>
+          <cell r="D29">
+            <v>0</v>
+          </cell>
+          <cell r="E29">
+            <v>0</v>
+          </cell>
+          <cell r="F29">
+            <v>0</v>
+          </cell>
+          <cell r="G29">
+            <v>0</v>
+          </cell>
+          <cell r="H29">
+            <v>0</v>
+          </cell>
+          <cell r="I29">
+            <v>1</v>
+          </cell>
+          <cell r="J29">
+            <v>0</v>
+          </cell>
+          <cell r="K29">
+            <v>0</v>
+          </cell>
+          <cell r="L29">
+            <v>0</v>
+          </cell>
+          <cell r="M29">
+            <v>0</v>
+          </cell>
+          <cell r="N29">
+            <v>0</v>
+          </cell>
+          <cell r="O29">
+            <v>0</v>
+          </cell>
+          <cell r="P29">
+            <v>0</v>
+          </cell>
+          <cell r="Q29">
+            <v>0</v>
+          </cell>
+          <cell r="R29">
+            <v>0</v>
+          </cell>
+          <cell r="S29">
+            <v>1</v>
+          </cell>
+          <cell r="T29">
+            <v>0</v>
+          </cell>
+          <cell r="U29">
+            <v>0</v>
+          </cell>
+          <cell r="V29">
+            <v>0</v>
+          </cell>
+          <cell r="W29">
+            <v>1</v>
+          </cell>
+          <cell r="X29">
+            <v>0</v>
+          </cell>
+          <cell r="Y29">
+            <v>0</v>
+          </cell>
+          <cell r="Z29">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="resultados_integracion_partido_"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Distrito</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>AH</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>AMA</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>DEM</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>EVO</v>
+          </cell>
+          <cell r="F1" t="str">
+            <v>FA</v>
+          </cell>
+          <cell r="G1" t="str">
+            <v>FREVS</v>
+          </cell>
+          <cell r="H1" t="str">
+            <v>IGU</v>
+          </cell>
+          <cell r="I1" t="str">
+            <v>IND</v>
+          </cell>
+          <cell r="J1" t="str">
+            <v>PAVP</v>
+          </cell>
+          <cell r="K1" t="str">
+            <v>PCCH</v>
+          </cell>
+          <cell r="L1" t="str">
+            <v>PDC</v>
+          </cell>
+          <cell r="M1" t="str">
+            <v>PDG</v>
+          </cell>
+          <cell r="N1" t="str">
+            <v>PH</v>
+          </cell>
+          <cell r="O1" t="str">
+            <v>PL</v>
+          </cell>
+          <cell r="P1" t="str">
+            <v>POP</v>
+          </cell>
+          <cell r="Q1" t="str">
+            <v>PPD</v>
+          </cell>
+          <cell r="R1" t="str">
+            <v>PR</v>
+          </cell>
+          <cell r="S1" t="str">
+            <v>PS</v>
+          </cell>
+          <cell r="T1" t="str">
+            <v>PSC</v>
+          </cell>
+          <cell r="U1" t="str">
+            <v>PTR</v>
+          </cell>
+          <cell r="V1" t="str">
+            <v>REP</v>
+          </cell>
+          <cell r="W1" t="str">
+            <v>RN</v>
+          </cell>
+          <cell r="X1" t="str">
+            <v>UDI</v>
+          </cell>
+          <cell r="Y1" t="str">
+            <v>Votos Blancos</v>
+          </cell>
+          <cell r="Z1" t="str">
+            <v>Votos Nulos</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+          <cell r="B2">
+            <v>0</v>
+          </cell>
+          <cell r="C2">
+            <v>0</v>
+          </cell>
+          <cell r="D2">
+            <v>0</v>
+          </cell>
+          <cell r="E2">
+            <v>0</v>
+          </cell>
+          <cell r="F2">
+            <v>0</v>
+          </cell>
+          <cell r="G2">
+            <v>0</v>
+          </cell>
+          <cell r="H2">
+            <v>0</v>
+          </cell>
+          <cell r="I2">
+            <v>0</v>
+          </cell>
+          <cell r="J2">
+            <v>0</v>
+          </cell>
+          <cell r="K2">
+            <v>1</v>
+          </cell>
+          <cell r="L2">
+            <v>0</v>
+          </cell>
+          <cell r="M2">
+            <v>0</v>
+          </cell>
+          <cell r="N2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+          <cell r="P2">
+            <v>0</v>
+          </cell>
+          <cell r="Q2">
+            <v>0</v>
+          </cell>
+          <cell r="R2">
+            <v>0</v>
+          </cell>
+          <cell r="S2">
+            <v>1</v>
+          </cell>
+          <cell r="T2">
+            <v>0</v>
+          </cell>
+          <cell r="U2">
+            <v>0</v>
+          </cell>
+          <cell r="V2">
+            <v>1</v>
+          </cell>
+          <cell r="W2">
+            <v>0</v>
+          </cell>
+          <cell r="X2">
+            <v>0</v>
+          </cell>
+          <cell r="Y2">
+            <v>0</v>
+          </cell>
+          <cell r="Z2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+          <cell r="B3">
+            <v>0</v>
+          </cell>
+          <cell r="C3">
+            <v>0</v>
+          </cell>
+          <cell r="D3">
+            <v>0</v>
+          </cell>
+          <cell r="E3">
+            <v>0</v>
+          </cell>
+          <cell r="F3">
+            <v>0</v>
+          </cell>
+          <cell r="G3">
+            <v>0</v>
+          </cell>
+          <cell r="H3">
+            <v>0</v>
+          </cell>
+          <cell r="I3">
+            <v>0</v>
+          </cell>
+          <cell r="J3">
+            <v>0</v>
+          </cell>
+          <cell r="K3">
+            <v>0</v>
+          </cell>
+          <cell r="L3">
+            <v>1</v>
+          </cell>
+          <cell r="M3">
+            <v>0</v>
+          </cell>
+          <cell r="N3">
+            <v>0</v>
+          </cell>
+          <cell r="O3">
+            <v>0</v>
+          </cell>
+          <cell r="P3">
+            <v>0</v>
+          </cell>
+          <cell r="Q3">
+            <v>0</v>
+          </cell>
+          <cell r="R3">
+            <v>0</v>
+          </cell>
+          <cell r="S3">
+            <v>0</v>
+          </cell>
+          <cell r="T3">
+            <v>0</v>
+          </cell>
+          <cell r="U3">
+            <v>0</v>
+          </cell>
+          <cell r="V3">
+            <v>1</v>
+          </cell>
+          <cell r="W3">
+            <v>1</v>
+          </cell>
+          <cell r="X3">
+            <v>0</v>
+          </cell>
+          <cell r="Y3">
+            <v>0</v>
+          </cell>
+          <cell r="Z3">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+          <cell r="B4">
+            <v>0</v>
+          </cell>
+          <cell r="C4">
+            <v>0</v>
+          </cell>
+          <cell r="D4">
+            <v>0</v>
+          </cell>
+          <cell r="E4">
+            <v>0</v>
+          </cell>
+          <cell r="F4">
+            <v>0</v>
+          </cell>
+          <cell r="G4">
+            <v>1</v>
+          </cell>
+          <cell r="H4">
+            <v>0</v>
+          </cell>
+          <cell r="I4">
+            <v>0</v>
+          </cell>
+          <cell r="J4">
+            <v>0</v>
+          </cell>
+          <cell r="K4">
+            <v>1</v>
+          </cell>
+          <cell r="L4">
+            <v>0</v>
+          </cell>
+          <cell r="M4">
+            <v>0</v>
+          </cell>
+          <cell r="N4">
+            <v>0</v>
+          </cell>
+          <cell r="O4">
+            <v>0</v>
+          </cell>
+          <cell r="P4">
+            <v>0</v>
+          </cell>
+          <cell r="Q4">
+            <v>0</v>
+          </cell>
+          <cell r="R4">
+            <v>1</v>
+          </cell>
+          <cell r="S4">
+            <v>0</v>
+          </cell>
+          <cell r="T4">
+            <v>0</v>
+          </cell>
+          <cell r="U4">
+            <v>0</v>
+          </cell>
+          <cell r="V4">
+            <v>1</v>
+          </cell>
+          <cell r="W4">
+            <v>1</v>
+          </cell>
+          <cell r="X4">
+            <v>0</v>
+          </cell>
+          <cell r="Y4">
+            <v>0</v>
+          </cell>
+          <cell r="Z4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+          <cell r="B5">
+            <v>0</v>
+          </cell>
+          <cell r="C5">
+            <v>0</v>
+          </cell>
+          <cell r="D5">
+            <v>0</v>
+          </cell>
+          <cell r="E5">
+            <v>0</v>
+          </cell>
+          <cell r="F5">
+            <v>0</v>
+          </cell>
+          <cell r="G5">
+            <v>1</v>
+          </cell>
+          <cell r="H5">
+            <v>0</v>
+          </cell>
+          <cell r="I5">
+            <v>0</v>
+          </cell>
+          <cell r="J5">
+            <v>0</v>
+          </cell>
+          <cell r="K5">
+            <v>1</v>
+          </cell>
+          <cell r="L5">
+            <v>0</v>
+          </cell>
+          <cell r="M5">
+            <v>0</v>
+          </cell>
+          <cell r="N5">
+            <v>0</v>
+          </cell>
+          <cell r="O5">
+            <v>0</v>
+          </cell>
+          <cell r="P5">
+            <v>0</v>
+          </cell>
+          <cell r="Q5">
+            <v>0</v>
+          </cell>
+          <cell r="R5">
+            <v>0</v>
+          </cell>
+          <cell r="S5">
+            <v>1</v>
+          </cell>
+          <cell r="T5">
+            <v>0</v>
+          </cell>
+          <cell r="U5">
+            <v>0</v>
+          </cell>
+          <cell r="V5">
+            <v>1</v>
+          </cell>
+          <cell r="W5">
+            <v>1</v>
+          </cell>
+          <cell r="X5">
+            <v>0</v>
+          </cell>
+          <cell r="Y5">
+            <v>0</v>
+          </cell>
+          <cell r="Z5">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+          <cell r="B6">
+            <v>0</v>
+          </cell>
+          <cell r="C6">
+            <v>0</v>
+          </cell>
+          <cell r="D6">
+            <v>0</v>
+          </cell>
+          <cell r="E6">
+            <v>0</v>
+          </cell>
+          <cell r="F6">
+            <v>0</v>
+          </cell>
+          <cell r="G6">
+            <v>0</v>
+          </cell>
+          <cell r="H6">
+            <v>0</v>
+          </cell>
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+          <cell r="J6">
+            <v>0</v>
+          </cell>
+          <cell r="K6">
+            <v>1</v>
+          </cell>
+          <cell r="L6">
+            <v>1</v>
+          </cell>
+          <cell r="M6">
+            <v>0</v>
+          </cell>
+          <cell r="N6">
+            <v>0</v>
+          </cell>
+          <cell r="O6">
+            <v>0</v>
+          </cell>
+          <cell r="P6">
+            <v>0</v>
+          </cell>
+          <cell r="Q6">
+            <v>0</v>
+          </cell>
+          <cell r="R6">
+            <v>1</v>
+          </cell>
+          <cell r="S6">
+            <v>1</v>
+          </cell>
+          <cell r="T6">
+            <v>0</v>
+          </cell>
+          <cell r="U6">
+            <v>0</v>
+          </cell>
+          <cell r="V6">
+            <v>1</v>
+          </cell>
+          <cell r="W6">
+            <v>1</v>
+          </cell>
+          <cell r="X6">
+            <v>1</v>
+          </cell>
+          <cell r="Y6">
+            <v>0</v>
+          </cell>
+          <cell r="Z6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+          <cell r="B7">
+            <v>0</v>
+          </cell>
+          <cell r="C7">
+            <v>0</v>
+          </cell>
+          <cell r="D7">
+            <v>0</v>
+          </cell>
+          <cell r="E7">
+            <v>0</v>
+          </cell>
+          <cell r="F7">
+            <v>1</v>
+          </cell>
+          <cell r="G7">
+            <v>0</v>
+          </cell>
+          <cell r="H7">
+            <v>0</v>
+          </cell>
+          <cell r="I7">
+            <v>0</v>
+          </cell>
+          <cell r="J7">
+            <v>0</v>
+          </cell>
+          <cell r="K7">
+            <v>0</v>
+          </cell>
+          <cell r="L7">
+            <v>1</v>
+          </cell>
+          <cell r="M7">
+            <v>0</v>
+          </cell>
+          <cell r="N7">
+            <v>0</v>
+          </cell>
+          <cell r="O7">
+            <v>0</v>
+          </cell>
+          <cell r="P7">
+            <v>0</v>
+          </cell>
+          <cell r="Q7">
+            <v>0</v>
+          </cell>
+          <cell r="R7">
+            <v>1</v>
+          </cell>
+          <cell r="S7">
+            <v>1</v>
+          </cell>
+          <cell r="T7">
+            <v>0</v>
+          </cell>
+          <cell r="U7">
+            <v>0</v>
+          </cell>
+          <cell r="V7">
+            <v>2</v>
+          </cell>
+          <cell r="W7">
+            <v>2</v>
+          </cell>
+          <cell r="X7">
+            <v>0</v>
+          </cell>
+          <cell r="Y7">
+            <v>0</v>
+          </cell>
+          <cell r="Z7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+          <cell r="B8">
+            <v>0</v>
+          </cell>
+          <cell r="C8">
+            <v>0</v>
+          </cell>
+          <cell r="D8">
+            <v>0</v>
+          </cell>
+          <cell r="E8">
+            <v>0</v>
+          </cell>
+          <cell r="F8">
+            <v>1</v>
+          </cell>
+          <cell r="G8">
+            <v>0</v>
+          </cell>
+          <cell r="H8">
+            <v>0</v>
+          </cell>
+          <cell r="I8">
+            <v>0</v>
+          </cell>
+          <cell r="J8">
+            <v>0</v>
+          </cell>
+          <cell r="K8">
+            <v>1</v>
+          </cell>
+          <cell r="L8">
+            <v>1</v>
+          </cell>
+          <cell r="M8">
+            <v>0</v>
+          </cell>
+          <cell r="N8">
+            <v>0</v>
+          </cell>
+          <cell r="O8">
+            <v>0</v>
+          </cell>
+          <cell r="P8">
+            <v>0</v>
+          </cell>
+          <cell r="Q8">
+            <v>0</v>
+          </cell>
+          <cell r="R8">
+            <v>0</v>
+          </cell>
+          <cell r="S8">
+            <v>1</v>
+          </cell>
+          <cell r="T8">
+            <v>0</v>
+          </cell>
+          <cell r="U8">
+            <v>0</v>
+          </cell>
+          <cell r="V8">
+            <v>2</v>
+          </cell>
+          <cell r="W8">
+            <v>1</v>
+          </cell>
+          <cell r="X8">
+            <v>1</v>
+          </cell>
+          <cell r="Y8">
+            <v>0</v>
+          </cell>
+          <cell r="Z8">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+          <cell r="B9">
+            <v>0</v>
+          </cell>
+          <cell r="C9">
+            <v>0</v>
+          </cell>
+          <cell r="D9">
+            <v>0</v>
+          </cell>
+          <cell r="E9">
+            <v>0</v>
+          </cell>
+          <cell r="F9">
+            <v>2</v>
+          </cell>
+          <cell r="G9">
+            <v>0</v>
+          </cell>
+          <cell r="H9">
+            <v>0</v>
+          </cell>
+          <cell r="I9">
+            <v>0</v>
+          </cell>
+          <cell r="J9">
+            <v>0</v>
+          </cell>
+          <cell r="K9">
+            <v>1</v>
+          </cell>
+          <cell r="L9">
+            <v>1</v>
+          </cell>
+          <cell r="M9">
+            <v>0</v>
+          </cell>
+          <cell r="N9">
+            <v>0</v>
+          </cell>
+          <cell r="O9">
+            <v>0</v>
+          </cell>
+          <cell r="P9">
+            <v>0</v>
+          </cell>
+          <cell r="Q9">
+            <v>0</v>
+          </cell>
+          <cell r="R9">
+            <v>0</v>
+          </cell>
+          <cell r="S9">
+            <v>1</v>
+          </cell>
+          <cell r="T9">
+            <v>0</v>
+          </cell>
+          <cell r="U9">
+            <v>0</v>
+          </cell>
+          <cell r="V9">
+            <v>2</v>
+          </cell>
+          <cell r="W9">
+            <v>1</v>
+          </cell>
+          <cell r="X9">
+            <v>0</v>
+          </cell>
+          <cell r="Y9">
+            <v>0</v>
+          </cell>
+          <cell r="Z9">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+          <cell r="B10">
+            <v>0</v>
+          </cell>
+          <cell r="C10">
+            <v>0</v>
+          </cell>
+          <cell r="D10">
+            <v>0</v>
+          </cell>
+          <cell r="E10">
+            <v>0</v>
+          </cell>
+          <cell r="F10">
+            <v>1</v>
+          </cell>
+          <cell r="G10">
+            <v>0</v>
+          </cell>
+          <cell r="H10">
+            <v>0</v>
+          </cell>
+          <cell r="I10">
+            <v>0</v>
+          </cell>
+          <cell r="J10">
+            <v>0</v>
+          </cell>
+          <cell r="K10">
+            <v>1</v>
+          </cell>
+          <cell r="L10">
+            <v>0</v>
+          </cell>
+          <cell r="M10">
+            <v>0</v>
+          </cell>
+          <cell r="N10">
+            <v>0</v>
+          </cell>
+          <cell r="O10">
+            <v>0</v>
+          </cell>
+          <cell r="P10">
+            <v>0</v>
+          </cell>
+          <cell r="Q10">
+            <v>1</v>
+          </cell>
+          <cell r="R10">
+            <v>0</v>
+          </cell>
+          <cell r="S10">
+            <v>1</v>
+          </cell>
+          <cell r="T10">
+            <v>0</v>
+          </cell>
+          <cell r="U10">
+            <v>0</v>
+          </cell>
+          <cell r="V10">
+            <v>1</v>
+          </cell>
+          <cell r="W10">
+            <v>1</v>
+          </cell>
+          <cell r="X10">
+            <v>1</v>
+          </cell>
+          <cell r="Y10">
+            <v>0</v>
+          </cell>
+          <cell r="Z10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+          <cell r="B11">
+            <v>0</v>
+          </cell>
+          <cell r="C11">
+            <v>0</v>
+          </cell>
+          <cell r="D11">
+            <v>0</v>
+          </cell>
+          <cell r="E11">
+            <v>0</v>
+          </cell>
+          <cell r="F11">
+            <v>3</v>
+          </cell>
+          <cell r="G11">
+            <v>0</v>
+          </cell>
+          <cell r="H11">
+            <v>0</v>
+          </cell>
+          <cell r="I11">
+            <v>0</v>
+          </cell>
+          <cell r="J11">
+            <v>0</v>
+          </cell>
+          <cell r="K11">
+            <v>1</v>
+          </cell>
+          <cell r="L11">
+            <v>0</v>
+          </cell>
+          <cell r="M11">
+            <v>0</v>
+          </cell>
+          <cell r="N11">
+            <v>0</v>
+          </cell>
+          <cell r="O11">
+            <v>0</v>
+          </cell>
+          <cell r="P11">
+            <v>0</v>
+          </cell>
+          <cell r="Q11">
+            <v>0</v>
+          </cell>
+          <cell r="R11">
+            <v>0</v>
+          </cell>
+          <cell r="S11">
+            <v>1</v>
+          </cell>
+          <cell r="T11">
+            <v>0</v>
+          </cell>
+          <cell r="U11">
+            <v>0</v>
+          </cell>
+          <cell r="V11">
+            <v>1</v>
+          </cell>
+          <cell r="W11">
+            <v>1</v>
+          </cell>
+          <cell r="X11">
+            <v>1</v>
+          </cell>
+          <cell r="Y11">
+            <v>0</v>
+          </cell>
+          <cell r="Z11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+          <cell r="B12">
+            <v>0</v>
+          </cell>
+          <cell r="C12">
+            <v>0</v>
+          </cell>
+          <cell r="D12">
+            <v>0</v>
+          </cell>
+          <cell r="E12">
+            <v>1</v>
+          </cell>
+          <cell r="F12">
+            <v>1</v>
+          </cell>
+          <cell r="G12">
+            <v>0</v>
+          </cell>
+          <cell r="H12">
+            <v>0</v>
+          </cell>
+          <cell r="I12">
+            <v>0</v>
+          </cell>
+          <cell r="J12">
+            <v>0</v>
+          </cell>
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+          <cell r="L12">
+            <v>1</v>
+          </cell>
+          <cell r="M12">
+            <v>0</v>
+          </cell>
+          <cell r="N12">
+            <v>0</v>
+          </cell>
+          <cell r="O12">
+            <v>0</v>
+          </cell>
+          <cell r="P12">
+            <v>0</v>
+          </cell>
+          <cell r="Q12">
+            <v>0</v>
+          </cell>
+          <cell r="R12">
+            <v>0</v>
+          </cell>
+          <cell r="S12">
+            <v>0</v>
+          </cell>
+          <cell r="T12">
+            <v>0</v>
+          </cell>
+          <cell r="U12">
+            <v>0</v>
+          </cell>
+          <cell r="V12">
+            <v>1</v>
+          </cell>
+          <cell r="W12">
+            <v>1</v>
+          </cell>
+          <cell r="X12">
+            <v>1</v>
+          </cell>
+          <cell r="Y12">
+            <v>0</v>
+          </cell>
+          <cell r="Z12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+          <cell r="B13">
+            <v>0</v>
+          </cell>
+          <cell r="C13">
+            <v>0</v>
+          </cell>
+          <cell r="D13">
+            <v>0</v>
+          </cell>
+          <cell r="E13">
+            <v>0</v>
+          </cell>
+          <cell r="F13">
+            <v>1</v>
+          </cell>
+          <cell r="G13">
+            <v>0</v>
+          </cell>
+          <cell r="H13">
+            <v>0</v>
+          </cell>
+          <cell r="I13">
+            <v>0</v>
+          </cell>
+          <cell r="J13">
+            <v>0</v>
+          </cell>
+          <cell r="K13">
+            <v>2</v>
+          </cell>
+          <cell r="L13">
+            <v>0</v>
+          </cell>
+          <cell r="M13">
+            <v>0</v>
+          </cell>
+          <cell r="N13">
+            <v>0</v>
+          </cell>
+          <cell r="O13">
+            <v>0</v>
+          </cell>
+          <cell r="P13">
+            <v>0</v>
+          </cell>
+          <cell r="Q13">
+            <v>0</v>
+          </cell>
+          <cell r="R13">
+            <v>0</v>
+          </cell>
+          <cell r="S13">
+            <v>1</v>
+          </cell>
+          <cell r="T13">
+            <v>0</v>
+          </cell>
+          <cell r="U13">
+            <v>0</v>
+          </cell>
+          <cell r="V13">
+            <v>1</v>
+          </cell>
+          <cell r="W13">
+            <v>2</v>
+          </cell>
+          <cell r="X13">
+            <v>0</v>
+          </cell>
+          <cell r="Y13">
+            <v>0</v>
+          </cell>
+          <cell r="Z13">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+          <cell r="B14">
+            <v>0</v>
+          </cell>
+          <cell r="C14">
+            <v>0</v>
+          </cell>
+          <cell r="D14">
+            <v>0</v>
+          </cell>
+          <cell r="E14">
+            <v>0</v>
+          </cell>
+          <cell r="F14">
+            <v>1</v>
+          </cell>
+          <cell r="G14">
+            <v>0</v>
+          </cell>
+          <cell r="H14">
+            <v>0</v>
+          </cell>
+          <cell r="I14">
+            <v>0</v>
+          </cell>
+          <cell r="J14">
+            <v>0</v>
+          </cell>
+          <cell r="K14">
+            <v>1</v>
+          </cell>
+          <cell r="L14">
+            <v>0</v>
+          </cell>
+          <cell r="M14">
+            <v>0</v>
+          </cell>
+          <cell r="N14">
+            <v>0</v>
+          </cell>
+          <cell r="O14">
+            <v>0</v>
+          </cell>
+          <cell r="P14">
+            <v>0</v>
+          </cell>
+          <cell r="Q14">
+            <v>0</v>
+          </cell>
+          <cell r="R14">
+            <v>0</v>
+          </cell>
+          <cell r="S14">
+            <v>1</v>
+          </cell>
+          <cell r="T14">
+            <v>0</v>
+          </cell>
+          <cell r="U14">
+            <v>0</v>
+          </cell>
+          <cell r="V14">
+            <v>1</v>
+          </cell>
+          <cell r="W14">
+            <v>1</v>
+          </cell>
+          <cell r="X14">
+            <v>0</v>
+          </cell>
+          <cell r="Y14">
+            <v>0</v>
+          </cell>
+          <cell r="Z14">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+          <cell r="B15">
+            <v>0</v>
+          </cell>
+          <cell r="C15">
+            <v>0</v>
+          </cell>
+          <cell r="D15">
+            <v>0</v>
+          </cell>
+          <cell r="E15">
+            <v>0</v>
+          </cell>
+          <cell r="F15">
+            <v>1</v>
+          </cell>
+          <cell r="G15">
+            <v>0</v>
+          </cell>
+          <cell r="H15">
+            <v>0</v>
+          </cell>
+          <cell r="I15">
+            <v>0</v>
+          </cell>
+          <cell r="J15">
+            <v>0</v>
+          </cell>
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+          <cell r="L15">
+            <v>0</v>
+          </cell>
+          <cell r="M15">
+            <v>0</v>
+          </cell>
+          <cell r="N15">
+            <v>0</v>
+          </cell>
+          <cell r="O15">
+            <v>0</v>
+          </cell>
+          <cell r="P15">
+            <v>0</v>
+          </cell>
+          <cell r="Q15">
+            <v>0</v>
+          </cell>
+          <cell r="R15">
+            <v>0</v>
+          </cell>
+          <cell r="S15">
+            <v>2</v>
+          </cell>
+          <cell r="T15">
+            <v>0</v>
+          </cell>
+          <cell r="U15">
+            <v>0</v>
+          </cell>
+          <cell r="V15">
+            <v>1</v>
+          </cell>
+          <cell r="W15">
+            <v>1</v>
+          </cell>
+          <cell r="X15">
+            <v>1</v>
+          </cell>
+          <cell r="Y15">
+            <v>0</v>
+          </cell>
+          <cell r="Z15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+          <cell r="B16">
+            <v>0</v>
+          </cell>
+          <cell r="C16">
+            <v>0</v>
+          </cell>
+          <cell r="D16">
+            <v>0</v>
+          </cell>
+          <cell r="E16">
+            <v>0</v>
+          </cell>
+          <cell r="F16">
+            <v>1</v>
+          </cell>
+          <cell r="G16">
+            <v>0</v>
+          </cell>
+          <cell r="H16">
+            <v>0</v>
+          </cell>
+          <cell r="I16">
+            <v>0</v>
+          </cell>
+          <cell r="J16">
+            <v>0</v>
+          </cell>
+          <cell r="K16">
+            <v>0</v>
+          </cell>
+          <cell r="L16">
+            <v>0</v>
+          </cell>
+          <cell r="M16">
+            <v>0</v>
+          </cell>
+          <cell r="N16">
+            <v>0</v>
+          </cell>
+          <cell r="O16">
+            <v>0</v>
+          </cell>
+          <cell r="P16">
+            <v>0</v>
+          </cell>
+          <cell r="Q16">
+            <v>1</v>
+          </cell>
+          <cell r="R16">
+            <v>0</v>
+          </cell>
+          <cell r="S16">
+            <v>1</v>
+          </cell>
+          <cell r="T16">
+            <v>0</v>
+          </cell>
+          <cell r="U16">
+            <v>0</v>
+          </cell>
+          <cell r="V16">
+            <v>1</v>
+          </cell>
+          <cell r="W16">
+            <v>1</v>
+          </cell>
+          <cell r="X16">
+            <v>0</v>
+          </cell>
+          <cell r="Y16">
+            <v>0</v>
+          </cell>
+          <cell r="Z16">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+          <cell r="B17">
+            <v>0</v>
+          </cell>
+          <cell r="C17">
+            <v>0</v>
+          </cell>
+          <cell r="D17">
+            <v>0</v>
+          </cell>
+          <cell r="E17">
+            <v>0</v>
+          </cell>
+          <cell r="F17">
+            <v>0</v>
+          </cell>
+          <cell r="G17">
+            <v>0</v>
+          </cell>
+          <cell r="H17">
+            <v>0</v>
+          </cell>
+          <cell r="I17">
+            <v>0</v>
+          </cell>
+          <cell r="J17">
+            <v>0</v>
+          </cell>
+          <cell r="K17">
+            <v>0</v>
+          </cell>
+          <cell r="L17">
+            <v>0</v>
+          </cell>
+          <cell r="M17">
+            <v>0</v>
+          </cell>
+          <cell r="N17">
+            <v>0</v>
+          </cell>
+          <cell r="O17">
+            <v>0</v>
+          </cell>
+          <cell r="P17">
+            <v>0</v>
+          </cell>
+          <cell r="Q17">
+            <v>0</v>
+          </cell>
+          <cell r="R17">
+            <v>1</v>
+          </cell>
+          <cell r="S17">
+            <v>1</v>
+          </cell>
+          <cell r="T17">
+            <v>0</v>
+          </cell>
+          <cell r="U17">
+            <v>0</v>
+          </cell>
+          <cell r="V17">
+            <v>0</v>
+          </cell>
+          <cell r="W17">
+            <v>1</v>
+          </cell>
+          <cell r="X17">
+            <v>1</v>
+          </cell>
+          <cell r="Y17">
+            <v>0</v>
+          </cell>
+          <cell r="Z17">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+          <cell r="B18">
+            <v>0</v>
+          </cell>
+          <cell r="C18">
+            <v>0</v>
+          </cell>
+          <cell r="D18">
+            <v>0</v>
+          </cell>
+          <cell r="E18">
+            <v>0</v>
+          </cell>
+          <cell r="F18">
+            <v>1</v>
+          </cell>
+          <cell r="G18">
+            <v>0</v>
+          </cell>
+          <cell r="H18">
+            <v>0</v>
+          </cell>
+          <cell r="I18">
+            <v>0</v>
+          </cell>
+          <cell r="J18">
+            <v>0</v>
+          </cell>
+          <cell r="K18">
+            <v>0</v>
+          </cell>
+          <cell r="L18">
+            <v>1</v>
+          </cell>
+          <cell r="M18">
+            <v>0</v>
+          </cell>
+          <cell r="N18">
+            <v>0</v>
+          </cell>
+          <cell r="O18">
+            <v>0</v>
+          </cell>
+          <cell r="P18">
+            <v>0</v>
+          </cell>
+          <cell r="Q18">
+            <v>0</v>
+          </cell>
+          <cell r="R18">
+            <v>1</v>
+          </cell>
+          <cell r="S18">
+            <v>0</v>
+          </cell>
+          <cell r="T18">
+            <v>0</v>
+          </cell>
+          <cell r="U18">
+            <v>0</v>
+          </cell>
+          <cell r="V18">
+            <v>1</v>
+          </cell>
+          <cell r="W18">
+            <v>2</v>
+          </cell>
+          <cell r="X18">
+            <v>1</v>
+          </cell>
+          <cell r="Y18">
+            <v>0</v>
+          </cell>
+          <cell r="Z18">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+          <cell r="B19">
+            <v>0</v>
+          </cell>
+          <cell r="C19">
+            <v>0</v>
+          </cell>
+          <cell r="D19">
+            <v>0</v>
+          </cell>
+          <cell r="E19">
+            <v>0</v>
+          </cell>
+          <cell r="F19">
+            <v>0</v>
+          </cell>
+          <cell r="G19">
+            <v>0</v>
+          </cell>
+          <cell r="H19">
+            <v>0</v>
+          </cell>
+          <cell r="I19">
+            <v>0</v>
+          </cell>
+          <cell r="J19">
+            <v>0</v>
+          </cell>
+          <cell r="K19">
+            <v>0</v>
+          </cell>
+          <cell r="L19">
+            <v>0</v>
+          </cell>
+          <cell r="M19">
+            <v>0</v>
+          </cell>
+          <cell r="N19">
+            <v>0</v>
+          </cell>
+          <cell r="O19">
+            <v>0</v>
+          </cell>
+          <cell r="P19">
+            <v>0</v>
+          </cell>
+          <cell r="Q19">
+            <v>1</v>
+          </cell>
+          <cell r="R19">
+            <v>0</v>
+          </cell>
+          <cell r="S19">
+            <v>0</v>
+          </cell>
+          <cell r="T19">
+            <v>0</v>
+          </cell>
+          <cell r="U19">
+            <v>0</v>
+          </cell>
+          <cell r="V19">
+            <v>1</v>
+          </cell>
+          <cell r="W19">
+            <v>1</v>
+          </cell>
+          <cell r="X19">
+            <v>1</v>
+          </cell>
+          <cell r="Y19">
+            <v>0</v>
+          </cell>
+          <cell r="Z19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+          <cell r="B20">
+            <v>0</v>
+          </cell>
+          <cell r="C20">
+            <v>0</v>
+          </cell>
+          <cell r="D20">
+            <v>0</v>
+          </cell>
+          <cell r="E20">
+            <v>0</v>
+          </cell>
+          <cell r="F20">
+            <v>0</v>
+          </cell>
+          <cell r="G20">
+            <v>0</v>
+          </cell>
+          <cell r="H20">
+            <v>0</v>
+          </cell>
+          <cell r="I20">
+            <v>0</v>
+          </cell>
+          <cell r="J20">
+            <v>0</v>
+          </cell>
+          <cell r="K20">
+            <v>0</v>
+          </cell>
+          <cell r="L20">
+            <v>0</v>
+          </cell>
+          <cell r="M20">
+            <v>0</v>
+          </cell>
+          <cell r="N20">
+            <v>0</v>
+          </cell>
+          <cell r="O20">
+            <v>0</v>
+          </cell>
+          <cell r="P20">
+            <v>0</v>
+          </cell>
+          <cell r="Q20">
+            <v>0</v>
+          </cell>
+          <cell r="R20">
+            <v>1</v>
+          </cell>
+          <cell r="S20">
+            <v>1</v>
+          </cell>
+          <cell r="T20">
+            <v>0</v>
+          </cell>
+          <cell r="U20">
+            <v>0</v>
+          </cell>
+          <cell r="V20">
+            <v>1</v>
+          </cell>
+          <cell r="W20">
+            <v>1</v>
+          </cell>
+          <cell r="X20">
+            <v>1</v>
+          </cell>
+          <cell r="Y20">
+            <v>0</v>
+          </cell>
+          <cell r="Z20">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>20</v>
+          </cell>
+          <cell r="B21">
+            <v>0</v>
+          </cell>
+          <cell r="C21">
+            <v>0</v>
+          </cell>
+          <cell r="D21">
+            <v>0</v>
+          </cell>
+          <cell r="E21">
+            <v>0</v>
+          </cell>
+          <cell r="F21">
+            <v>0</v>
+          </cell>
+          <cell r="G21">
+            <v>1</v>
+          </cell>
+          <cell r="H21">
+            <v>0</v>
+          </cell>
+          <cell r="I21">
+            <v>0</v>
+          </cell>
+          <cell r="J21">
+            <v>0</v>
+          </cell>
+          <cell r="K21">
+            <v>1</v>
+          </cell>
+          <cell r="L21">
+            <v>1</v>
+          </cell>
+          <cell r="M21">
+            <v>0</v>
+          </cell>
+          <cell r="N21">
+            <v>0</v>
+          </cell>
+          <cell r="O21">
+            <v>0</v>
+          </cell>
+          <cell r="P21">
+            <v>0</v>
+          </cell>
+          <cell r="Q21">
+            <v>0</v>
+          </cell>
+          <cell r="R21">
+            <v>0</v>
+          </cell>
+          <cell r="S21">
+            <v>1</v>
+          </cell>
+          <cell r="T21">
+            <v>1</v>
+          </cell>
+          <cell r="U21">
+            <v>0</v>
+          </cell>
+          <cell r="V21">
+            <v>1</v>
+          </cell>
+          <cell r="W21">
+            <v>1</v>
+          </cell>
+          <cell r="X21">
+            <v>1</v>
+          </cell>
+          <cell r="Y21">
+            <v>0</v>
+          </cell>
+          <cell r="Z21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>21</v>
+          </cell>
+          <cell r="B22">
+            <v>0</v>
+          </cell>
+          <cell r="C22">
+            <v>0</v>
+          </cell>
+          <cell r="D22">
+            <v>0</v>
+          </cell>
+          <cell r="E22">
+            <v>0</v>
+          </cell>
+          <cell r="F22">
+            <v>0</v>
+          </cell>
+          <cell r="G22">
+            <v>0</v>
+          </cell>
+          <cell r="H22">
+            <v>0</v>
+          </cell>
+          <cell r="I22">
+            <v>0</v>
+          </cell>
+          <cell r="J22">
+            <v>0</v>
+          </cell>
+          <cell r="K22">
+            <v>0</v>
+          </cell>
+          <cell r="L22">
+            <v>1</v>
+          </cell>
+          <cell r="M22">
+            <v>0</v>
+          </cell>
+          <cell r="N22">
+            <v>0</v>
+          </cell>
+          <cell r="O22">
+            <v>0</v>
+          </cell>
+          <cell r="P22">
+            <v>0</v>
+          </cell>
+          <cell r="Q22">
+            <v>0</v>
+          </cell>
+          <cell r="R22">
+            <v>1</v>
+          </cell>
+          <cell r="S22">
+            <v>0</v>
+          </cell>
+          <cell r="T22">
+            <v>0</v>
+          </cell>
+          <cell r="U22">
+            <v>0</v>
+          </cell>
+          <cell r="V22">
+            <v>1</v>
+          </cell>
+          <cell r="W22">
+            <v>1</v>
+          </cell>
+          <cell r="X22">
+            <v>1</v>
+          </cell>
+          <cell r="Y22">
+            <v>0</v>
+          </cell>
+          <cell r="Z22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>22</v>
+          </cell>
+          <cell r="B23">
+            <v>0</v>
+          </cell>
+          <cell r="C23">
+            <v>0</v>
+          </cell>
+          <cell r="D23">
+            <v>0</v>
+          </cell>
+          <cell r="E23">
+            <v>0</v>
+          </cell>
+          <cell r="F23">
+            <v>0</v>
+          </cell>
+          <cell r="G23">
+            <v>0</v>
+          </cell>
+          <cell r="H23">
+            <v>0</v>
+          </cell>
+          <cell r="I23">
+            <v>0</v>
+          </cell>
+          <cell r="J23">
+            <v>0</v>
+          </cell>
+          <cell r="K23">
+            <v>0</v>
+          </cell>
+          <cell r="L23">
+            <v>0</v>
+          </cell>
+          <cell r="M23">
+            <v>0</v>
+          </cell>
+          <cell r="N23">
+            <v>0</v>
+          </cell>
+          <cell r="O23">
+            <v>0</v>
+          </cell>
+          <cell r="P23">
+            <v>0</v>
+          </cell>
+          <cell r="Q23">
+            <v>1</v>
+          </cell>
+          <cell r="R23">
+            <v>0</v>
+          </cell>
+          <cell r="S23">
+            <v>0</v>
+          </cell>
+          <cell r="T23">
+            <v>0</v>
+          </cell>
+          <cell r="U23">
+            <v>0</v>
+          </cell>
+          <cell r="V23">
+            <v>1</v>
+          </cell>
+          <cell r="W23">
+            <v>1</v>
+          </cell>
+          <cell r="X23">
+            <v>1</v>
+          </cell>
+          <cell r="Y23">
+            <v>0</v>
+          </cell>
+          <cell r="Z23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>23</v>
+          </cell>
+          <cell r="B24">
+            <v>0</v>
+          </cell>
+          <cell r="C24">
+            <v>0</v>
+          </cell>
+          <cell r="D24">
+            <v>0</v>
+          </cell>
+          <cell r="E24">
+            <v>0</v>
+          </cell>
+          <cell r="F24">
+            <v>1</v>
+          </cell>
+          <cell r="G24">
+            <v>0</v>
+          </cell>
+          <cell r="H24">
+            <v>0</v>
+          </cell>
+          <cell r="I24">
+            <v>0</v>
+          </cell>
+          <cell r="J24">
+            <v>0</v>
+          </cell>
+          <cell r="K24">
+            <v>0</v>
+          </cell>
+          <cell r="L24">
+            <v>0</v>
+          </cell>
+          <cell r="M24">
+            <v>0</v>
+          </cell>
+          <cell r="N24">
+            <v>0</v>
+          </cell>
+          <cell r="O24">
+            <v>0</v>
+          </cell>
+          <cell r="P24">
+            <v>0</v>
+          </cell>
+          <cell r="Q24">
+            <v>1</v>
+          </cell>
+          <cell r="R24">
+            <v>1</v>
+          </cell>
+          <cell r="S24">
+            <v>0</v>
+          </cell>
+          <cell r="T24">
+            <v>0</v>
+          </cell>
+          <cell r="U24">
+            <v>0</v>
+          </cell>
+          <cell r="V24">
+            <v>1</v>
+          </cell>
+          <cell r="W24">
+            <v>2</v>
+          </cell>
+          <cell r="X24">
+            <v>1</v>
+          </cell>
+          <cell r="Y24">
+            <v>0</v>
+          </cell>
+          <cell r="Z24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>24</v>
+          </cell>
+          <cell r="B25">
+            <v>0</v>
+          </cell>
+          <cell r="C25">
+            <v>0</v>
+          </cell>
+          <cell r="D25">
+            <v>0</v>
+          </cell>
+          <cell r="E25">
+            <v>0</v>
+          </cell>
+          <cell r="F25">
+            <v>1</v>
+          </cell>
+          <cell r="G25">
+            <v>0</v>
+          </cell>
+          <cell r="H25">
+            <v>0</v>
+          </cell>
+          <cell r="I25">
+            <v>0</v>
+          </cell>
+          <cell r="J25">
+            <v>0</v>
+          </cell>
+          <cell r="K25">
+            <v>0</v>
+          </cell>
+          <cell r="L25">
+            <v>0</v>
+          </cell>
+          <cell r="M25">
+            <v>0</v>
+          </cell>
+          <cell r="N25">
+            <v>0</v>
+          </cell>
+          <cell r="O25">
+            <v>0</v>
+          </cell>
+          <cell r="P25">
+            <v>0</v>
+          </cell>
+          <cell r="Q25">
+            <v>1</v>
+          </cell>
+          <cell r="R25">
+            <v>0</v>
+          </cell>
+          <cell r="S25">
+            <v>1</v>
+          </cell>
+          <cell r="T25">
+            <v>0</v>
+          </cell>
+          <cell r="U25">
+            <v>0</v>
+          </cell>
+          <cell r="V25">
+            <v>1</v>
+          </cell>
+          <cell r="W25">
+            <v>1</v>
+          </cell>
+          <cell r="X25">
+            <v>0</v>
+          </cell>
+          <cell r="Y25">
+            <v>0</v>
+          </cell>
+          <cell r="Z25">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>25</v>
+          </cell>
+          <cell r="B26">
+            <v>0</v>
+          </cell>
+          <cell r="C26">
+            <v>0</v>
+          </cell>
+          <cell r="D26">
+            <v>0</v>
+          </cell>
+          <cell r="E26">
+            <v>0</v>
+          </cell>
+          <cell r="F26">
+            <v>0</v>
+          </cell>
+          <cell r="G26">
+            <v>0</v>
+          </cell>
+          <cell r="H26">
+            <v>0</v>
+          </cell>
+          <cell r="I26">
+            <v>0</v>
+          </cell>
+          <cell r="J26">
+            <v>0</v>
+          </cell>
+          <cell r="K26">
+            <v>0</v>
+          </cell>
+          <cell r="L26">
+            <v>1</v>
+          </cell>
+          <cell r="M26">
+            <v>0</v>
+          </cell>
+          <cell r="N26">
+            <v>0</v>
+          </cell>
+          <cell r="O26">
+            <v>0</v>
+          </cell>
+          <cell r="P26">
+            <v>0</v>
+          </cell>
+          <cell r="Q26">
+            <v>0</v>
+          </cell>
+          <cell r="R26">
+            <v>0</v>
+          </cell>
+          <cell r="S26">
+            <v>1</v>
+          </cell>
+          <cell r="T26">
+            <v>0</v>
+          </cell>
+          <cell r="U26">
+            <v>0</v>
+          </cell>
+          <cell r="V26">
+            <v>1</v>
+          </cell>
+          <cell r="W26">
+            <v>1</v>
+          </cell>
+          <cell r="X26">
+            <v>0</v>
+          </cell>
+          <cell r="Y26">
+            <v>0</v>
+          </cell>
+          <cell r="Z26">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>26</v>
+          </cell>
+          <cell r="B27">
+            <v>0</v>
+          </cell>
+          <cell r="C27">
+            <v>0</v>
+          </cell>
+          <cell r="D27">
+            <v>0</v>
+          </cell>
+          <cell r="E27">
+            <v>0</v>
+          </cell>
+          <cell r="F27">
+            <v>0</v>
+          </cell>
+          <cell r="G27">
+            <v>0</v>
+          </cell>
+          <cell r="H27">
+            <v>0</v>
+          </cell>
+          <cell r="I27">
+            <v>0</v>
+          </cell>
+          <cell r="J27">
+            <v>0</v>
+          </cell>
+          <cell r="K27">
+            <v>0</v>
+          </cell>
+          <cell r="L27">
+            <v>1</v>
+          </cell>
+          <cell r="M27">
+            <v>0</v>
+          </cell>
+          <cell r="N27">
+            <v>0</v>
+          </cell>
+          <cell r="O27">
+            <v>0</v>
+          </cell>
+          <cell r="P27">
+            <v>0</v>
+          </cell>
+          <cell r="Q27">
+            <v>0</v>
+          </cell>
+          <cell r="R27">
+            <v>0</v>
+          </cell>
+          <cell r="S27">
+            <v>1</v>
+          </cell>
+          <cell r="T27">
+            <v>0</v>
+          </cell>
+          <cell r="U27">
+            <v>0</v>
+          </cell>
+          <cell r="V27">
+            <v>1</v>
+          </cell>
+          <cell r="W27">
+            <v>1</v>
+          </cell>
+          <cell r="X27">
+            <v>1</v>
+          </cell>
+          <cell r="Y27">
+            <v>0</v>
+          </cell>
+          <cell r="Z27">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>27</v>
+          </cell>
+          <cell r="B28">
+            <v>0</v>
+          </cell>
+          <cell r="C28">
+            <v>0</v>
+          </cell>
+          <cell r="D28">
+            <v>0</v>
+          </cell>
+          <cell r="E28">
+            <v>0</v>
+          </cell>
+          <cell r="F28">
+            <v>0</v>
+          </cell>
+          <cell r="G28">
+            <v>0</v>
+          </cell>
+          <cell r="H28">
+            <v>0</v>
+          </cell>
+          <cell r="I28">
+            <v>0</v>
+          </cell>
+          <cell r="J28">
+            <v>0</v>
+          </cell>
+          <cell r="K28">
+            <v>0</v>
+          </cell>
+          <cell r="L28">
+            <v>1</v>
+          </cell>
+          <cell r="M28">
+            <v>0</v>
+          </cell>
+          <cell r="N28">
+            <v>0</v>
+          </cell>
+          <cell r="O28">
+            <v>0</v>
+          </cell>
+          <cell r="P28">
+            <v>0</v>
+          </cell>
+          <cell r="Q28">
+            <v>0</v>
+          </cell>
+          <cell r="R28">
+            <v>0</v>
+          </cell>
+          <cell r="S28">
+            <v>0</v>
+          </cell>
+          <cell r="T28">
+            <v>0</v>
+          </cell>
+          <cell r="U28">
+            <v>0</v>
+          </cell>
+          <cell r="V28">
+            <v>0</v>
+          </cell>
+          <cell r="W28">
+            <v>1</v>
+          </cell>
+          <cell r="X28">
+            <v>1</v>
+          </cell>
+          <cell r="Y28">
+            <v>0</v>
+          </cell>
+          <cell r="Z28">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>28</v>
+          </cell>
+          <cell r="B29">
+            <v>0</v>
+          </cell>
+          <cell r="C29">
+            <v>0</v>
+          </cell>
+          <cell r="D29">
+            <v>0</v>
+          </cell>
+          <cell r="E29">
+            <v>0</v>
+          </cell>
+          <cell r="F29">
+            <v>0</v>
+          </cell>
+          <cell r="G29">
+            <v>0</v>
+          </cell>
+          <cell r="H29">
+            <v>0</v>
+          </cell>
+          <cell r="I29">
+            <v>1</v>
+          </cell>
+          <cell r="J29">
+            <v>0</v>
+          </cell>
+          <cell r="K29">
+            <v>0</v>
+          </cell>
+          <cell r="L29">
+            <v>0</v>
+          </cell>
+          <cell r="M29">
+            <v>0</v>
+          </cell>
+          <cell r="N29">
+            <v>0</v>
+          </cell>
+          <cell r="O29">
+            <v>0</v>
+          </cell>
+          <cell r="P29">
+            <v>0</v>
+          </cell>
+          <cell r="Q29">
+            <v>0</v>
+          </cell>
+          <cell r="R29">
+            <v>0</v>
+          </cell>
+          <cell r="S29">
+            <v>1</v>
+          </cell>
+          <cell r="T29">
+            <v>0</v>
+          </cell>
+          <cell r="U29">
+            <v>0</v>
+          </cell>
+          <cell r="V29">
+            <v>0</v>
+          </cell>
+          <cell r="W29">
+            <v>1</v>
+          </cell>
+          <cell r="X29">
+            <v>0</v>
+          </cell>
+          <cell r="Y29">
+            <v>0</v>
+          </cell>
+          <cell r="Z29">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -45773,7 +50454,7 @@
       <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
+      <sheetData sheetId="0">
         <row r="1">
           <cell r="A1" t="str">
             <v>Distrito</v>
@@ -48110,7 +52791,7 @@
       <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
+      <sheetData sheetId="0">
         <row r="1">
           <cell r="A1" t="str">
             <v>Distrito</v>
@@ -50447,7 +55128,7 @@
       <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
+      <sheetData sheetId="0">
         <row r="1">
           <cell r="A1" t="str">
             <v>Distrito</v>
@@ -52784,7 +57465,7 @@
       <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
+      <sheetData sheetId="0">
         <row r="1">
           <cell r="A1" t="str">
             <v>Distrito</v>
@@ -57410,14 +62091,14 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E45570FC-AD57-4C4E-AD9C-A3B1E85C5742}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="5.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6328125" customWidth="1"/>
     <col min="10" max="10" width="16.26953125" customWidth="1"/>
     <col min="11" max="11" width="44.08984375" customWidth="1"/>
   </cols>
@@ -57478,28 +62159,28 @@
         <v>29</v>
       </c>
       <c r="C4" s="8">
-        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>9.0066017788393002E-2</v>
+        <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <v>9.0928837999999998E-2</v>
       </c>
       <c r="D4" s="8">
-        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>8.1391535927221606E-2</v>
+        <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <v>8.0669268000000002E-2</v>
       </c>
       <c r="E4" s="8">
-        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>9.0351092923415893E-2</v>
+        <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <v>9.2068584999999994E-2</v>
       </c>
       <c r="F4" s="8">
-        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>4.5703230876148103E-2</v>
+        <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <v>4.5647593E-2</v>
       </c>
       <c r="G4" s="8">
-        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>0.10105248853606499</v>
+        <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <v>9.9967991000000006E-2</v>
       </c>
       <c r="H4" s="8">
-        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>9.9342776262546797E-2</v>
+        <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <v>0.10105185999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -57507,27 +62188,27 @@
         <v>2</v>
       </c>
       <c r="C5" s="6">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[13]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[13]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D5" s="6">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[13]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[13]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E5" s="6">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[13]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[13]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F5" s="6">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[13]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[13]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G5" s="6">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[13]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[13]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H5" s="6">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[13]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[13]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -57536,27 +62217,27 @@
         <v>3</v>
       </c>
       <c r="C6" s="6">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[14]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[14]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D6" s="6">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[14]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[14]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E6" s="6">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[14]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[14]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F6" s="6">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[14]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[14]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G6" s="6">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[14]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[14]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H6" s="6">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[14]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[14]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -57565,27 +62246,27 @@
         <v>4</v>
       </c>
       <c r="C7" s="6">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[15]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[15]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D7" s="6">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[15]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[15]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E7" s="6">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[15]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[15]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F7" s="6">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[15]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[15]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G7" s="6">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[15]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[15]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H7" s="6">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[15]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[15]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -57594,27 +62275,27 @@
         <v>5</v>
       </c>
       <c r="C8" s="6">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[16]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[16]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D8" s="6">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[16]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[16]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E8" s="6">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[16]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[16]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F8" s="6">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[16]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[16]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G8" s="6">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[16]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[16]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H8" s="6">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[16]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[16]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -57623,27 +62304,27 @@
         <v>31</v>
       </c>
       <c r="C9" s="6">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[17]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[17]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D9" s="6">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[17]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[17]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E9" s="6">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[17]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[17]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F9" s="6">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[17]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[17]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G9" s="6">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[17]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[17]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H9" s="6">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[17]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[17]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -57652,27 +62333,27 @@
         <v>32</v>
       </c>
       <c r="C10" s="6">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[18]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[18]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D10" s="6">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[18]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[18]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E10" s="6">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[18]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[18]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F10" s="6">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[18]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[18]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G10" s="6">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[18]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[18]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H10" s="6">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[18]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[18]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -57681,27 +62362,27 @@
         <v>33</v>
       </c>
       <c r="C11" s="6">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[19]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[19]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D11" s="6">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[19]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[19]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E11" s="6">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[19]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[19]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F11" s="6">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[19]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[19]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G11" s="6">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[19]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[19]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H11" s="6">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[19]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[19]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -57710,27 +62391,27 @@
         <v>34</v>
       </c>
       <c r="C12" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[20]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[20]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D12" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[20]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[20]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E12" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[20]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[20]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F12" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[20]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[20]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G12" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[20]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[20]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H12" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[20]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[20]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -57739,27 +62420,27 @@
         <v>77</v>
       </c>
       <c r="C13" s="6">
-        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[21]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[21]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D13" s="6">
-        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[21]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[21]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E13" s="6">
-        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[21]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[21]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F13" s="6">
-        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[21]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[21]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G13" s="6">
-        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[21]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[21]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H13" s="6">
-        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[21]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[21]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -57768,59 +62449,99 @@
         <v>78</v>
       </c>
       <c r="C14" s="6">
-        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[22]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[22]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D14" s="6">
-        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[22]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[22]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E14" s="6">
-        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[22]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[22]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F14" s="6">
-        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[22]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[22]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G14" s="6">
-        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[22]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[22]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H14" s="6">
-        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[22]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[22]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="35" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="6">
+        <f>VLOOKUP($A$1,[23]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[23]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D15" s="6">
+        <f>VLOOKUP($A$1,[23]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[23]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E15" s="6">
+        <f>VLOOKUP($A$1,[23]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[23]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F15" s="6">
+        <f>VLOOKUP($A$1,[23]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[23]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="6">
+        <f>VLOOKUP($A$1,[23]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[23]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H15" s="6">
+        <f>VLOOKUP($A$1,[23]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[23]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="6">
+        <f>VLOOKUP($A$1,[24]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[24]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="6">
+        <f>VLOOKUP($A$1,[24]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[24]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E16" s="6">
+        <f>VLOOKUP($A$1,[24]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[24]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F16" s="6">
+        <f>VLOOKUP($A$1,[24]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[24]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="6">
+        <f>VLOOKUP($A$1,[24]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[24]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H16" s="6">
+        <f>VLOOKUP($A$1,[24]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[24]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="2:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="37"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B17" s="38"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="40"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B18" s="38"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="40"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="37"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B19" s="38"/>
@@ -57849,7 +62570,7 @@
       <c r="G21" s="39"/>
       <c r="H21" s="40"/>
     </row>
-    <row r="22" spans="2:8" ht="71" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B22" s="38"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -57867,7 +62588,7 @@
       <c r="G23" s="39"/>
       <c r="H23" s="40"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" ht="71" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -57876,18 +62597,36 @@
       <c r="G24" s="39"/>
       <c r="H24" s="40"/>
     </row>
-    <row r="25" spans="2:8" ht="89" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="41"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="43"/>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="38"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="40"/>
+    </row>
+    <row r="27" spans="2:8" ht="89" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="41"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B16:H25"/>
+    <mergeCell ref="B18:H27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -61498,35 +66237,35 @@
       </c>
       <c r="C4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>7.7847658371007794E-2</v>
+        <v>7.7847658E-2</v>
       </c>
       <c r="D4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>3.6327261851874397E-2</v>
+        <v>3.6327261999999999E-2</v>
       </c>
       <c r="E4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>0.142161517086385</v>
+        <v>0.14216151699999999</v>
       </c>
       <c r="F4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>9.5841427190132195E-2</v>
+        <v>9.5841427000000007E-2</v>
       </c>
       <c r="G4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>2.6257487724922101E-2</v>
+        <v>2.6257487999999999E-2</v>
       </c>
       <c r="H4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>8.2692357947368803E-2</v>
+        <v>8.2692357999999994E-2</v>
       </c>
       <c r="I4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(I$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>7.8123502817968704E-2</v>
+        <v>7.8123502999999997E-2</v>
       </c>
       <c r="J4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(J$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>4.45169383008562E-2</v>
+        <v>4.4516937999999999E-2</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -65578,39 +70317,39 @@
       </c>
       <c r="C4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>0.137276543372437</v>
+        <v>0.137276543</v>
       </c>
       <c r="D4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>2.72213274411598E-2</v>
+        <v>2.7221327E-2</v>
       </c>
       <c r="E4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>3.5892942434443201E-2</v>
+        <v>3.5892941999999997E-2</v>
       </c>
       <c r="F4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>7.1687039662798602E-2</v>
+        <v>7.1687039999999994E-2</v>
       </c>
       <c r="G4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>5.7095239140274999E-2</v>
+        <v>5.7095238999999999E-2</v>
       </c>
       <c r="H4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>7.2019616312884699E-2</v>
+        <v>7.2019615999999995E-2</v>
       </c>
       <c r="I4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(I$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>0.136010825155855</v>
+        <v>0.136010825</v>
       </c>
       <c r="J4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(J$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>2.7566750399618301E-2</v>
+        <v>2.7566750000000001E-2</v>
       </c>
       <c r="K4" s="8">
         <f>VLOOKUP($A$1,[12]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(K$2,[12]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
-        <v>4.0093506851275197E-2</v>
+        <v>4.0093507E-2</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
